--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118644154</v>
+        <v>118644504</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,38 +1148,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579992</v>
+        <v>580053</v>
       </c>
       <c r="R6" t="n">
-        <v>7049709</v>
+        <v>7049779</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118644504</v>
+        <v>118644154</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,42 +1264,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580053</v>
+        <v>579992</v>
       </c>
       <c r="R7" t="n">
-        <v>7049779</v>
+        <v>7049709</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118643173</v>
+        <v>118644513</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>57306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580202</v>
+        <v>580057</v>
       </c>
       <c r="R2" t="n">
-        <v>7049653</v>
+        <v>7049777</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -903,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118644274</v>
+        <v>118644154</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,42 +920,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579969</v>
+        <v>579992</v>
       </c>
       <c r="R4" t="n">
-        <v>7049721</v>
+        <v>7049709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118643561</v>
+        <v>118643749</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1064,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580118</v>
+        <v>580116</v>
       </c>
       <c r="R5" t="n">
-        <v>7049814</v>
+        <v>7049726</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22:09</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>22:09</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1137,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118644504</v>
+        <v>118643973</v>
       </c>
       <c r="B6" t="n">
         <v>97846</v>
@@ -1171,7 +1172,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1180,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580053</v>
+        <v>580064</v>
       </c>
       <c r="R6" t="n">
-        <v>7049779</v>
+        <v>7049713</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118644154</v>
+        <v>118643561</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,34 +1269,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579992</v>
+        <v>580118</v>
       </c>
       <c r="R7" t="n">
-        <v>7049709</v>
+        <v>7049814</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118644513</v>
+        <v>118643173</v>
       </c>
       <c r="B8" t="n">
-        <v>57306</v>
+        <v>78484</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,39 +1386,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580057</v>
+        <v>580202</v>
       </c>
       <c r="R8" t="n">
-        <v>7049777</v>
+        <v>7049653</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118643973</v>
+        <v>118644547</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>78220</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,42 +1494,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580064</v>
+        <v>580056</v>
       </c>
       <c r="R9" t="n">
-        <v>7049713</v>
+        <v>7049785</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1570,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118644547</v>
+        <v>118644504</v>
       </c>
       <c r="B10" t="n">
-        <v>78220</v>
+        <v>97846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1609,38 +1606,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580056</v>
+        <v>580053</v>
       </c>
       <c r="R10" t="n">
-        <v>7049785</v>
+        <v>7049779</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:08</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:08</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118643749</v>
+        <v>118644274</v>
       </c>
       <c r="B11" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,31 +1722,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580116</v>
+        <v>579969</v>
       </c>
       <c r="R11" t="n">
-        <v>7049726</v>
+        <v>7049721</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118644513</v>
+        <v>118643173</v>
       </c>
       <c r="B2" t="n">
-        <v>57306</v>
+        <v>78484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580057</v>
+        <v>580202</v>
       </c>
       <c r="R2" t="n">
-        <v>7049777</v>
+        <v>7049653</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118644684</v>
+        <v>118644274</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -827,7 +822,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580133</v>
+        <v>579969</v>
       </c>
       <c r="R3" t="n">
-        <v>7049804</v>
+        <v>7049721</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:19</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:19</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118644154</v>
+        <v>118644504</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +915,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579992</v>
+        <v>580053</v>
       </c>
       <c r="R4" t="n">
-        <v>7049709</v>
+        <v>7049779</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +1019,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118643749</v>
+        <v>118643561</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1065,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580116</v>
+        <v>580118</v>
       </c>
       <c r="R5" t="n">
-        <v>7049726</v>
+        <v>7049814</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118643973</v>
+        <v>118643749</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,30 +1148,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580064</v>
+        <v>580116</v>
       </c>
       <c r="R6" t="n">
-        <v>7049713</v>
+        <v>7049726</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118643561</v>
+        <v>118644547</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>78220</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,39 +1269,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580118</v>
+        <v>580056</v>
       </c>
       <c r="R7" t="n">
-        <v>7049814</v>
+        <v>7049785</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22:09</t>
+          <t>23:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>22:09</t>
+          <t>23:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118643173</v>
+        <v>118644513</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>57306</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,34 +1381,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580202</v>
+        <v>580057</v>
       </c>
       <c r="R8" t="n">
-        <v>7049653</v>
+        <v>7049777</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118644547</v>
+        <v>118644684</v>
       </c>
       <c r="B9" t="n">
-        <v>78220</v>
+        <v>97846</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,38 +1494,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580056</v>
+        <v>580133</v>
       </c>
       <c r="R9" t="n">
-        <v>7049785</v>
+        <v>7049804</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23:08</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>23:08</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,7 +1598,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118644504</v>
+        <v>118643973</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1629,7 +1633,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1638,10 +1642,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580053</v>
+        <v>580064</v>
       </c>
       <c r="R10" t="n">
-        <v>7049779</v>
+        <v>7049713</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1673,7 +1677,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1687,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1714,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118644274</v>
+        <v>118644154</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,42 +1726,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579969</v>
+        <v>579992</v>
       </c>
       <c r="R11" t="n">
-        <v>7049721</v>
+        <v>7049709</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118643173</v>
+        <v>118644684</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580202</v>
+        <v>580133</v>
       </c>
       <c r="R2" t="n">
-        <v>7049653</v>
+        <v>7049804</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118644274</v>
+        <v>118644504</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,7 +826,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579969</v>
+        <v>580053</v>
       </c>
       <c r="R3" t="n">
-        <v>7049721</v>
+        <v>7049779</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118644504</v>
+        <v>118643973</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,7 +942,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -947,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580053</v>
+        <v>580064</v>
       </c>
       <c r="R4" t="n">
-        <v>7049779</v>
+        <v>7049713</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1136,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118643749</v>
+        <v>118643173</v>
       </c>
       <c r="B6" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,39 +1156,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580116</v>
+        <v>580202</v>
       </c>
       <c r="R6" t="n">
-        <v>7049726</v>
+        <v>7049653</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,7 +1255,7 @@
         <v>118644547</v>
       </c>
       <c r="B7" t="n">
-        <v>78220</v>
+        <v>78227</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1365,10 +1364,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118644513</v>
+        <v>118644274</v>
       </c>
       <c r="B8" t="n">
-        <v>57306</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,31 +1376,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1410,10 +1408,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580057</v>
+        <v>579969</v>
       </c>
       <c r="R8" t="n">
-        <v>7049777</v>
+        <v>7049721</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,7 +1443,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1453,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118644684</v>
+        <v>118644154</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>78491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,42 +1492,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580133</v>
+        <v>579992</v>
       </c>
       <c r="R9" t="n">
-        <v>7049804</v>
+        <v>7049709</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1555,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23:19</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1565,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>23:19</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118643973</v>
+        <v>118644513</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>57306</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,30 +1604,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1642,10 +1637,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580064</v>
+        <v>580057</v>
       </c>
       <c r="R10" t="n">
-        <v>7049713</v>
+        <v>7049777</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1672,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1687,7 +1682,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118644154</v>
+        <v>118643749</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,34 +1725,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579992</v>
+        <v>580116</v>
       </c>
       <c r="R11" t="n">
-        <v>7049709</v>
+        <v>7049726</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118644684</v>
+        <v>118644547</v>
       </c>
       <c r="B2" t="n">
-        <v>97853</v>
+        <v>78227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580133</v>
+        <v>580056</v>
       </c>
       <c r="R2" t="n">
-        <v>7049804</v>
+        <v>7049785</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:19</t>
+          <t>23:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:19</t>
+          <t>23:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118644504</v>
+        <v>118643749</v>
       </c>
       <c r="B3" t="n">
-        <v>97853</v>
+        <v>57290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,30 +799,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580053</v>
+        <v>580116</v>
       </c>
       <c r="R3" t="n">
-        <v>7049779</v>
+        <v>7049726</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118643973</v>
+        <v>118643561</v>
       </c>
       <c r="B4" t="n">
-        <v>97853</v>
+        <v>57290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,30 +916,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -951,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580064</v>
+        <v>580118</v>
       </c>
       <c r="R4" t="n">
-        <v>7049713</v>
+        <v>7049814</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118643561</v>
+        <v>118643973</v>
       </c>
       <c r="B5" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,31 +1033,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1068,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580118</v>
+        <v>580064</v>
       </c>
       <c r="R5" t="n">
-        <v>7049814</v>
+        <v>7049713</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22:09</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>22:09</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118643173</v>
+        <v>118644513</v>
       </c>
       <c r="B6" t="n">
-        <v>78491</v>
+        <v>57306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,34 +1153,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580202</v>
+        <v>580057</v>
       </c>
       <c r="R6" t="n">
-        <v>7049653</v>
+        <v>7049777</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118644547</v>
+        <v>118643173</v>
       </c>
       <c r="B7" t="n">
-        <v>78227</v>
+        <v>78491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,21 +1270,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1292,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580056</v>
+        <v>580202</v>
       </c>
       <c r="R7" t="n">
-        <v>7049785</v>
+        <v>7049653</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23:08</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1337,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>23:08</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1480,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118644154</v>
+        <v>118644684</v>
       </c>
       <c r="B9" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,38 +1494,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579992</v>
+        <v>580133</v>
       </c>
       <c r="R9" t="n">
-        <v>7049709</v>
+        <v>7049804</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1565,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118644513</v>
+        <v>118644154</v>
       </c>
       <c r="B10" t="n">
-        <v>57306</v>
+        <v>78491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,39 +1614,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nipan (Nipan), Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580057</v>
+        <v>579992</v>
       </c>
       <c r="R10" t="n">
-        <v>7049777</v>
+        <v>7049709</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118643749</v>
+        <v>118644504</v>
       </c>
       <c r="B11" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,31 +1722,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580116</v>
+        <v>580053</v>
       </c>
       <c r="R11" t="n">
-        <v>7049726</v>
+        <v>7049779</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1824,6 +1824,4679 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123306079</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>580118</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7049697</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123304879</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>580143</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7049655</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123304880</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>580159</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7049755</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123307802</v>
+      </c>
+      <c r="B15" t="n">
+        <v>82553</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>580037</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7049768</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123306981</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>580007</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7049703</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123304172</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>580186</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7049672</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123307604</v>
+      </c>
+      <c r="B18" t="n">
+        <v>82553</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>580021</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7049755</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123307659</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>580022</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7049763</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123307841</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>580049</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7049765</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123303674</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>580206</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7049658</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123309206</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>580174</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7049673</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123308246</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>580053</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7049735</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123307927</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>580078</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7049752</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123306199</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>580119</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7049689</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123306520</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>580082</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7049717</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>123304342</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92233</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>580158</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7049670</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>123305011</v>
+      </c>
+      <c r="B28" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>580151</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7049633</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>123305019</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>580166</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7049779</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>123307053</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>579979</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7049720</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>123306094</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>580111</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7049724</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>123305387</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>580124</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7049764</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>123305088</v>
+      </c>
+      <c r="B33" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>580164</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7049642</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>123308600</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>580103</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7049748</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>123307517</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>580020</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7049752</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>123303895</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92233</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>580189</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7049660</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>123308088</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>580037</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7049732</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>123309023</v>
+      </c>
+      <c r="B38" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>580106</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7049714</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>123309182</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>580139</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7049712</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>123303786</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>580193</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7049674</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123304722</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>580163</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7049654</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>123307482</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>579986</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7049735</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>123306694</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>580043</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7049753</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>123306062</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92233</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>580126</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7049722</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>123307810</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>580037</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7049763</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>123304706</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92233</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>580179</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7049708</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123305283</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>580160</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7049663</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123308517</v>
+      </c>
+      <c r="B48" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>580100</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7049758</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>123304811</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>580141</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7049654</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>123306849</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>580039</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7049688</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>123307035</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>579970</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7049717</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>123307914</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>580053</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7049758</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -2287,10 +2287,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123306981</v>
+        <v>123304172</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2299,38 +2299,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580007</v>
+        <v>580186</v>
       </c>
       <c r="R16" t="n">
-        <v>7049703</v>
+        <v>7049672</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2371,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2381,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,22 +2396,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123304172</v>
+        <v>123306981</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2411,47 +2420,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580186</v>
+        <v>580007</v>
       </c>
       <c r="R17" t="n">
-        <v>7049672</v>
+        <v>7049703</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,12 +2508,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123307659</v>
+        <v>123303674</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2648,21 +2648,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580022</v>
+        <v>580206</v>
       </c>
       <c r="R19" t="n">
-        <v>7049763</v>
+        <v>7049658</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,10 +2744,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123307841</v>
+        <v>123309206</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2756,42 +2756,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580049</v>
+        <v>580174</v>
       </c>
       <c r="R20" t="n">
-        <v>7049765</v>
+        <v>7049673</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2823,7 +2819,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2833,7 +2829,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,10 +2856,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123303674</v>
+        <v>123307659</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2876,21 +2872,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2900,10 +2896,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580206</v>
+        <v>580022</v>
       </c>
       <c r="R21" t="n">
-        <v>7049658</v>
+        <v>7049763</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2935,7 +2931,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2945,7 +2941,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2972,10 +2968,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123309206</v>
+        <v>123307841</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2984,38 +2980,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580174</v>
+        <v>580049</v>
       </c>
       <c r="R22" t="n">
-        <v>7049673</v>
+        <v>7049765</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4002,10 +4002,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123306094</v>
+        <v>123305387</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4018,21 +4018,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580111</v>
+        <v>580124</v>
       </c>
       <c r="R31" t="n">
-        <v>7049724</v>
+        <v>7049764</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4114,10 +4114,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123305387</v>
+        <v>123306094</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4130,21 +4130,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4154,10 +4154,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580124</v>
+        <v>580111</v>
       </c>
       <c r="R32" t="n">
-        <v>7049764</v>
+        <v>7049724</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5366,10 +5366,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123306694</v>
+        <v>123306062</v>
       </c>
       <c r="B43" t="n">
-        <v>98365</v>
+        <v>92233</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5378,42 +5378,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580043</v>
+        <v>580126</v>
       </c>
       <c r="R43" t="n">
-        <v>7049753</v>
+        <v>7049722</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5445,7 +5441,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5455,7 +5451,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5482,10 +5478,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123306062</v>
+        <v>123306694</v>
       </c>
       <c r="B44" t="n">
-        <v>92233</v>
+        <v>98365</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5494,38 +5490,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580126</v>
+        <v>580043</v>
       </c>
       <c r="R44" t="n">
-        <v>7049722</v>
+        <v>7049753</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5818,10 +5818,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123305283</v>
+        <v>123308517</v>
       </c>
       <c r="B47" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5830,42 +5830,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580160</v>
+        <v>580100</v>
       </c>
       <c r="R47" t="n">
-        <v>7049663</v>
+        <v>7049758</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5897,7 +5893,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5907,7 +5903,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5934,10 +5930,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123308517</v>
+        <v>123305283</v>
       </c>
       <c r="B48" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5946,38 +5942,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580100</v>
+        <v>580160</v>
       </c>
       <c r="R48" t="n">
-        <v>7049758</v>
+        <v>7049663</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -2287,10 +2287,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123304172</v>
+        <v>123306981</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2299,47 +2299,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580186</v>
+        <v>580007</v>
       </c>
       <c r="R16" t="n">
-        <v>7049672</v>
+        <v>7049703</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2371,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2381,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,22 +2387,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123306981</v>
+        <v>123304172</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2420,38 +2411,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580007</v>
+        <v>580186</v>
       </c>
       <c r="R17" t="n">
-        <v>7049703</v>
+        <v>7049672</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,12 +2508,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3084,7 +3084,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123308246</v>
+        <v>123306199</v>
       </c>
       <c r="B23" t="n">
         <v>98365</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580053</v>
+        <v>580119</v>
       </c>
       <c r="R23" t="n">
-        <v>7049735</v>
+        <v>7049689</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123307927</v>
+        <v>123306520</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3212,38 +3212,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580078</v>
+        <v>580082</v>
       </c>
       <c r="R24" t="n">
-        <v>7049752</v>
+        <v>7049717</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3275,7 +3279,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3285,7 +3289,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3312,7 +3316,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123306199</v>
+        <v>123308246</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3347,7 +3351,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3356,10 +3360,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580119</v>
+        <v>580053</v>
       </c>
       <c r="R25" t="n">
-        <v>7049689</v>
+        <v>7049735</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3391,7 +3395,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3401,7 +3405,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3428,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123306520</v>
+        <v>123307927</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3440,42 +3444,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580082</v>
+        <v>580078</v>
       </c>
       <c r="R26" t="n">
-        <v>7049717</v>
+        <v>7049752</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4002,10 +4002,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123305387</v>
+        <v>123306094</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4018,21 +4018,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580124</v>
+        <v>580111</v>
       </c>
       <c r="R31" t="n">
-        <v>7049764</v>
+        <v>7049724</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4114,10 +4114,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123306094</v>
+        <v>123305387</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4130,21 +4130,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4154,10 +4154,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580111</v>
+        <v>580124</v>
       </c>
       <c r="R32" t="n">
-        <v>7049724</v>
+        <v>7049764</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4796,10 +4796,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123309023</v>
+        <v>123303786</v>
       </c>
       <c r="B38" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4812,34 +4812,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580106</v>
+        <v>580193</v>
       </c>
       <c r="R38" t="n">
-        <v>7049714</v>
+        <v>7049674</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4871,7 +4876,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4881,7 +4886,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4908,7 +4918,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123309182</v>
+        <v>123304722</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -4948,10 +4958,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580139</v>
+        <v>580163</v>
       </c>
       <c r="R39" t="n">
-        <v>7049712</v>
+        <v>7049654</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4983,7 +4993,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4993,7 +5003,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5020,10 +5030,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123303786</v>
+        <v>123309182</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5036,39 +5046,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580193</v>
+        <v>580139</v>
       </c>
       <c r="R40" t="n">
-        <v>7049674</v>
+        <v>7049712</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5100,7 +5105,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5110,12 +5115,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5142,10 +5142,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123304722</v>
+        <v>123309023</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5158,21 +5158,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580163</v>
+        <v>580106</v>
       </c>
       <c r="R41" t="n">
-        <v>7049654</v>
+        <v>7049714</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5366,10 +5366,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123306062</v>
+        <v>123307810</v>
       </c>
       <c r="B43" t="n">
-        <v>92233</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5378,25 +5378,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580126</v>
+        <v>580037</v>
       </c>
       <c r="R43" t="n">
-        <v>7049722</v>
+        <v>7049763</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5466,22 +5466,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123306694</v>
+        <v>123304706</v>
       </c>
       <c r="B44" t="n">
-        <v>98365</v>
+        <v>92233</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5490,42 +5490,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580043</v>
+        <v>580179</v>
       </c>
       <c r="R44" t="n">
-        <v>7049753</v>
+        <v>7049708</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5557,7 +5553,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5567,7 +5563,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5594,10 +5590,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123307810</v>
+        <v>123306062</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>92233</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5606,25 +5602,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5634,10 +5630,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580037</v>
+        <v>580126</v>
       </c>
       <c r="R45" t="n">
-        <v>7049763</v>
+        <v>7049722</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5669,7 +5665,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5679,7 +5675,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5694,22 +5690,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123304706</v>
+        <v>123306694</v>
       </c>
       <c r="B46" t="n">
-        <v>92233</v>
+        <v>98365</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5718,38 +5714,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580179</v>
+        <v>580043</v>
       </c>
       <c r="R46" t="n">
-        <v>7049708</v>
+        <v>7049753</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -2287,10 +2287,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123306981</v>
+        <v>123304172</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2299,38 +2299,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580007</v>
+        <v>580186</v>
       </c>
       <c r="R16" t="n">
-        <v>7049703</v>
+        <v>7049672</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2371,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2381,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2387,22 +2396,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123304172</v>
+        <v>123306981</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2411,47 +2420,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580186</v>
+        <v>580007</v>
       </c>
       <c r="R17" t="n">
-        <v>7049672</v>
+        <v>7049703</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,12 +2508,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3084,7 +3084,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123306199</v>
+        <v>123306520</v>
       </c>
       <c r="B23" t="n">
         <v>98365</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580119</v>
+        <v>580082</v>
       </c>
       <c r="R23" t="n">
-        <v>7049689</v>
+        <v>7049717</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123306520</v>
+        <v>123307927</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3212,42 +3212,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580082</v>
+        <v>580078</v>
       </c>
       <c r="R24" t="n">
-        <v>7049717</v>
+        <v>7049752</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3279,7 +3275,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3285,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3432,10 +3428,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123307927</v>
+        <v>123306199</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3444,38 +3440,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580078</v>
+        <v>580119</v>
       </c>
       <c r="R26" t="n">
-        <v>7049752</v>
+        <v>7049689</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4796,10 +4796,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123303786</v>
+        <v>123309023</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4812,39 +4812,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580193</v>
+        <v>580106</v>
       </c>
       <c r="R38" t="n">
-        <v>7049674</v>
+        <v>7049714</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4876,7 +4871,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4886,12 +4881,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4918,7 +4908,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123304722</v>
+        <v>123309182</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -4958,10 +4948,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580163</v>
+        <v>580139</v>
       </c>
       <c r="R39" t="n">
-        <v>7049654</v>
+        <v>7049712</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4993,7 +4983,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5003,7 +4993,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5030,10 +5020,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123309182</v>
+        <v>123303786</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5046,34 +5036,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580139</v>
+        <v>580193</v>
       </c>
       <c r="R40" t="n">
-        <v>7049712</v>
+        <v>7049674</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5105,7 +5100,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5115,7 +5110,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5142,10 +5142,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123309023</v>
+        <v>123304722</v>
       </c>
       <c r="B41" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5158,21 +5158,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580106</v>
+        <v>580163</v>
       </c>
       <c r="R41" t="n">
-        <v>7049714</v>
+        <v>7049654</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -2287,10 +2287,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123304172</v>
+        <v>123306981</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2299,47 +2299,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580186</v>
+        <v>580007</v>
       </c>
       <c r="R16" t="n">
-        <v>7049672</v>
+        <v>7049703</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2371,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2381,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,22 +2387,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123306981</v>
+        <v>123304172</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2420,38 +2411,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580007</v>
+        <v>580186</v>
       </c>
       <c r="R17" t="n">
-        <v>7049703</v>
+        <v>7049672</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,12 +2508,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3084,7 +3084,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123306520</v>
+        <v>123306199</v>
       </c>
       <c r="B23" t="n">
         <v>98365</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580082</v>
+        <v>580119</v>
       </c>
       <c r="R23" t="n">
-        <v>7049717</v>
+        <v>7049689</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3200,10 +3200,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123307927</v>
+        <v>123306520</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3212,38 +3212,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580078</v>
+        <v>580082</v>
       </c>
       <c r="R24" t="n">
-        <v>7049752</v>
+        <v>7049717</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3275,7 +3279,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3285,7 +3289,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3428,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123306199</v>
+        <v>123307927</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3440,42 +3444,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580119</v>
+        <v>580078</v>
       </c>
       <c r="R26" t="n">
-        <v>7049689</v>
+        <v>7049752</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -1826,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123306079</v>
+        <v>123303674</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580118</v>
+        <v>580206</v>
       </c>
       <c r="R12" t="n">
-        <v>7049697</v>
+        <v>7049658</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123304879</v>
+        <v>123307659</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>79850</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,42 +1950,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580143</v>
+        <v>580022</v>
       </c>
       <c r="R13" t="n">
-        <v>7049655</v>
+        <v>7049763</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123304880</v>
+        <v>123304879</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2089,12 +2085,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2103,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580159</v>
+        <v>580143</v>
       </c>
       <c r="R14" t="n">
-        <v>7049755</v>
+        <v>7049655</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2138,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2148,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,22 +2154,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123307802</v>
+        <v>123306520</v>
       </c>
       <c r="B15" t="n">
-        <v>82553</v>
+        <v>98368</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2187,38 +2178,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580037</v>
+        <v>580082</v>
       </c>
       <c r="R15" t="n">
-        <v>7049768</v>
+        <v>7049717</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2250,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2260,7 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,10 +2282,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123306981</v>
+        <v>123309182</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2327,10 +2322,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580007</v>
+        <v>580139</v>
       </c>
       <c r="R16" t="n">
-        <v>7049703</v>
+        <v>7049712</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2362,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2372,7 +2367,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123304172</v>
+        <v>123306079</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>78769</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2411,47 +2406,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580186</v>
+        <v>580118</v>
       </c>
       <c r="R17" t="n">
-        <v>7049672</v>
+        <v>7049697</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2483,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2493,7 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,22 +2494,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123307604</v>
+        <v>123309206</v>
       </c>
       <c r="B18" t="n">
-        <v>82553</v>
+        <v>78769</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2536,21 +2522,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2560,10 +2546,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580021</v>
+        <v>580174</v>
       </c>
       <c r="R18" t="n">
-        <v>7049755</v>
+        <v>7049673</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2605,7 +2591,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123303674</v>
+        <v>123305387</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2672,10 +2658,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580206</v>
+        <v>580124</v>
       </c>
       <c r="R19" t="n">
-        <v>7049658</v>
+        <v>7049764</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2707,7 +2693,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2717,7 +2703,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2732,22 +2718,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123309206</v>
+        <v>123307604</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>82556</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2760,21 +2746,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2784,10 +2770,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580174</v>
+        <v>580021</v>
       </c>
       <c r="R20" t="n">
-        <v>7049673</v>
+        <v>7049755</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2819,7 +2805,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2829,7 +2815,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2856,10 +2842,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123307659</v>
+        <v>123306849</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2872,21 +2858,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2896,10 +2882,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580022</v>
+        <v>580039</v>
       </c>
       <c r="R21" t="n">
-        <v>7049763</v>
+        <v>7049688</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2931,7 +2917,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2941,7 +2927,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2968,10 +2954,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123307841</v>
+        <v>123307482</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>78769</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2980,42 +2966,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580049</v>
+        <v>579986</v>
       </c>
       <c r="R22" t="n">
-        <v>7049765</v>
+        <v>7049735</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,7 +3029,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,7 +3039,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,10 +3066,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123306199</v>
+        <v>123307914</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>79850</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3096,42 +3078,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580119</v>
+        <v>580053</v>
       </c>
       <c r="R23" t="n">
-        <v>7049689</v>
+        <v>7049758</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3163,7 +3141,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3173,7 +3151,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3200,10 +3178,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123306520</v>
+        <v>123304172</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3235,7 +3213,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3244,10 +3227,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580082</v>
+        <v>580186</v>
       </c>
       <c r="R24" t="n">
-        <v>7049717</v>
+        <v>7049672</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3279,7 +3262,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3289,7 +3272,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3304,22 +3287,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123308246</v>
+        <v>123304342</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>92236</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3328,42 +3311,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580053</v>
+        <v>580158</v>
       </c>
       <c r="R25" t="n">
-        <v>7049735</v>
+        <v>7049670</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3395,7 +3374,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3405,7 +3384,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3432,10 +3411,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123307927</v>
+        <v>123304811</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3472,10 +3451,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580078</v>
+        <v>580141</v>
       </c>
       <c r="R26" t="n">
-        <v>7049752</v>
+        <v>7049654</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3507,7 +3486,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3517,7 +3496,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3544,10 +3523,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123304342</v>
+        <v>123307841</v>
       </c>
       <c r="B27" t="n">
-        <v>92233</v>
+        <v>98368</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3556,38 +3535,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580158</v>
+        <v>580049</v>
       </c>
       <c r="R27" t="n">
-        <v>7049670</v>
+        <v>7049765</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3619,7 +3602,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3629,7 +3612,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3656,10 +3639,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123305011</v>
+        <v>123305283</v>
       </c>
       <c r="B28" t="n">
-        <v>90952</v>
+        <v>98368</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3668,38 +3651,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580151</v>
+        <v>580160</v>
       </c>
       <c r="R28" t="n">
-        <v>7049633</v>
+        <v>7049663</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3731,7 +3718,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3741,7 +3728,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3768,10 +3755,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123305019</v>
+        <v>123305011</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>90955</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3784,39 +3771,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580166</v>
+        <v>580151</v>
       </c>
       <c r="R29" t="n">
-        <v>7049779</v>
+        <v>7049633</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3848,7 +3830,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3858,12 +3840,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3878,22 +3855,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123307053</v>
+        <v>123305019</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3906,34 +3883,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>579979</v>
+        <v>580166</v>
       </c>
       <c r="R30" t="n">
-        <v>7049720</v>
+        <v>7049779</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3965,7 +3947,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3975,7 +3957,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3990,22 +3977,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123306094</v>
+        <v>123309023</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>90955</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4018,21 +4005,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4042,10 +4029,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580111</v>
+        <v>580106</v>
       </c>
       <c r="R31" t="n">
-        <v>7049724</v>
+        <v>7049714</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4077,7 +4064,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4087,7 +4074,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4102,22 +4089,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123305387</v>
+        <v>123303895</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>92236</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4126,25 +4113,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4154,10 +4141,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580124</v>
+        <v>580189</v>
       </c>
       <c r="R32" t="n">
-        <v>7049764</v>
+        <v>7049660</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4189,7 +4176,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4199,7 +4186,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4214,22 +4201,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123305088</v>
+        <v>123308600</v>
       </c>
       <c r="B33" t="n">
-        <v>90952</v>
+        <v>79850</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4242,21 +4229,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4266,10 +4253,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580164</v>
+        <v>580103</v>
       </c>
       <c r="R33" t="n">
-        <v>7049642</v>
+        <v>7049748</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4301,7 +4288,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4311,7 +4298,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4338,10 +4325,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123308600</v>
+        <v>123307810</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4354,21 +4341,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4378,10 +4365,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580103</v>
+        <v>580037</v>
       </c>
       <c r="R34" t="n">
-        <v>7049748</v>
+        <v>7049763</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4413,7 +4400,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4423,7 +4410,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4450,10 +4437,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123307517</v>
+        <v>123306094</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4466,21 +4453,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4490,10 +4477,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580020</v>
+        <v>580111</v>
       </c>
       <c r="R35" t="n">
-        <v>7049752</v>
+        <v>7049724</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4525,7 +4512,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4535,7 +4522,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4550,22 +4537,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123303895</v>
+        <v>123307517</v>
       </c>
       <c r="B36" t="n">
-        <v>92233</v>
+        <v>78769</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4574,25 +4561,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4602,10 +4589,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580189</v>
+        <v>580020</v>
       </c>
       <c r="R36" t="n">
-        <v>7049660</v>
+        <v>7049752</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4637,7 +4624,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4647,7 +4634,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4674,10 +4661,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123308088</v>
+        <v>123305088</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>90955</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4690,39 +4677,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580037</v>
+        <v>580164</v>
       </c>
       <c r="R37" t="n">
-        <v>7049732</v>
+        <v>7049642</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4754,7 +4736,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4764,12 +4746,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4796,10 +4773,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123309023</v>
+        <v>123307927</v>
       </c>
       <c r="B38" t="n">
-        <v>90952</v>
+        <v>79850</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4812,21 +4789,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4836,10 +4813,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580106</v>
+        <v>580078</v>
       </c>
       <c r="R38" t="n">
-        <v>7049714</v>
+        <v>7049752</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4871,7 +4848,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4881,7 +4858,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4908,10 +4885,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123309182</v>
+        <v>123303786</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4924,34 +4901,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580139</v>
+        <v>580193</v>
       </c>
       <c r="R39" t="n">
-        <v>7049712</v>
+        <v>7049674</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4983,7 +4965,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4993,7 +4975,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5020,10 +5007,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123303786</v>
+        <v>123307802</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>82556</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5036,39 +5023,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580193</v>
+        <v>580037</v>
       </c>
       <c r="R40" t="n">
-        <v>7049674</v>
+        <v>7049768</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5100,7 +5082,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5110,12 +5092,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5142,10 +5119,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123304722</v>
+        <v>123307053</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5182,10 +5159,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580163</v>
+        <v>579979</v>
       </c>
       <c r="R41" t="n">
-        <v>7049654</v>
+        <v>7049720</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5217,7 +5194,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5227,7 +5204,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5254,10 +5231,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123307482</v>
+        <v>123304706</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>92236</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5266,25 +5243,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5294,10 +5271,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>579986</v>
+        <v>580179</v>
       </c>
       <c r="R42" t="n">
-        <v>7049735</v>
+        <v>7049708</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5329,7 +5306,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5339,7 +5316,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5354,22 +5331,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123307810</v>
+        <v>123306694</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>98368</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5378,38 +5355,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580037</v>
+        <v>580043</v>
       </c>
       <c r="R43" t="n">
-        <v>7049763</v>
+        <v>7049753</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5441,7 +5422,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5451,7 +5432,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5466,22 +5447,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123304706</v>
+        <v>123306199</v>
       </c>
       <c r="B44" t="n">
-        <v>92233</v>
+        <v>98368</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5490,38 +5471,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580179</v>
+        <v>580119</v>
       </c>
       <c r="R44" t="n">
-        <v>7049708</v>
+        <v>7049689</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5553,7 +5538,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5563,7 +5548,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5578,22 +5563,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123306062</v>
+        <v>123308517</v>
       </c>
       <c r="B45" t="n">
-        <v>92233</v>
+        <v>90955</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5602,25 +5587,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5630,10 +5615,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580126</v>
+        <v>580100</v>
       </c>
       <c r="R45" t="n">
-        <v>7049722</v>
+        <v>7049758</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5665,7 +5650,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5675,7 +5660,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5690,22 +5675,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123306694</v>
+        <v>123306981</v>
       </c>
       <c r="B46" t="n">
-        <v>98365</v>
+        <v>78769</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5714,42 +5699,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580043</v>
+        <v>580007</v>
       </c>
       <c r="R46" t="n">
-        <v>7049753</v>
+        <v>7049703</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5781,7 +5762,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5791,7 +5772,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5806,22 +5787,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123308517</v>
+        <v>123304880</v>
       </c>
       <c r="B47" t="n">
-        <v>90952</v>
+        <v>98368</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5830,38 +5811,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580100</v>
+        <v>580159</v>
       </c>
       <c r="R47" t="n">
-        <v>7049758</v>
+        <v>7049755</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5893,7 +5883,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5903,7 +5893,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5918,22 +5908,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123305283</v>
+        <v>123308246</v>
       </c>
       <c r="B48" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5965,7 +5955,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5974,10 +5964,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580160</v>
+        <v>580053</v>
       </c>
       <c r="R48" t="n">
-        <v>7049663</v>
+        <v>7049735</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6009,7 +5999,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6019,7 +6009,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6046,10 +6036,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123304811</v>
+        <v>123306062</v>
       </c>
       <c r="B49" t="n">
-        <v>79847</v>
+        <v>92236</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6058,25 +6048,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6086,10 +6076,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580141</v>
+        <v>580126</v>
       </c>
       <c r="R49" t="n">
-        <v>7049654</v>
+        <v>7049722</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6121,7 +6111,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6131,7 +6121,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6146,22 +6136,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123306849</v>
+        <v>123304722</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6198,10 +6188,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580039</v>
+        <v>580163</v>
       </c>
       <c r="R50" t="n">
-        <v>7049688</v>
+        <v>7049654</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6233,7 +6223,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6243,7 +6233,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6270,10 +6260,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123307035</v>
+        <v>123308088</v>
       </c>
       <c r="B51" t="n">
-        <v>57494</v>
+        <v>57481</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6286,16 +6276,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6315,10 +6305,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>579970</v>
+        <v>580037</v>
       </c>
       <c r="R51" t="n">
-        <v>7049717</v>
+        <v>7049732</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6350,7 +6340,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6360,7 +6350,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6387,10 +6382,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123307914</v>
+        <v>123307035</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>57497</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6403,34 +6398,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580053</v>
+        <v>579970</v>
       </c>
       <c r="R52" t="n">
-        <v>7049758</v>
+        <v>7049717</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -1826,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123303674</v>
+        <v>123305387</v>
       </c>
       <c r="B12" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580206</v>
+        <v>580124</v>
       </c>
       <c r="R12" t="n">
-        <v>7049658</v>
+        <v>7049764</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,22 +1926,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123307659</v>
+        <v>123307517</v>
       </c>
       <c r="B13" t="n">
-        <v>79850</v>
+        <v>78771</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,21 +1954,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580022</v>
+        <v>580020</v>
       </c>
       <c r="R13" t="n">
-        <v>7049763</v>
+        <v>7049752</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123304879</v>
+        <v>123304706</v>
       </c>
       <c r="B14" t="n">
-        <v>98368</v>
+        <v>92238</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,42 +2062,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580143</v>
+        <v>580179</v>
       </c>
       <c r="R14" t="n">
-        <v>7049655</v>
+        <v>7049708</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2125,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2135,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,22 +2150,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123306520</v>
+        <v>123304722</v>
       </c>
       <c r="B15" t="n">
-        <v>98368</v>
+        <v>78771</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,42 +2174,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580082</v>
+        <v>580163</v>
       </c>
       <c r="R15" t="n">
-        <v>7049717</v>
+        <v>7049654</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2237,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2247,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123309182</v>
+        <v>123307802</v>
       </c>
       <c r="B16" t="n">
-        <v>78769</v>
+        <v>82558</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2298,21 +2290,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2322,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580139</v>
+        <v>580037</v>
       </c>
       <c r="R16" t="n">
-        <v>7049712</v>
+        <v>7049768</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,10 +2386,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123306079</v>
+        <v>123305088</v>
       </c>
       <c r="B17" t="n">
-        <v>78769</v>
+        <v>90957</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2410,21 +2402,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2434,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580118</v>
+        <v>580164</v>
       </c>
       <c r="R17" t="n">
-        <v>7049697</v>
+        <v>7049642</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,7 +2461,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2471,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,10 +2498,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123309206</v>
+        <v>123307914</v>
       </c>
       <c r="B18" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2522,21 +2514,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2546,10 +2538,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580174</v>
+        <v>580053</v>
       </c>
       <c r="R18" t="n">
-        <v>7049673</v>
+        <v>7049758</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,7 +2573,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2583,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,10 +2610,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123305387</v>
+        <v>123308088</v>
       </c>
       <c r="B19" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2634,34 +2626,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580124</v>
+        <v>580037</v>
       </c>
       <c r="R19" t="n">
-        <v>7049764</v>
+        <v>7049732</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2693,7 +2690,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2703,7 +2700,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2718,22 +2720,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123307604</v>
+        <v>123306520</v>
       </c>
       <c r="B20" t="n">
-        <v>82556</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2742,38 +2744,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580021</v>
+        <v>580082</v>
       </c>
       <c r="R20" t="n">
-        <v>7049755</v>
+        <v>7049717</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2805,7 +2811,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2815,7 +2821,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2842,10 +2848,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123306849</v>
+        <v>123306079</v>
       </c>
       <c r="B21" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2882,10 +2888,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580039</v>
+        <v>580118</v>
       </c>
       <c r="R21" t="n">
-        <v>7049688</v>
+        <v>7049697</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2917,7 +2923,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2927,7 +2933,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2954,10 +2960,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123307482</v>
+        <v>123304342</v>
       </c>
       <c r="B22" t="n">
-        <v>78769</v>
+        <v>92238</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2966,25 +2972,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2994,10 +3000,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579986</v>
+        <v>580158</v>
       </c>
       <c r="R22" t="n">
-        <v>7049735</v>
+        <v>7049670</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3029,7 +3035,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3039,7 +3045,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3066,10 +3072,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123307914</v>
+        <v>123307810</v>
       </c>
       <c r="B23" t="n">
-        <v>79850</v>
+        <v>78771</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3082,21 +3088,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3106,10 +3112,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580053</v>
+        <v>580037</v>
       </c>
       <c r="R23" t="n">
-        <v>7049758</v>
+        <v>7049763</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3141,7 +3147,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3151,7 +3157,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3178,10 +3184,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123304172</v>
+        <v>123303786</v>
       </c>
       <c r="B24" t="n">
-        <v>98368</v>
+        <v>57481</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3190,35 +3196,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3227,10 +3229,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580186</v>
+        <v>580193</v>
       </c>
       <c r="R24" t="n">
-        <v>7049672</v>
+        <v>7049674</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3262,7 +3264,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3272,7 +3274,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3287,22 +3294,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123304342</v>
+        <v>123305011</v>
       </c>
       <c r="B25" t="n">
-        <v>92236</v>
+        <v>90957</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3311,25 +3318,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3339,10 +3346,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580158</v>
+        <v>580151</v>
       </c>
       <c r="R25" t="n">
-        <v>7049670</v>
+        <v>7049633</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3374,7 +3381,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3384,7 +3391,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3411,10 +3418,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123304811</v>
+        <v>123309023</v>
       </c>
       <c r="B26" t="n">
-        <v>79850</v>
+        <v>90957</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3427,21 +3434,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3451,10 +3458,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580141</v>
+        <v>580106</v>
       </c>
       <c r="R26" t="n">
-        <v>7049654</v>
+        <v>7049714</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3486,7 +3493,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3496,7 +3503,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3523,10 +3530,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123307841</v>
+        <v>123308246</v>
       </c>
       <c r="B27" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3558,7 +3565,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3567,10 +3574,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580049</v>
+        <v>580053</v>
       </c>
       <c r="R27" t="n">
-        <v>7049765</v>
+        <v>7049735</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3602,7 +3609,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3612,7 +3619,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3639,10 +3646,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123305283</v>
+        <v>123306981</v>
       </c>
       <c r="B28" t="n">
-        <v>98368</v>
+        <v>78771</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3651,42 +3658,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580160</v>
+        <v>580007</v>
       </c>
       <c r="R28" t="n">
-        <v>7049663</v>
+        <v>7049703</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3718,7 +3721,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3728,7 +3731,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3755,10 +3758,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123305011</v>
+        <v>123306062</v>
       </c>
       <c r="B29" t="n">
-        <v>90955</v>
+        <v>92238</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3767,25 +3770,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3795,10 +3798,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580151</v>
+        <v>580126</v>
       </c>
       <c r="R29" t="n">
-        <v>7049633</v>
+        <v>7049722</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3830,7 +3833,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3840,7 +3843,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3855,22 +3858,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123305019</v>
+        <v>123307053</v>
       </c>
       <c r="B30" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3883,39 +3886,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580166</v>
+        <v>579979</v>
       </c>
       <c r="R30" t="n">
-        <v>7049779</v>
+        <v>7049720</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3947,7 +3945,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3957,12 +3955,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3977,22 +3970,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123309023</v>
+        <v>123307035</v>
       </c>
       <c r="B31" t="n">
-        <v>90955</v>
+        <v>57497</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4005,34 +3998,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580106</v>
+        <v>579970</v>
       </c>
       <c r="R31" t="n">
-        <v>7049714</v>
+        <v>7049717</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4064,7 +4062,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4074,7 +4072,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4101,10 +4099,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123303895</v>
+        <v>123306849</v>
       </c>
       <c r="B32" t="n">
-        <v>92236</v>
+        <v>78771</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4113,25 +4111,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4141,10 +4139,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580189</v>
+        <v>580039</v>
       </c>
       <c r="R32" t="n">
-        <v>7049660</v>
+        <v>7049688</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4176,7 +4174,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4186,7 +4184,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4213,10 +4211,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123308600</v>
+        <v>123306199</v>
       </c>
       <c r="B33" t="n">
-        <v>79850</v>
+        <v>98370</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4225,38 +4223,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580103</v>
+        <v>580119</v>
       </c>
       <c r="R33" t="n">
-        <v>7049748</v>
+        <v>7049689</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4288,7 +4290,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4298,7 +4300,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4325,10 +4327,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123307810</v>
+        <v>123308600</v>
       </c>
       <c r="B34" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4341,21 +4343,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4365,10 +4367,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580037</v>
+        <v>580103</v>
       </c>
       <c r="R34" t="n">
-        <v>7049763</v>
+        <v>7049748</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4400,7 +4402,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4410,7 +4412,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4437,10 +4439,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123306094</v>
+        <v>123307841</v>
       </c>
       <c r="B35" t="n">
-        <v>79850</v>
+        <v>98370</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4449,38 +4451,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580111</v>
+        <v>580049</v>
       </c>
       <c r="R35" t="n">
-        <v>7049724</v>
+        <v>7049765</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4512,7 +4518,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4522,7 +4528,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4537,22 +4543,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123307517</v>
+        <v>123307659</v>
       </c>
       <c r="B36" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4565,21 +4571,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4589,10 +4595,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580020</v>
+        <v>580022</v>
       </c>
       <c r="R36" t="n">
-        <v>7049752</v>
+        <v>7049763</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4624,7 +4630,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4634,7 +4640,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4661,10 +4667,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123305088</v>
+        <v>123304879</v>
       </c>
       <c r="B37" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4673,38 +4679,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580164</v>
+        <v>580143</v>
       </c>
       <c r="R37" t="n">
-        <v>7049642</v>
+        <v>7049655</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4736,7 +4746,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4746,7 +4756,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4773,10 +4783,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123307927</v>
+        <v>123308517</v>
       </c>
       <c r="B38" t="n">
-        <v>79850</v>
+        <v>90957</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4789,21 +4799,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4813,10 +4823,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580078</v>
+        <v>580100</v>
       </c>
       <c r="R38" t="n">
-        <v>7049752</v>
+        <v>7049758</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4848,7 +4858,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4858,7 +4868,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4885,10 +4895,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123303786</v>
+        <v>123306094</v>
       </c>
       <c r="B39" t="n">
-        <v>57481</v>
+        <v>79852</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4901,39 +4911,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580193</v>
+        <v>580111</v>
       </c>
       <c r="R39" t="n">
-        <v>7049674</v>
+        <v>7049724</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4965,7 +4970,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4975,12 +4980,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4995,22 +4995,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123307802</v>
+        <v>123304811</v>
       </c>
       <c r="B40" t="n">
-        <v>82556</v>
+        <v>79852</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5023,21 +5023,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5047,10 +5047,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580037</v>
+        <v>580141</v>
       </c>
       <c r="R40" t="n">
-        <v>7049768</v>
+        <v>7049654</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5119,10 +5119,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123307053</v>
+        <v>123309206</v>
       </c>
       <c r="B41" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>579979</v>
+        <v>580174</v>
       </c>
       <c r="R41" t="n">
-        <v>7049720</v>
+        <v>7049673</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5231,10 +5231,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123304706</v>
+        <v>123304880</v>
       </c>
       <c r="B42" t="n">
-        <v>92236</v>
+        <v>98370</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5243,38 +5243,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580179</v>
+        <v>580159</v>
       </c>
       <c r="R42" t="n">
-        <v>7049708</v>
+        <v>7049755</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5306,7 +5315,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5316,7 +5325,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5343,10 +5352,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123306694</v>
+        <v>123307927</v>
       </c>
       <c r="B43" t="n">
-        <v>98368</v>
+        <v>79852</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5355,42 +5364,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580043</v>
+        <v>580078</v>
       </c>
       <c r="R43" t="n">
-        <v>7049753</v>
+        <v>7049752</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5422,7 +5427,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5432,7 +5437,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5447,22 +5452,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123306199</v>
+        <v>123307482</v>
       </c>
       <c r="B44" t="n">
-        <v>98368</v>
+        <v>78771</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5471,42 +5476,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580119</v>
+        <v>579986</v>
       </c>
       <c r="R44" t="n">
-        <v>7049689</v>
+        <v>7049735</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5538,7 +5539,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5548,7 +5549,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5575,10 +5576,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123308517</v>
+        <v>123305283</v>
       </c>
       <c r="B45" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5587,38 +5588,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580100</v>
+        <v>580160</v>
       </c>
       <c r="R45" t="n">
-        <v>7049758</v>
+        <v>7049663</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5650,7 +5655,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5660,7 +5665,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5687,10 +5692,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123306981</v>
+        <v>123307604</v>
       </c>
       <c r="B46" t="n">
-        <v>78769</v>
+        <v>82558</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5703,21 +5708,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5727,10 +5732,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580007</v>
+        <v>580021</v>
       </c>
       <c r="R46" t="n">
-        <v>7049703</v>
+        <v>7049755</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5762,7 +5767,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5772,7 +5777,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5799,10 +5804,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123304880</v>
+        <v>123309182</v>
       </c>
       <c r="B47" t="n">
-        <v>98368</v>
+        <v>78771</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5811,47 +5816,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580159</v>
+        <v>580139</v>
       </c>
       <c r="R47" t="n">
-        <v>7049755</v>
+        <v>7049712</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5883,7 +5879,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5893,7 +5889,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5908,22 +5904,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123308246</v>
+        <v>123305019</v>
       </c>
       <c r="B48" t="n">
-        <v>98368</v>
+        <v>57481</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5932,30 +5928,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5964,10 +5961,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580053</v>
+        <v>580166</v>
       </c>
       <c r="R48" t="n">
-        <v>7049735</v>
+        <v>7049779</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5999,7 +5996,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6009,7 +6006,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6024,22 +6026,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123306062</v>
+        <v>123306694</v>
       </c>
       <c r="B49" t="n">
-        <v>92236</v>
+        <v>98370</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6048,38 +6050,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580126</v>
+        <v>580043</v>
       </c>
       <c r="R49" t="n">
-        <v>7049722</v>
+        <v>7049753</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6111,7 +6117,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6121,7 +6127,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6148,10 +6154,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123304722</v>
+        <v>123304172</v>
       </c>
       <c r="B50" t="n">
-        <v>78769</v>
+        <v>98370</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6160,38 +6166,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580163</v>
+        <v>580186</v>
       </c>
       <c r="R50" t="n">
-        <v>7049654</v>
+        <v>7049672</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6223,7 +6238,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6233,7 +6248,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6248,22 +6263,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123308088</v>
+        <v>123303895</v>
       </c>
       <c r="B51" t="n">
-        <v>57481</v>
+        <v>92238</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6272,43 +6287,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580037</v>
+        <v>580189</v>
       </c>
       <c r="R51" t="n">
-        <v>7049732</v>
+        <v>7049660</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6340,7 +6350,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6350,12 +6360,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6382,10 +6387,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123307035</v>
+        <v>123303674</v>
       </c>
       <c r="B52" t="n">
-        <v>57497</v>
+        <v>78771</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6398,39 +6403,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>579970</v>
+        <v>580206</v>
       </c>
       <c r="R52" t="n">
-        <v>7049717</v>
+        <v>7049658</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -2162,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123304722</v>
+        <v>123307914</v>
       </c>
       <c r="B15" t="n">
-        <v>78771</v>
+        <v>79852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,21 +2178,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580163</v>
+        <v>580053</v>
       </c>
       <c r="R15" t="n">
-        <v>7049654</v>
+        <v>7049758</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123307802</v>
+        <v>123308088</v>
       </c>
       <c r="B16" t="n">
-        <v>82558</v>
+        <v>57481</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,24 +2290,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
@@ -2317,7 +2322,7 @@
         <v>580037</v>
       </c>
       <c r="R16" t="n">
-        <v>7049768</v>
+        <v>7049732</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2349,7 +2354,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2364,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,10 +2396,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123305088</v>
+        <v>123306520</v>
       </c>
       <c r="B17" t="n">
-        <v>90957</v>
+        <v>98370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2398,38 +2408,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580164</v>
+        <v>580082</v>
       </c>
       <c r="R17" t="n">
-        <v>7049642</v>
+        <v>7049717</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2471,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2498,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123307914</v>
+        <v>123304722</v>
       </c>
       <c r="B18" t="n">
-        <v>79852</v>
+        <v>78771</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,21 +2528,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2538,10 +2552,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580053</v>
+        <v>580163</v>
       </c>
       <c r="R18" t="n">
-        <v>7049758</v>
+        <v>7049654</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2573,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2597,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,10 +2624,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123308088</v>
+        <v>123307802</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
+        <v>82558</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2626,29 +2640,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
@@ -2658,7 +2667,7 @@
         <v>580037</v>
       </c>
       <c r="R19" t="n">
-        <v>7049732</v>
+        <v>7049768</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2690,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2700,12 +2709,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2732,10 +2736,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123306520</v>
+        <v>123305088</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>90957</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2744,42 +2748,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580082</v>
+        <v>580164</v>
       </c>
       <c r="R20" t="n">
-        <v>7049717</v>
+        <v>7049642</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3982,10 +3982,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123307035</v>
+        <v>123306849</v>
       </c>
       <c r="B31" t="n">
-        <v>57497</v>
+        <v>78771</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3998,39 +3998,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>579970</v>
+        <v>580039</v>
       </c>
       <c r="R31" t="n">
-        <v>7049717</v>
+        <v>7049688</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4062,7 +4057,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4072,7 +4067,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4099,10 +4094,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123306849</v>
+        <v>123307035</v>
       </c>
       <c r="B32" t="n">
-        <v>78771</v>
+        <v>57497</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4115,34 +4110,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580039</v>
+        <v>579970</v>
       </c>
       <c r="R32" t="n">
-        <v>7049688</v>
+        <v>7049717</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4327,10 +4327,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123308600</v>
+        <v>123307841</v>
       </c>
       <c r="B34" t="n">
-        <v>79852</v>
+        <v>98370</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4339,38 +4339,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580103</v>
+        <v>580049</v>
       </c>
       <c r="R34" t="n">
-        <v>7049748</v>
+        <v>7049765</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4402,7 +4406,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4412,7 +4416,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4439,10 +4443,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123307841</v>
+        <v>123308600</v>
       </c>
       <c r="B35" t="n">
-        <v>98370</v>
+        <v>79852</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4451,42 +4455,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580049</v>
+        <v>580103</v>
       </c>
       <c r="R35" t="n">
-        <v>7049765</v>
+        <v>7049748</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5692,10 +5692,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123307604</v>
+        <v>123305019</v>
       </c>
       <c r="B46" t="n">
-        <v>82558</v>
+        <v>57481</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5708,34 +5708,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580021</v>
+        <v>580166</v>
       </c>
       <c r="R46" t="n">
-        <v>7049755</v>
+        <v>7049779</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5767,7 +5772,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5777,7 +5782,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5792,22 +5802,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123309182</v>
+        <v>123306694</v>
       </c>
       <c r="B47" t="n">
-        <v>78771</v>
+        <v>98370</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5816,38 +5826,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580139</v>
+        <v>580043</v>
       </c>
       <c r="R47" t="n">
-        <v>7049712</v>
+        <v>7049753</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5879,7 +5893,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5889,7 +5903,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5904,22 +5918,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123305019</v>
+        <v>123304172</v>
       </c>
       <c r="B48" t="n">
-        <v>57481</v>
+        <v>98370</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5928,31 +5942,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5961,10 +5979,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580166</v>
+        <v>580186</v>
       </c>
       <c r="R48" t="n">
-        <v>7049779</v>
+        <v>7049672</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5996,7 +6014,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6006,12 +6024,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6038,10 +6051,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123306694</v>
+        <v>123307604</v>
       </c>
       <c r="B49" t="n">
-        <v>98370</v>
+        <v>82558</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6050,42 +6063,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580043</v>
+        <v>580021</v>
       </c>
       <c r="R49" t="n">
-        <v>7049753</v>
+        <v>7049755</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6117,7 +6126,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6127,7 +6136,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6142,22 +6151,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123304172</v>
+        <v>123309182</v>
       </c>
       <c r="B50" t="n">
-        <v>98370</v>
+        <v>78771</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6166,47 +6175,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580186</v>
+        <v>580139</v>
       </c>
       <c r="R50" t="n">
-        <v>7049672</v>
+        <v>7049712</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6263,12 +6263,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -1826,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123305387</v>
+        <v>123304879</v>
       </c>
       <c r="B12" t="n">
-        <v>78771</v>
+        <v>98376</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,38 +1838,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580124</v>
+        <v>580143</v>
       </c>
       <c r="R12" t="n">
-        <v>7049764</v>
+        <v>7049655</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,22 +1930,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123307517</v>
+        <v>123305283</v>
       </c>
       <c r="B13" t="n">
-        <v>78771</v>
+        <v>98376</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,38 +1954,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580020</v>
+        <v>580160</v>
       </c>
       <c r="R13" t="n">
-        <v>7049752</v>
+        <v>7049663</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123304706</v>
+        <v>123304722</v>
       </c>
       <c r="B14" t="n">
-        <v>92238</v>
+        <v>78772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,25 +2070,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2090,10 +2098,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580179</v>
+        <v>580163</v>
       </c>
       <c r="R14" t="n">
-        <v>7049708</v>
+        <v>7049654</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2135,7 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,22 +2158,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123307914</v>
+        <v>123307053</v>
       </c>
       <c r="B15" t="n">
-        <v>79852</v>
+        <v>78772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,21 +2186,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2202,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580053</v>
+        <v>579979</v>
       </c>
       <c r="R15" t="n">
-        <v>7049758</v>
+        <v>7049720</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2247,7 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,7 +2282,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123308088</v>
+        <v>123303786</v>
       </c>
       <c r="B16" t="n">
         <v>57481</v>
@@ -2310,7 +2318,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2319,10 +2327,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580037</v>
+        <v>580193</v>
       </c>
       <c r="R16" t="n">
-        <v>7049732</v>
+        <v>7049674</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,7 +2362,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2364,7 +2372,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2396,10 +2404,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123306520</v>
+        <v>123306199</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,7 +2439,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2440,10 +2448,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580082</v>
+        <v>580119</v>
       </c>
       <c r="R17" t="n">
-        <v>7049717</v>
+        <v>7049689</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2483,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2493,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,10 +2520,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123304722</v>
+        <v>123308517</v>
       </c>
       <c r="B18" t="n">
-        <v>78771</v>
+        <v>90963</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,21 +2536,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2552,10 +2560,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580163</v>
+        <v>580100</v>
       </c>
       <c r="R18" t="n">
-        <v>7049654</v>
+        <v>7049758</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,7 +2595,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,7 +2605,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2624,10 +2632,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123307802</v>
+        <v>123306520</v>
       </c>
       <c r="B19" t="n">
-        <v>82558</v>
+        <v>98376</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2636,38 +2644,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580037</v>
+        <v>580082</v>
       </c>
       <c r="R19" t="n">
-        <v>7049768</v>
+        <v>7049717</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,7 +2721,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,10 +2748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123305088</v>
+        <v>123306079</v>
       </c>
       <c r="B20" t="n">
-        <v>90957</v>
+        <v>78772</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2752,21 +2764,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2776,10 +2788,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580164</v>
+        <v>580118</v>
       </c>
       <c r="R20" t="n">
-        <v>7049642</v>
+        <v>7049697</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2811,7 +2823,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2821,7 +2833,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123306079</v>
+        <v>123303895</v>
       </c>
       <c r="B21" t="n">
-        <v>78771</v>
+        <v>92244</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2860,25 +2872,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2888,10 +2900,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580118</v>
+        <v>580189</v>
       </c>
       <c r="R21" t="n">
-        <v>7049697</v>
+        <v>7049660</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2923,7 +2935,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2933,7 +2945,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2960,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123304342</v>
+        <v>123307659</v>
       </c>
       <c r="B22" t="n">
-        <v>92238</v>
+        <v>79853</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2972,25 +2984,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3000,10 +3012,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580158</v>
+        <v>580022</v>
       </c>
       <c r="R22" t="n">
-        <v>7049670</v>
+        <v>7049763</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3035,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3045,7 +3057,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3072,10 +3084,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123307810</v>
+        <v>123307914</v>
       </c>
       <c r="B23" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3088,21 +3100,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3112,10 +3124,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580037</v>
+        <v>580053</v>
       </c>
       <c r="R23" t="n">
-        <v>7049763</v>
+        <v>7049758</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3147,7 +3159,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3157,7 +3169,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3184,10 +3196,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123303786</v>
+        <v>123309023</v>
       </c>
       <c r="B24" t="n">
-        <v>57481</v>
+        <v>90963</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3200,39 +3212,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580193</v>
+        <v>580106</v>
       </c>
       <c r="R24" t="n">
-        <v>7049674</v>
+        <v>7049714</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3264,7 +3271,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3274,12 +3281,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3306,10 +3308,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123305011</v>
+        <v>123304342</v>
       </c>
       <c r="B25" t="n">
-        <v>90957</v>
+        <v>92244</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3318,25 +3320,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3346,10 +3348,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580151</v>
+        <v>580158</v>
       </c>
       <c r="R25" t="n">
-        <v>7049633</v>
+        <v>7049670</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3381,7 +3383,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3391,7 +3393,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3418,10 +3420,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123309023</v>
+        <v>123305088</v>
       </c>
       <c r="B26" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3458,10 +3460,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580106</v>
+        <v>580164</v>
       </c>
       <c r="R26" t="n">
-        <v>7049714</v>
+        <v>7049642</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3493,7 +3495,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3503,7 +3505,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3530,10 +3532,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123308246</v>
+        <v>123309182</v>
       </c>
       <c r="B27" t="n">
-        <v>98370</v>
+        <v>78772</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3542,42 +3544,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580053</v>
+        <v>580139</v>
       </c>
       <c r="R27" t="n">
-        <v>7049735</v>
+        <v>7049712</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3609,7 +3607,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3619,7 +3617,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3646,10 +3644,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123306981</v>
+        <v>123307604</v>
       </c>
       <c r="B28" t="n">
-        <v>78771</v>
+        <v>82559</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3662,21 +3660,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3686,10 +3684,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580007</v>
+        <v>580021</v>
       </c>
       <c r="R28" t="n">
-        <v>7049703</v>
+        <v>7049755</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3721,7 +3719,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3731,7 +3729,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3758,10 +3756,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123306062</v>
+        <v>123306694</v>
       </c>
       <c r="B29" t="n">
-        <v>92238</v>
+        <v>98376</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3770,38 +3768,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580126</v>
+        <v>580043</v>
       </c>
       <c r="R29" t="n">
-        <v>7049722</v>
+        <v>7049753</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3833,7 +3835,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3843,7 +3845,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3870,10 +3872,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123307053</v>
+        <v>123307482</v>
       </c>
       <c r="B30" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3910,10 +3912,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>579979</v>
+        <v>579986</v>
       </c>
       <c r="R30" t="n">
-        <v>7049720</v>
+        <v>7049735</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3945,7 +3947,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3955,7 +3957,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3982,10 +3984,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123306849</v>
+        <v>123304880</v>
       </c>
       <c r="B31" t="n">
-        <v>78771</v>
+        <v>98376</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3994,38 +3996,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580039</v>
+        <v>580159</v>
       </c>
       <c r="R31" t="n">
-        <v>7049688</v>
+        <v>7049755</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4057,7 +4068,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4067,7 +4078,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4082,22 +4093,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123307035</v>
+        <v>123308246</v>
       </c>
       <c r="B32" t="n">
-        <v>57497</v>
+        <v>98376</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4106,31 +4117,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4139,10 +4149,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>579970</v>
+        <v>580053</v>
       </c>
       <c r="R32" t="n">
-        <v>7049717</v>
+        <v>7049735</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4174,7 +4184,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4184,7 +4194,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4211,10 +4221,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123306199</v>
+        <v>123306062</v>
       </c>
       <c r="B33" t="n">
-        <v>98370</v>
+        <v>92244</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4223,42 +4233,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580119</v>
+        <v>580126</v>
       </c>
       <c r="R33" t="n">
-        <v>7049689</v>
+        <v>7049722</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4290,7 +4296,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4300,7 +4306,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4315,22 +4321,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123307841</v>
+        <v>123309206</v>
       </c>
       <c r="B34" t="n">
-        <v>98370</v>
+        <v>78772</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4339,42 +4345,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580049</v>
+        <v>580174</v>
       </c>
       <c r="R34" t="n">
-        <v>7049765</v>
+        <v>7049673</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4406,7 +4408,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4416,7 +4418,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4443,10 +4445,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123308600</v>
+        <v>123304172</v>
       </c>
       <c r="B35" t="n">
-        <v>79852</v>
+        <v>98376</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4455,38 +4457,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580103</v>
+        <v>580186</v>
       </c>
       <c r="R35" t="n">
-        <v>7049748</v>
+        <v>7049672</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4518,7 +4529,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4528,7 +4539,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4543,22 +4554,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123307659</v>
+        <v>123307517</v>
       </c>
       <c r="B36" t="n">
-        <v>79852</v>
+        <v>78772</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4571,21 +4582,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4595,10 +4606,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580022</v>
+        <v>580020</v>
       </c>
       <c r="R36" t="n">
-        <v>7049763</v>
+        <v>7049752</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4630,7 +4641,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4640,7 +4651,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4667,10 +4678,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123304879</v>
+        <v>123305019</v>
       </c>
       <c r="B37" t="n">
-        <v>98370</v>
+        <v>57481</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4679,30 +4690,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4711,10 +4723,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580143</v>
+        <v>580166</v>
       </c>
       <c r="R37" t="n">
-        <v>7049655</v>
+        <v>7049779</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4746,7 +4758,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4756,7 +4768,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4771,22 +4788,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123308517</v>
+        <v>123307841</v>
       </c>
       <c r="B38" t="n">
-        <v>90957</v>
+        <v>98376</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4795,38 +4812,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580100</v>
+        <v>580049</v>
       </c>
       <c r="R38" t="n">
-        <v>7049758</v>
+        <v>7049765</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4858,7 +4879,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4868,7 +4889,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4895,10 +4916,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123306094</v>
+        <v>123307810</v>
       </c>
       <c r="B39" t="n">
-        <v>79852</v>
+        <v>78772</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4911,21 +4932,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4935,10 +4956,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580111</v>
+        <v>580037</v>
       </c>
       <c r="R39" t="n">
-        <v>7049724</v>
+        <v>7049763</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4970,7 +4991,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4980,7 +5001,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4995,22 +5016,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123304811</v>
+        <v>123305011</v>
       </c>
       <c r="B40" t="n">
-        <v>79852</v>
+        <v>90963</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5023,21 +5044,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5047,10 +5068,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580141</v>
+        <v>580151</v>
       </c>
       <c r="R40" t="n">
-        <v>7049654</v>
+        <v>7049633</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5082,7 +5103,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5092,7 +5113,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5119,10 +5140,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123309206</v>
+        <v>123308088</v>
       </c>
       <c r="B41" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5135,34 +5156,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580174</v>
+        <v>580037</v>
       </c>
       <c r="R41" t="n">
-        <v>7049673</v>
+        <v>7049732</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5194,7 +5220,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5204,7 +5230,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5231,10 +5262,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123304880</v>
+        <v>123308600</v>
       </c>
       <c r="B42" t="n">
-        <v>98370</v>
+        <v>79853</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5243,47 +5274,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580159</v>
+        <v>580103</v>
       </c>
       <c r="R42" t="n">
-        <v>7049755</v>
+        <v>7049748</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5315,7 +5337,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5325,7 +5347,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5340,22 +5362,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123307927</v>
+        <v>123303674</v>
       </c>
       <c r="B43" t="n">
-        <v>79852</v>
+        <v>78772</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5368,21 +5390,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5392,10 +5414,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580078</v>
+        <v>580206</v>
       </c>
       <c r="R43" t="n">
-        <v>7049752</v>
+        <v>7049658</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5427,7 +5449,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5437,7 +5459,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5464,10 +5486,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123307482</v>
+        <v>123307927</v>
       </c>
       <c r="B44" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5480,21 +5502,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5504,10 +5526,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>579986</v>
+        <v>580078</v>
       </c>
       <c r="R44" t="n">
-        <v>7049735</v>
+        <v>7049752</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5539,7 +5561,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5549,7 +5571,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5576,10 +5598,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123305283</v>
+        <v>123305387</v>
       </c>
       <c r="B45" t="n">
-        <v>98370</v>
+        <v>78772</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5588,42 +5610,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580160</v>
+        <v>580124</v>
       </c>
       <c r="R45" t="n">
-        <v>7049663</v>
+        <v>7049764</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5655,7 +5673,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5665,7 +5683,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5680,22 +5698,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123305019</v>
+        <v>123307802</v>
       </c>
       <c r="B46" t="n">
-        <v>57481</v>
+        <v>82559</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5708,39 +5726,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580166</v>
+        <v>580037</v>
       </c>
       <c r="R46" t="n">
-        <v>7049779</v>
+        <v>7049768</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5772,7 +5785,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5782,12 +5795,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5802,22 +5810,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123306694</v>
+        <v>123306981</v>
       </c>
       <c r="B47" t="n">
-        <v>98370</v>
+        <v>78772</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5826,42 +5834,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580043</v>
+        <v>580007</v>
       </c>
       <c r="R47" t="n">
-        <v>7049753</v>
+        <v>7049703</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5893,7 +5897,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5903,7 +5907,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5918,22 +5922,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123304172</v>
+        <v>123307035</v>
       </c>
       <c r="B48" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5942,35 +5946,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580186</v>
+        <v>579970</v>
       </c>
       <c r="R48" t="n">
-        <v>7049672</v>
+        <v>7049717</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6039,22 +6039,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123307604</v>
+        <v>123304706</v>
       </c>
       <c r="B49" t="n">
-        <v>82558</v>
+        <v>92244</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6063,25 +6063,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580021</v>
+        <v>580179</v>
       </c>
       <c r="R49" t="n">
-        <v>7049755</v>
+        <v>7049708</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6126,7 +6126,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6151,22 +6151,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123309182</v>
+        <v>123306094</v>
       </c>
       <c r="B50" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6179,21 +6179,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6203,10 +6203,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580139</v>
+        <v>580111</v>
       </c>
       <c r="R50" t="n">
-        <v>7049712</v>
+        <v>7049724</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6263,22 +6263,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123303895</v>
+        <v>123304811</v>
       </c>
       <c r="B51" t="n">
-        <v>92238</v>
+        <v>79853</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6287,25 +6287,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580189</v>
+        <v>580141</v>
       </c>
       <c r="R51" t="n">
-        <v>7049660</v>
+        <v>7049654</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6387,10 +6387,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123303674</v>
+        <v>123306849</v>
       </c>
       <c r="B52" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580206</v>
+        <v>580039</v>
       </c>
       <c r="R52" t="n">
-        <v>7049658</v>
+        <v>7049688</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -3980,10 +3980,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123305019</v>
+        <v>123306694</v>
       </c>
       <c r="B31" t="n">
-        <v>57481</v>
+        <v>98379</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3992,31 +3992,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4025,10 +4024,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580166</v>
+        <v>580043</v>
       </c>
       <c r="R31" t="n">
-        <v>7049779</v>
+        <v>7049753</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4060,7 +4059,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4070,12 +4069,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4102,10 +4096,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123306694</v>
+        <v>123305019</v>
       </c>
       <c r="B32" t="n">
-        <v>98379</v>
+        <v>57481</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4114,30 +4108,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4146,10 +4141,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580043</v>
+        <v>580166</v>
       </c>
       <c r="R32" t="n">
-        <v>7049753</v>
+        <v>7049779</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4181,7 +4176,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4191,7 +4186,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4330,10 +4330,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123307914</v>
+        <v>123304880</v>
       </c>
       <c r="B34" t="n">
-        <v>79856</v>
+        <v>98379</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4342,38 +4342,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580053</v>
+        <v>580159</v>
       </c>
       <c r="R34" t="n">
-        <v>7049758</v>
+        <v>7049755</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4405,7 +4414,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4415,7 +4424,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4430,22 +4439,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123304880</v>
+        <v>123307914</v>
       </c>
       <c r="B35" t="n">
-        <v>98379</v>
+        <v>79856</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4454,47 +4463,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580159</v>
+        <v>580053</v>
       </c>
       <c r="R35" t="n">
-        <v>7049755</v>
+        <v>7049758</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4551,12 +4551,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -1826,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123307810</v>
+        <v>123307927</v>
       </c>
       <c r="B12" t="n">
-        <v>78775</v>
+        <v>79862</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,21 +1842,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580037</v>
+        <v>580078</v>
       </c>
       <c r="R12" t="n">
-        <v>7049763</v>
+        <v>7049752</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123307517</v>
+        <v>123305019</v>
       </c>
       <c r="B13" t="n">
-        <v>78775</v>
+        <v>57487</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,34 +1954,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580020</v>
+        <v>580166</v>
       </c>
       <c r="R13" t="n">
-        <v>7049752</v>
+        <v>7049779</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2028,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,22 +2048,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123305387</v>
+        <v>123307659</v>
       </c>
       <c r="B14" t="n">
-        <v>78775</v>
+        <v>79862</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,21 +2076,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2090,10 +2100,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580124</v>
+        <v>580022</v>
       </c>
       <c r="R14" t="n">
-        <v>7049764</v>
+        <v>7049763</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,7 +2135,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2135,7 +2145,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,22 +2160,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123307053</v>
+        <v>123306079</v>
       </c>
       <c r="B15" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2202,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579979</v>
+        <v>580118</v>
       </c>
       <c r="R15" t="n">
-        <v>7049720</v>
+        <v>7049697</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,7 +2247,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2247,7 +2257,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,10 +2284,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123308517</v>
+        <v>123304342</v>
       </c>
       <c r="B16" t="n">
-        <v>90966</v>
+        <v>92264</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,25 +2296,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2314,10 +2324,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580100</v>
+        <v>580158</v>
       </c>
       <c r="R16" t="n">
-        <v>7049758</v>
+        <v>7049670</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2349,7 +2359,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2369,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,10 +2396,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123307841</v>
+        <v>123303674</v>
       </c>
       <c r="B17" t="n">
-        <v>98379</v>
+        <v>78781</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2398,42 +2408,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580049</v>
+        <v>580206</v>
       </c>
       <c r="R17" t="n">
-        <v>7049765</v>
+        <v>7049658</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,7 +2471,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2475,7 +2481,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2502,10 +2508,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123306199</v>
+        <v>123303786</v>
       </c>
       <c r="B18" t="n">
-        <v>98379</v>
+        <v>57487</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,30 +2520,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2546,10 +2553,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580119</v>
+        <v>580193</v>
       </c>
       <c r="R18" t="n">
-        <v>7049689</v>
+        <v>7049674</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,7 +2588,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2598,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123309206</v>
+        <v>123307841</v>
       </c>
       <c r="B19" t="n">
-        <v>78775</v>
+        <v>98396</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,38 +2642,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580174</v>
+        <v>580049</v>
       </c>
       <c r="R19" t="n">
-        <v>7049673</v>
+        <v>7049765</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2693,7 +2709,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2703,7 +2719,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,10 +2746,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123308088</v>
+        <v>123309206</v>
       </c>
       <c r="B20" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2746,39 +2762,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580037</v>
+        <v>580174</v>
       </c>
       <c r="R20" t="n">
-        <v>7049732</v>
+        <v>7049673</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2810,7 +2821,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2820,12 +2831,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,10 +2858,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123308600</v>
+        <v>123304880</v>
       </c>
       <c r="B21" t="n">
-        <v>79856</v>
+        <v>98396</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2864,38 +2870,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580103</v>
+        <v>580159</v>
       </c>
       <c r="R21" t="n">
-        <v>7049748</v>
+        <v>7049755</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2927,7 +2942,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2937,7 +2952,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2952,22 +2967,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123309182</v>
+        <v>123308517</v>
       </c>
       <c r="B22" t="n">
-        <v>78775</v>
+        <v>90983</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2980,21 +2995,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3004,10 +3019,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580139</v>
+        <v>580100</v>
       </c>
       <c r="R22" t="n">
-        <v>7049712</v>
+        <v>7049758</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3039,7 +3054,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3049,7 +3064,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3076,10 +3091,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123304342</v>
+        <v>123307914</v>
       </c>
       <c r="B23" t="n">
-        <v>92247</v>
+        <v>79862</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3088,25 +3103,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3116,10 +3131,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580158</v>
+        <v>580053</v>
       </c>
       <c r="R23" t="n">
-        <v>7049670</v>
+        <v>7049758</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3151,7 +3166,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3161,7 +3176,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3188,10 +3203,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123306079</v>
+        <v>123304879</v>
       </c>
       <c r="B24" t="n">
-        <v>78775</v>
+        <v>98396</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3200,38 +3215,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580118</v>
+        <v>580143</v>
       </c>
       <c r="R24" t="n">
-        <v>7049697</v>
+        <v>7049655</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3263,7 +3282,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3273,7 +3292,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3300,10 +3319,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123304879</v>
+        <v>123305387</v>
       </c>
       <c r="B25" t="n">
-        <v>98379</v>
+        <v>78781</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3312,42 +3331,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580143</v>
+        <v>580124</v>
       </c>
       <c r="R25" t="n">
-        <v>7049655</v>
+        <v>7049764</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3379,7 +3394,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3389,7 +3404,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3404,22 +3419,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123307927</v>
+        <v>123304722</v>
       </c>
       <c r="B26" t="n">
-        <v>79856</v>
+        <v>78781</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3432,21 +3447,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3456,10 +3471,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580078</v>
+        <v>580163</v>
       </c>
       <c r="R26" t="n">
-        <v>7049752</v>
+        <v>7049654</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3491,7 +3506,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3501,7 +3516,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3528,10 +3543,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123303674</v>
+        <v>123308600</v>
       </c>
       <c r="B27" t="n">
-        <v>78775</v>
+        <v>79862</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3544,21 +3559,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3568,10 +3583,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580206</v>
+        <v>580103</v>
       </c>
       <c r="R27" t="n">
-        <v>7049658</v>
+        <v>7049748</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3603,7 +3618,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3613,7 +3628,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3640,10 +3655,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123304706</v>
+        <v>123306094</v>
       </c>
       <c r="B28" t="n">
-        <v>92247</v>
+        <v>79862</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3652,25 +3667,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3680,10 +3695,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580179</v>
+        <v>580111</v>
       </c>
       <c r="R28" t="n">
-        <v>7049708</v>
+        <v>7049724</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3715,7 +3730,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3725,7 +3740,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3752,10 +3767,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123306520</v>
+        <v>123307604</v>
       </c>
       <c r="B29" t="n">
-        <v>98379</v>
+        <v>82568</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3764,42 +3779,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580082</v>
+        <v>580021</v>
       </c>
       <c r="R29" t="n">
-        <v>7049717</v>
+        <v>7049755</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3831,7 +3842,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3841,7 +3852,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3868,10 +3879,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123306094</v>
+        <v>123308246</v>
       </c>
       <c r="B30" t="n">
-        <v>79856</v>
+        <v>98396</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3880,38 +3891,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580111</v>
+        <v>580053</v>
       </c>
       <c r="R30" t="n">
-        <v>7049724</v>
+        <v>7049735</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3943,7 +3958,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3953,7 +3968,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3968,22 +3983,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123306694</v>
+        <v>123304172</v>
       </c>
       <c r="B31" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4015,7 +4030,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4024,10 +4044,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580043</v>
+        <v>580186</v>
       </c>
       <c r="R31" t="n">
-        <v>7049753</v>
+        <v>7049672</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4059,7 +4079,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4069,7 +4089,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4096,10 +4116,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123305019</v>
+        <v>123306694</v>
       </c>
       <c r="B32" t="n">
-        <v>57481</v>
+        <v>98396</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4108,31 +4128,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4141,10 +4160,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580166</v>
+        <v>580043</v>
       </c>
       <c r="R32" t="n">
-        <v>7049779</v>
+        <v>7049753</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4176,7 +4195,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4186,12 +4205,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4218,10 +4232,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123307604</v>
+        <v>123307053</v>
       </c>
       <c r="B33" t="n">
-        <v>82562</v>
+        <v>78781</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4234,21 +4248,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4258,10 +4272,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580021</v>
+        <v>579979</v>
       </c>
       <c r="R33" t="n">
-        <v>7049755</v>
+        <v>7049720</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4293,7 +4307,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4303,7 +4317,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4330,10 +4344,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123304880</v>
+        <v>123307482</v>
       </c>
       <c r="B34" t="n">
-        <v>98379</v>
+        <v>78781</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4342,47 +4356,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580159</v>
+        <v>579986</v>
       </c>
       <c r="R34" t="n">
-        <v>7049755</v>
+        <v>7049735</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4414,7 +4419,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4424,7 +4429,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4439,22 +4444,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123307914</v>
+        <v>123306849</v>
       </c>
       <c r="B35" t="n">
-        <v>79856</v>
+        <v>78781</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4467,21 +4472,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4491,10 +4496,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580053</v>
+        <v>580039</v>
       </c>
       <c r="R35" t="n">
-        <v>7049758</v>
+        <v>7049688</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4526,7 +4531,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4536,7 +4541,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4563,10 +4568,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123303895</v>
+        <v>123306520</v>
       </c>
       <c r="B36" t="n">
-        <v>92247</v>
+        <v>98396</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4575,38 +4580,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580189</v>
+        <v>580082</v>
       </c>
       <c r="R36" t="n">
-        <v>7049660</v>
+        <v>7049717</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4638,7 +4647,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4648,7 +4657,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4675,10 +4684,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123304172</v>
+        <v>123309182</v>
       </c>
       <c r="B37" t="n">
-        <v>98379</v>
+        <v>78781</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4687,47 +4696,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580186</v>
+        <v>580139</v>
       </c>
       <c r="R37" t="n">
-        <v>7049672</v>
+        <v>7049712</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4784,22 +4784,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123308246</v>
+        <v>123308088</v>
       </c>
       <c r="B38" t="n">
-        <v>98379</v>
+        <v>57487</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4808,30 +4808,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4840,10 +4841,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580053</v>
+        <v>580037</v>
       </c>
       <c r="R38" t="n">
-        <v>7049735</v>
+        <v>7049732</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4875,7 +4876,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4885,7 +4886,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4912,10 +4918,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123309023</v>
+        <v>123305283</v>
       </c>
       <c r="B39" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4924,38 +4930,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580106</v>
+        <v>580160</v>
       </c>
       <c r="R39" t="n">
-        <v>7049714</v>
+        <v>7049663</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4987,7 +4997,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4997,7 +5007,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5024,10 +5034,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123303786</v>
+        <v>123306062</v>
       </c>
       <c r="B40" t="n">
-        <v>57481</v>
+        <v>92264</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5036,43 +5046,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580193</v>
+        <v>580126</v>
       </c>
       <c r="R40" t="n">
-        <v>7049674</v>
+        <v>7049722</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5104,7 +5109,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5114,12 +5119,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5134,22 +5134,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123304811</v>
+        <v>123307810</v>
       </c>
       <c r="B41" t="n">
-        <v>79856</v>
+        <v>78781</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5162,21 +5162,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5186,10 +5186,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580141</v>
+        <v>580037</v>
       </c>
       <c r="R41" t="n">
-        <v>7049654</v>
+        <v>7049763</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5258,10 +5258,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123307802</v>
+        <v>123307517</v>
       </c>
       <c r="B42" t="n">
-        <v>82562</v>
+        <v>78781</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5274,21 +5274,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5298,10 +5298,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580037</v>
+        <v>580020</v>
       </c>
       <c r="R42" t="n">
-        <v>7049768</v>
+        <v>7049752</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5370,10 +5370,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123305011</v>
+        <v>123309023</v>
       </c>
       <c r="B43" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5410,10 +5410,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580151</v>
+        <v>580106</v>
       </c>
       <c r="R43" t="n">
-        <v>7049633</v>
+        <v>7049714</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5482,10 +5482,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123307659</v>
+        <v>123304811</v>
       </c>
       <c r="B44" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5522,10 +5522,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580022</v>
+        <v>580141</v>
       </c>
       <c r="R44" t="n">
-        <v>7049763</v>
+        <v>7049654</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5594,10 +5594,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123306849</v>
+        <v>123304706</v>
       </c>
       <c r="B45" t="n">
-        <v>78775</v>
+        <v>92264</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5606,25 +5606,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5634,10 +5634,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580039</v>
+        <v>580179</v>
       </c>
       <c r="R45" t="n">
-        <v>7049688</v>
+        <v>7049708</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5694,22 +5694,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123306981</v>
+        <v>123303895</v>
       </c>
       <c r="B46" t="n">
-        <v>78775</v>
+        <v>92264</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5718,25 +5718,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5746,10 +5746,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580007</v>
+        <v>580189</v>
       </c>
       <c r="R46" t="n">
-        <v>7049703</v>
+        <v>7049660</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5818,10 +5818,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123305283</v>
+        <v>123307802</v>
       </c>
       <c r="B47" t="n">
-        <v>98379</v>
+        <v>82568</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5830,42 +5830,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580160</v>
+        <v>580037</v>
       </c>
       <c r="R47" t="n">
-        <v>7049663</v>
+        <v>7049768</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5897,7 +5893,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5907,7 +5903,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5934,10 +5930,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123305088</v>
+        <v>123306199</v>
       </c>
       <c r="B48" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5946,38 +5942,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580164</v>
+        <v>580119</v>
       </c>
       <c r="R48" t="n">
-        <v>7049642</v>
+        <v>7049689</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6046,10 +6046,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123307035</v>
+        <v>123305088</v>
       </c>
       <c r="B49" t="n">
-        <v>57497</v>
+        <v>90983</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6062,39 +6062,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>579970</v>
+        <v>580164</v>
       </c>
       <c r="R49" t="n">
-        <v>7049717</v>
+        <v>7049642</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6126,7 +6121,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6136,7 +6131,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6163,10 +6158,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123306062</v>
+        <v>123305011</v>
       </c>
       <c r="B50" t="n">
-        <v>92247</v>
+        <v>90983</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6175,25 +6170,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6203,10 +6198,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580126</v>
+        <v>580151</v>
       </c>
       <c r="R50" t="n">
-        <v>7049722</v>
+        <v>7049633</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6238,7 +6233,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6248,7 +6243,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6263,22 +6258,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123304722</v>
+        <v>123307035</v>
       </c>
       <c r="B51" t="n">
-        <v>78775</v>
+        <v>57503</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6291,34 +6286,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580163</v>
+        <v>579970</v>
       </c>
       <c r="R51" t="n">
-        <v>7049654</v>
+        <v>7049717</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6387,10 +6387,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123307482</v>
+        <v>123306981</v>
       </c>
       <c r="B52" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>579986</v>
+        <v>580007</v>
       </c>
       <c r="R52" t="n">
-        <v>7049735</v>
+        <v>7049703</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -2979,10 +2979,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123308517</v>
+        <v>123305387</v>
       </c>
       <c r="B22" t="n">
-        <v>90983</v>
+        <v>78781</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2995,21 +2995,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580100</v>
+        <v>580124</v>
       </c>
       <c r="R22" t="n">
-        <v>7049758</v>
+        <v>7049764</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3079,22 +3079,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123307914</v>
+        <v>123308517</v>
       </c>
       <c r="B23" t="n">
-        <v>79862</v>
+        <v>90983</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3107,21 +3107,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580053</v>
+        <v>580100</v>
       </c>
       <c r="R23" t="n">
         <v>7049758</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3203,10 +3203,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123304879</v>
+        <v>123307914</v>
       </c>
       <c r="B24" t="n">
-        <v>98396</v>
+        <v>79862</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3215,42 +3215,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580143</v>
+        <v>580053</v>
       </c>
       <c r="R24" t="n">
-        <v>7049655</v>
+        <v>7049758</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3282,7 +3278,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3292,7 +3288,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3319,10 +3315,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123305387</v>
+        <v>123304879</v>
       </c>
       <c r="B25" t="n">
-        <v>78781</v>
+        <v>98396</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3331,38 +3327,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580124</v>
+        <v>580143</v>
       </c>
       <c r="R25" t="n">
-        <v>7049764</v>
+        <v>7049655</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3419,12 +3419,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -6046,10 +6046,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123305088</v>
+        <v>123307035</v>
       </c>
       <c r="B49" t="n">
-        <v>90983</v>
+        <v>57503</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6062,34 +6062,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580164</v>
+        <v>579970</v>
       </c>
       <c r="R49" t="n">
-        <v>7049642</v>
+        <v>7049717</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6121,7 +6126,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6131,7 +6136,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6158,7 +6163,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123305011</v>
+        <v>123305088</v>
       </c>
       <c r="B50" t="n">
         <v>90983</v>
@@ -6198,10 +6203,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580151</v>
+        <v>580164</v>
       </c>
       <c r="R50" t="n">
-        <v>7049633</v>
+        <v>7049642</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6233,7 +6238,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6243,7 +6248,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6270,10 +6275,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123307035</v>
+        <v>123305011</v>
       </c>
       <c r="B51" t="n">
-        <v>57503</v>
+        <v>90983</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6286,39 +6291,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>579970</v>
+        <v>580151</v>
       </c>
       <c r="R51" t="n">
-        <v>7049717</v>
+        <v>7049633</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -2630,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123307841</v>
+        <v>123309206</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
+        <v>78781</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2642,42 +2642,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580049</v>
+        <v>580174</v>
       </c>
       <c r="R19" t="n">
-        <v>7049765</v>
+        <v>7049673</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,7 +2705,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2719,7 +2715,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2746,10 +2742,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123309206</v>
+        <v>123307841</v>
       </c>
       <c r="B20" t="n">
-        <v>78781</v>
+        <v>98396</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2758,38 +2754,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580174</v>
+        <v>580049</v>
       </c>
       <c r="R20" t="n">
-        <v>7049673</v>
+        <v>7049765</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -6046,10 +6046,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123307035</v>
+        <v>123305088</v>
       </c>
       <c r="B49" t="n">
-        <v>57503</v>
+        <v>90983</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6062,39 +6062,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>579970</v>
+        <v>580164</v>
       </c>
       <c r="R49" t="n">
-        <v>7049717</v>
+        <v>7049642</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6126,7 +6121,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6136,7 +6131,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6163,7 +6158,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123305088</v>
+        <v>123305011</v>
       </c>
       <c r="B50" t="n">
         <v>90983</v>
@@ -6203,10 +6198,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580164</v>
+        <v>580151</v>
       </c>
       <c r="R50" t="n">
-        <v>7049642</v>
+        <v>7049633</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6238,7 +6233,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6248,7 +6243,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6275,10 +6270,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123305011</v>
+        <v>123307035</v>
       </c>
       <c r="B51" t="n">
-        <v>90983</v>
+        <v>57503</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6291,34 +6286,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580151</v>
+        <v>579970</v>
       </c>
       <c r="R51" t="n">
-        <v>7049633</v>
+        <v>7049717</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -2630,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123309206</v>
+        <v>123307841</v>
       </c>
       <c r="B19" t="n">
-        <v>78781</v>
+        <v>98396</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2642,38 +2642,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580174</v>
+        <v>580049</v>
       </c>
       <c r="R19" t="n">
-        <v>7049673</v>
+        <v>7049765</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,7 +2709,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2715,7 +2719,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2742,10 +2746,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123307841</v>
+        <v>123309206</v>
       </c>
       <c r="B20" t="n">
-        <v>98396</v>
+        <v>78781</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2754,42 +2758,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580049</v>
+        <v>580174</v>
       </c>
       <c r="R20" t="n">
-        <v>7049765</v>
+        <v>7049673</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2979,10 +2979,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123305387</v>
+        <v>123308517</v>
       </c>
       <c r="B22" t="n">
-        <v>78781</v>
+        <v>90983</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2995,21 +2995,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580124</v>
+        <v>580100</v>
       </c>
       <c r="R22" t="n">
-        <v>7049764</v>
+        <v>7049758</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3079,22 +3079,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123308517</v>
+        <v>123307914</v>
       </c>
       <c r="B23" t="n">
-        <v>90983</v>
+        <v>79862</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3107,21 +3107,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580100</v>
+        <v>580053</v>
       </c>
       <c r="R23" t="n">
         <v>7049758</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3203,10 +3203,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123307914</v>
+        <v>123304879</v>
       </c>
       <c r="B24" t="n">
-        <v>79862</v>
+        <v>98396</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3215,38 +3215,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580053</v>
+        <v>580143</v>
       </c>
       <c r="R24" t="n">
-        <v>7049758</v>
+        <v>7049655</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3278,7 +3282,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3288,7 +3292,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3315,10 +3319,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123304879</v>
+        <v>123305387</v>
       </c>
       <c r="B25" t="n">
-        <v>98396</v>
+        <v>78781</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3327,42 +3331,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580143</v>
+        <v>580124</v>
       </c>
       <c r="R25" t="n">
-        <v>7049655</v>
+        <v>7049764</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3419,12 +3419,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -1826,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123307927</v>
+        <v>123309023</v>
       </c>
       <c r="B12" t="n">
-        <v>79862</v>
+        <v>90988</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,21 +1842,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580078</v>
+        <v>580106</v>
       </c>
       <c r="R12" t="n">
-        <v>7049752</v>
+        <v>7049714</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123305019</v>
+        <v>123307810</v>
       </c>
       <c r="B13" t="n">
-        <v>57487</v>
+        <v>78786</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,39 +1954,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580166</v>
+        <v>580037</v>
       </c>
       <c r="R13" t="n">
-        <v>7049779</v>
+        <v>7049763</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,12 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,22 +2038,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123307659</v>
+        <v>123304879</v>
       </c>
       <c r="B14" t="n">
-        <v>79862</v>
+        <v>98502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2072,38 +2062,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580022</v>
+        <v>580143</v>
       </c>
       <c r="R14" t="n">
-        <v>7049763</v>
+        <v>7049655</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2145,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123306079</v>
+        <v>123307659</v>
       </c>
       <c r="B15" t="n">
-        <v>78781</v>
+        <v>79867</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,21 +2182,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2212,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580118</v>
+        <v>580022</v>
       </c>
       <c r="R15" t="n">
-        <v>7049697</v>
+        <v>7049763</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2247,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2257,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2284,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123304342</v>
+        <v>123303786</v>
       </c>
       <c r="B16" t="n">
-        <v>92264</v>
+        <v>57490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,38 +2290,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580158</v>
+        <v>580193</v>
       </c>
       <c r="R16" t="n">
-        <v>7049670</v>
+        <v>7049674</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2359,7 +2358,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2368,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123303674</v>
+        <v>123306079</v>
       </c>
       <c r="B17" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2436,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580206</v>
+        <v>580118</v>
       </c>
       <c r="R17" t="n">
-        <v>7049658</v>
+        <v>7049697</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123303786</v>
+        <v>123306981</v>
       </c>
       <c r="B18" t="n">
-        <v>57487</v>
+        <v>78786</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,39 +2528,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580193</v>
+        <v>580007</v>
       </c>
       <c r="R18" t="n">
-        <v>7049674</v>
+        <v>7049703</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2588,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2598,12 +2597,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2630,10 +2624,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123307841</v>
+        <v>123307053</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
+        <v>78786</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2642,42 +2636,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580049</v>
+        <v>579979</v>
       </c>
       <c r="R19" t="n">
-        <v>7049765</v>
+        <v>7049720</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2719,7 +2709,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2746,10 +2736,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123309206</v>
+        <v>123307841</v>
       </c>
       <c r="B20" t="n">
-        <v>78781</v>
+        <v>98502</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2758,38 +2748,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580174</v>
+        <v>580049</v>
       </c>
       <c r="R20" t="n">
-        <v>7049673</v>
+        <v>7049765</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2821,7 +2815,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2831,7 +2825,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2858,10 +2852,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123304880</v>
+        <v>123308088</v>
       </c>
       <c r="B21" t="n">
-        <v>98396</v>
+        <v>57490</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2870,35 +2864,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2907,10 +2897,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580159</v>
+        <v>580037</v>
       </c>
       <c r="R21" t="n">
-        <v>7049755</v>
+        <v>7049732</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2942,7 +2932,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2952,7 +2942,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2967,22 +2962,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123308517</v>
+        <v>123306849</v>
       </c>
       <c r="B22" t="n">
-        <v>90983</v>
+        <v>78786</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2995,21 +2990,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3019,10 +3014,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580100</v>
+        <v>580039</v>
       </c>
       <c r="R22" t="n">
-        <v>7049758</v>
+        <v>7049688</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,7 +3049,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3064,7 +3059,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3091,10 +3086,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123307914</v>
+        <v>123307802</v>
       </c>
       <c r="B23" t="n">
-        <v>79862</v>
+        <v>82573</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3107,21 +3102,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3131,10 +3126,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580053</v>
+        <v>580037</v>
       </c>
       <c r="R23" t="n">
-        <v>7049758</v>
+        <v>7049768</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3166,7 +3161,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3176,7 +3171,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3203,10 +3198,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123304879</v>
+        <v>123304811</v>
       </c>
       <c r="B24" t="n">
-        <v>98396</v>
+        <v>79867</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3215,42 +3210,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580143</v>
+        <v>580141</v>
       </c>
       <c r="R24" t="n">
-        <v>7049655</v>
+        <v>7049654</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3282,7 +3273,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3292,7 +3283,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3319,10 +3310,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123305387</v>
+        <v>123305283</v>
       </c>
       <c r="B25" t="n">
-        <v>78781</v>
+        <v>98502</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3331,38 +3322,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580124</v>
+        <v>580160</v>
       </c>
       <c r="R25" t="n">
-        <v>7049764</v>
+        <v>7049663</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3394,7 +3389,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3404,7 +3399,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3419,22 +3414,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123304722</v>
+        <v>123309182</v>
       </c>
       <c r="B26" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3471,10 +3466,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580163</v>
+        <v>580139</v>
       </c>
       <c r="R26" t="n">
-        <v>7049654</v>
+        <v>7049712</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3506,7 +3501,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3516,7 +3511,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3543,10 +3538,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123308600</v>
+        <v>123308517</v>
       </c>
       <c r="B27" t="n">
-        <v>79862</v>
+        <v>90988</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3559,21 +3554,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3583,10 +3578,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580103</v>
+        <v>580100</v>
       </c>
       <c r="R27" t="n">
-        <v>7049748</v>
+        <v>7049758</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3618,7 +3613,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3628,7 +3623,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3658,7 +3653,7 @@
         <v>123306094</v>
       </c>
       <c r="B28" t="n">
-        <v>79862</v>
+        <v>79867</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3767,10 +3762,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123307604</v>
+        <v>123305019</v>
       </c>
       <c r="B29" t="n">
-        <v>82568</v>
+        <v>57490</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3783,34 +3778,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580021</v>
+        <v>580166</v>
       </c>
       <c r="R29" t="n">
-        <v>7049755</v>
+        <v>7049779</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3852,7 +3852,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3867,22 +3872,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123308246</v>
+        <v>123304172</v>
       </c>
       <c r="B30" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3914,7 +3919,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3923,10 +3933,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580053</v>
+        <v>580186</v>
       </c>
       <c r="R30" t="n">
-        <v>7049735</v>
+        <v>7049672</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3958,7 +3968,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3968,7 +3978,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3983,22 +3993,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123304172</v>
+        <v>123306694</v>
       </c>
       <c r="B31" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4030,12 +4040,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4044,10 +4049,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580186</v>
+        <v>580043</v>
       </c>
       <c r="R31" t="n">
-        <v>7049672</v>
+        <v>7049753</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4079,7 +4084,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4089,7 +4094,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4116,10 +4121,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123306694</v>
+        <v>123305387</v>
       </c>
       <c r="B32" t="n">
-        <v>98396</v>
+        <v>78786</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4128,42 +4133,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580043</v>
+        <v>580124</v>
       </c>
       <c r="R32" t="n">
-        <v>7049753</v>
+        <v>7049764</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4195,7 +4196,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4205,7 +4206,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4232,10 +4233,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123307053</v>
+        <v>123307035</v>
       </c>
       <c r="B33" t="n">
-        <v>78781</v>
+        <v>57506</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4248,34 +4249,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>579979</v>
+        <v>579970</v>
       </c>
       <c r="R33" t="n">
-        <v>7049720</v>
+        <v>7049717</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4307,7 +4313,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4317,7 +4323,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4344,10 +4350,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123307482</v>
+        <v>123304706</v>
       </c>
       <c r="B34" t="n">
-        <v>78781</v>
+        <v>92269</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4356,25 +4362,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4384,10 +4390,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>579986</v>
+        <v>580179</v>
       </c>
       <c r="R34" t="n">
-        <v>7049735</v>
+        <v>7049708</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4419,7 +4425,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4429,7 +4435,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4444,22 +4450,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123306849</v>
+        <v>123307914</v>
       </c>
       <c r="B35" t="n">
-        <v>78781</v>
+        <v>79867</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4472,21 +4478,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4496,10 +4502,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580039</v>
+        <v>580053</v>
       </c>
       <c r="R35" t="n">
-        <v>7049688</v>
+        <v>7049758</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4531,7 +4537,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4541,7 +4547,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4568,10 +4574,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123306520</v>
+        <v>123303895</v>
       </c>
       <c r="B36" t="n">
-        <v>98396</v>
+        <v>92269</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4580,42 +4586,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580082</v>
+        <v>580189</v>
       </c>
       <c r="R36" t="n">
-        <v>7049717</v>
+        <v>7049660</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4647,7 +4649,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4657,7 +4659,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4684,10 +4686,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123309182</v>
+        <v>123304342</v>
       </c>
       <c r="B37" t="n">
-        <v>78781</v>
+        <v>92269</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4696,25 +4698,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4724,10 +4726,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580139</v>
+        <v>580158</v>
       </c>
       <c r="R37" t="n">
-        <v>7049712</v>
+        <v>7049670</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4759,7 +4761,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4769,7 +4771,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4796,10 +4798,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123308088</v>
+        <v>123306062</v>
       </c>
       <c r="B38" t="n">
-        <v>57487</v>
+        <v>92269</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4808,43 +4810,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580037</v>
+        <v>580126</v>
       </c>
       <c r="R38" t="n">
-        <v>7049732</v>
+        <v>7049722</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4876,7 +4873,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4886,12 +4883,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4906,22 +4898,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123305283</v>
+        <v>123304722</v>
       </c>
       <c r="B39" t="n">
-        <v>98396</v>
+        <v>78786</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4930,42 +4922,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580160</v>
+        <v>580163</v>
       </c>
       <c r="R39" t="n">
-        <v>7049663</v>
+        <v>7049654</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4997,7 +4985,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5007,7 +4995,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5034,10 +5022,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123306062</v>
+        <v>123305011</v>
       </c>
       <c r="B40" t="n">
-        <v>92264</v>
+        <v>90988</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5046,25 +5034,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5074,10 +5062,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580126</v>
+        <v>580151</v>
       </c>
       <c r="R40" t="n">
-        <v>7049722</v>
+        <v>7049633</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5109,7 +5097,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5119,7 +5107,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5134,22 +5122,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123307810</v>
+        <v>123305088</v>
       </c>
       <c r="B41" t="n">
-        <v>78781</v>
+        <v>90988</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5162,21 +5150,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5186,10 +5174,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580037</v>
+        <v>580164</v>
       </c>
       <c r="R41" t="n">
-        <v>7049763</v>
+        <v>7049642</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5221,7 +5209,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5231,7 +5219,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5258,10 +5246,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123307517</v>
+        <v>123307604</v>
       </c>
       <c r="B42" t="n">
-        <v>78781</v>
+        <v>82573</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5274,21 +5262,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5298,10 +5286,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580020</v>
+        <v>580021</v>
       </c>
       <c r="R42" t="n">
-        <v>7049752</v>
+        <v>7049755</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5333,7 +5321,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5343,7 +5331,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5370,10 +5358,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123309023</v>
+        <v>123304880</v>
       </c>
       <c r="B43" t="n">
-        <v>90983</v>
+        <v>98502</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5382,38 +5370,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580106</v>
+        <v>580159</v>
       </c>
       <c r="R43" t="n">
-        <v>7049714</v>
+        <v>7049755</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5445,7 +5442,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5455,7 +5452,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5470,22 +5467,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123304811</v>
+        <v>123306199</v>
       </c>
       <c r="B44" t="n">
-        <v>79862</v>
+        <v>98502</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5494,38 +5491,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580141</v>
+        <v>580119</v>
       </c>
       <c r="R44" t="n">
-        <v>7049654</v>
+        <v>7049689</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5557,7 +5558,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5567,7 +5568,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5594,10 +5595,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123304706</v>
+        <v>123307927</v>
       </c>
       <c r="B45" t="n">
-        <v>92264</v>
+        <v>79867</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5606,25 +5607,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5634,10 +5635,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580179</v>
+        <v>580078</v>
       </c>
       <c r="R45" t="n">
-        <v>7049708</v>
+        <v>7049752</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5669,7 +5670,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5679,7 +5680,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5694,22 +5695,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123303895</v>
+        <v>123307482</v>
       </c>
       <c r="B46" t="n">
-        <v>92264</v>
+        <v>78786</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5718,25 +5719,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5746,10 +5747,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580189</v>
+        <v>579986</v>
       </c>
       <c r="R46" t="n">
-        <v>7049660</v>
+        <v>7049735</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5781,7 +5782,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5791,7 +5792,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5818,10 +5819,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123307802</v>
+        <v>123306520</v>
       </c>
       <c r="B47" t="n">
-        <v>82568</v>
+        <v>98502</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5830,38 +5831,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580037</v>
+        <v>580082</v>
       </c>
       <c r="R47" t="n">
-        <v>7049768</v>
+        <v>7049717</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5893,7 +5898,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5903,7 +5908,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5930,10 +5935,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123306199</v>
+        <v>123303674</v>
       </c>
       <c r="B48" t="n">
-        <v>98396</v>
+        <v>78786</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5942,42 +5947,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580119</v>
+        <v>580206</v>
       </c>
       <c r="R48" t="n">
-        <v>7049689</v>
+        <v>7049658</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6009,7 +6010,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6019,7 +6020,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6046,10 +6047,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123305088</v>
+        <v>123308246</v>
       </c>
       <c r="B49" t="n">
-        <v>90983</v>
+        <v>98502</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6058,38 +6059,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580164</v>
+        <v>580053</v>
       </c>
       <c r="R49" t="n">
-        <v>7049642</v>
+        <v>7049735</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6121,7 +6126,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6131,7 +6136,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6158,10 +6163,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123305011</v>
+        <v>123307517</v>
       </c>
       <c r="B50" t="n">
-        <v>90983</v>
+        <v>78786</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6174,21 +6179,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6198,10 +6203,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580151</v>
+        <v>580020</v>
       </c>
       <c r="R50" t="n">
-        <v>7049633</v>
+        <v>7049752</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6233,7 +6238,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6243,7 +6248,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6270,10 +6275,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123307035</v>
+        <v>123309206</v>
       </c>
       <c r="B51" t="n">
-        <v>57503</v>
+        <v>78786</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6286,39 +6291,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>579970</v>
+        <v>580174</v>
       </c>
       <c r="R51" t="n">
-        <v>7049717</v>
+        <v>7049673</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6387,10 +6387,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123306981</v>
+        <v>123308600</v>
       </c>
       <c r="B52" t="n">
-        <v>78781</v>
+        <v>79867</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6403,21 +6403,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6427,10 +6427,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580007</v>
+        <v>580103</v>
       </c>
       <c r="R52" t="n">
-        <v>7049703</v>
+        <v>7049748</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -1826,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123309023</v>
+        <v>123306079</v>
       </c>
       <c r="B12" t="n">
-        <v>90988</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,21 +1842,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580106</v>
+        <v>580118</v>
       </c>
       <c r="R12" t="n">
-        <v>7049714</v>
+        <v>7049697</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123307810</v>
+        <v>123307927</v>
       </c>
       <c r="B13" t="n">
-        <v>78786</v>
+        <v>79869</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,21 +1954,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580037</v>
+        <v>580078</v>
       </c>
       <c r="R13" t="n">
-        <v>7049763</v>
+        <v>7049752</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123304879</v>
+        <v>123308088</v>
       </c>
       <c r="B14" t="n">
-        <v>98502</v>
+        <v>57491</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,30 +2062,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2094,10 +2095,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580143</v>
+        <v>580037</v>
       </c>
       <c r="R14" t="n">
-        <v>7049655</v>
+        <v>7049732</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2130,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2140,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123307659</v>
+        <v>123308600</v>
       </c>
       <c r="B15" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2206,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580022</v>
+        <v>580103</v>
       </c>
       <c r="R15" t="n">
-        <v>7049763</v>
+        <v>7049748</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2247,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2257,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,10 +2284,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123303786</v>
+        <v>123307914</v>
       </c>
       <c r="B16" t="n">
-        <v>57490</v>
+        <v>79869</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,39 +2300,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580193</v>
+        <v>580053</v>
       </c>
       <c r="R16" t="n">
-        <v>7049674</v>
+        <v>7049758</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2358,7 +2359,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2368,12 +2369,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,10 +2396,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123306079</v>
+        <v>123309182</v>
       </c>
       <c r="B17" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2440,10 +2436,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580118</v>
+        <v>580139</v>
       </c>
       <c r="R17" t="n">
-        <v>7049697</v>
+        <v>7049712</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2471,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2481,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,10 +2508,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123306981</v>
+        <v>123304342</v>
       </c>
       <c r="B18" t="n">
-        <v>78786</v>
+        <v>92271</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,25 +2520,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2552,10 +2548,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580007</v>
+        <v>580158</v>
       </c>
       <c r="R18" t="n">
-        <v>7049703</v>
+        <v>7049670</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,7 +2583,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,7 +2593,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2624,10 +2620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123307053</v>
+        <v>123303895</v>
       </c>
       <c r="B19" t="n">
-        <v>78786</v>
+        <v>92271</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2636,25 +2632,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2664,10 +2660,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579979</v>
+        <v>580189</v>
       </c>
       <c r="R19" t="n">
-        <v>7049720</v>
+        <v>7049660</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,7 +2695,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,7 +2705,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,10 +2732,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123307841</v>
+        <v>123307810</v>
       </c>
       <c r="B20" t="n">
-        <v>98502</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2748,42 +2744,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580049</v>
+        <v>580037</v>
       </c>
       <c r="R20" t="n">
-        <v>7049765</v>
+        <v>7049763</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,7 +2807,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2825,7 +2817,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,10 +2844,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123308088</v>
+        <v>123307802</v>
       </c>
       <c r="B21" t="n">
-        <v>57490</v>
+        <v>82575</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2868,29 +2860,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
@@ -2900,7 +2887,7 @@
         <v>580037</v>
       </c>
       <c r="R21" t="n">
-        <v>7049732</v>
+        <v>7049768</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2932,7 +2919,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2942,12 +2929,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,10 +2956,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123306849</v>
+        <v>123305283</v>
       </c>
       <c r="B22" t="n">
-        <v>78786</v>
+        <v>98504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2986,38 +2968,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580039</v>
+        <v>580160</v>
       </c>
       <c r="R22" t="n">
-        <v>7049688</v>
+        <v>7049663</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3049,7 +3035,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3059,7 +3045,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3086,10 +3072,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123307802</v>
+        <v>123303674</v>
       </c>
       <c r="B23" t="n">
-        <v>82573</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3102,21 +3088,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3126,10 +3112,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580037</v>
+        <v>580206</v>
       </c>
       <c r="R23" t="n">
-        <v>7049768</v>
+        <v>7049658</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3161,7 +3147,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3171,7 +3157,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3198,10 +3184,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123304811</v>
+        <v>123305088</v>
       </c>
       <c r="B24" t="n">
-        <v>79867</v>
+        <v>90990</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3214,21 +3200,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3238,10 +3224,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580141</v>
+        <v>580164</v>
       </c>
       <c r="R24" t="n">
-        <v>7049654</v>
+        <v>7049642</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3273,7 +3259,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3283,7 +3269,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,10 +3296,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123305283</v>
+        <v>123306199</v>
       </c>
       <c r="B25" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3345,7 +3331,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3354,10 +3340,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580160</v>
+        <v>580119</v>
       </c>
       <c r="R25" t="n">
-        <v>7049663</v>
+        <v>7049689</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3389,7 +3375,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3399,7 +3385,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3426,10 +3412,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123309182</v>
+        <v>123309023</v>
       </c>
       <c r="B26" t="n">
-        <v>78786</v>
+        <v>90990</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3442,21 +3428,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3466,10 +3452,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580139</v>
+        <v>580106</v>
       </c>
       <c r="R26" t="n">
-        <v>7049712</v>
+        <v>7049714</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3501,7 +3487,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3511,7 +3497,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3538,10 +3524,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123308517</v>
+        <v>123307659</v>
       </c>
       <c r="B27" t="n">
-        <v>90988</v>
+        <v>79869</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3554,21 +3540,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3578,10 +3564,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580100</v>
+        <v>580022</v>
       </c>
       <c r="R27" t="n">
-        <v>7049758</v>
+        <v>7049763</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3613,7 +3599,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3623,7 +3609,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3650,10 +3636,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123306094</v>
+        <v>123305011</v>
       </c>
       <c r="B28" t="n">
-        <v>79867</v>
+        <v>90990</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3666,21 +3652,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3690,10 +3676,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580111</v>
+        <v>580151</v>
       </c>
       <c r="R28" t="n">
-        <v>7049724</v>
+        <v>7049633</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3725,7 +3711,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3735,7 +3721,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3750,22 +3736,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123305019</v>
+        <v>123306981</v>
       </c>
       <c r="B29" t="n">
-        <v>57490</v>
+        <v>78788</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3778,39 +3764,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580166</v>
+        <v>580007</v>
       </c>
       <c r="R29" t="n">
-        <v>7049779</v>
+        <v>7049703</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3842,7 +3823,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3852,12 +3833,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3872,22 +3848,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123304172</v>
+        <v>123305387</v>
       </c>
       <c r="B30" t="n">
-        <v>98502</v>
+        <v>78788</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3896,47 +3872,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580186</v>
+        <v>580124</v>
       </c>
       <c r="R30" t="n">
-        <v>7049672</v>
+        <v>7049764</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3968,7 +3935,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3978,7 +3945,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4005,10 +3972,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123306694</v>
+        <v>123307053</v>
       </c>
       <c r="B31" t="n">
-        <v>98502</v>
+        <v>78788</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4017,42 +3984,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580043</v>
+        <v>579979</v>
       </c>
       <c r="R31" t="n">
-        <v>7049753</v>
+        <v>7049720</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4084,7 +4047,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4094,7 +4057,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4109,22 +4072,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123305387</v>
+        <v>123304722</v>
       </c>
       <c r="B32" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4161,10 +4124,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580124</v>
+        <v>580163</v>
       </c>
       <c r="R32" t="n">
-        <v>7049764</v>
+        <v>7049654</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4196,7 +4159,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4206,7 +4169,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4221,22 +4184,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123307035</v>
+        <v>123306094</v>
       </c>
       <c r="B33" t="n">
-        <v>57506</v>
+        <v>79869</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4249,39 +4212,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>579970</v>
+        <v>580111</v>
       </c>
       <c r="R33" t="n">
-        <v>7049717</v>
+        <v>7049724</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4313,7 +4271,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4323,7 +4281,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4338,22 +4296,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123304706</v>
+        <v>123304811</v>
       </c>
       <c r="B34" t="n">
-        <v>92269</v>
+        <v>79869</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4362,25 +4320,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4390,10 +4348,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580179</v>
+        <v>580141</v>
       </c>
       <c r="R34" t="n">
-        <v>7049708</v>
+        <v>7049654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4425,7 +4383,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4435,7 +4393,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4450,22 +4408,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123307914</v>
+        <v>123305019</v>
       </c>
       <c r="B35" t="n">
-        <v>79867</v>
+        <v>57491</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4478,34 +4436,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580053</v>
+        <v>580166</v>
       </c>
       <c r="R35" t="n">
-        <v>7049758</v>
+        <v>7049779</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4537,7 +4500,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4547,7 +4510,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4562,22 +4530,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123303895</v>
+        <v>123306062</v>
       </c>
       <c r="B36" t="n">
-        <v>92269</v>
+        <v>92271</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4614,10 +4582,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580189</v>
+        <v>580126</v>
       </c>
       <c r="R36" t="n">
-        <v>7049660</v>
+        <v>7049722</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4649,7 +4617,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4659,7 +4627,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4674,22 +4642,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123304342</v>
+        <v>123304706</v>
       </c>
       <c r="B37" t="n">
-        <v>92269</v>
+        <v>92271</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4726,10 +4694,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580158</v>
+        <v>580179</v>
       </c>
       <c r="R37" t="n">
-        <v>7049670</v>
+        <v>7049708</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4761,7 +4729,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4771,7 +4739,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4786,22 +4754,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123306062</v>
+        <v>123306849</v>
       </c>
       <c r="B38" t="n">
-        <v>92269</v>
+        <v>78788</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4810,25 +4778,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4838,10 +4806,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580126</v>
+        <v>580039</v>
       </c>
       <c r="R38" t="n">
-        <v>7049722</v>
+        <v>7049688</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4873,7 +4841,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4883,7 +4851,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4898,22 +4866,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123304722</v>
+        <v>123304880</v>
       </c>
       <c r="B39" t="n">
-        <v>78786</v>
+        <v>98504</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4922,38 +4890,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580163</v>
+        <v>580159</v>
       </c>
       <c r="R39" t="n">
-        <v>7049654</v>
+        <v>7049755</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4985,7 +4962,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4995,7 +4972,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5010,22 +4987,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123305011</v>
+        <v>123307604</v>
       </c>
       <c r="B40" t="n">
-        <v>90988</v>
+        <v>82575</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5038,21 +5015,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5062,10 +5039,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580151</v>
+        <v>580021</v>
       </c>
       <c r="R40" t="n">
-        <v>7049633</v>
+        <v>7049755</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5097,7 +5074,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5107,7 +5084,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5134,10 +5111,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123305088</v>
+        <v>123307035</v>
       </c>
       <c r="B41" t="n">
-        <v>90988</v>
+        <v>57507</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5150,34 +5127,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580164</v>
+        <v>579970</v>
       </c>
       <c r="R41" t="n">
-        <v>7049642</v>
+        <v>7049717</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5209,7 +5191,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5219,7 +5201,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5246,10 +5228,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123307604</v>
+        <v>123307841</v>
       </c>
       <c r="B42" t="n">
-        <v>82573</v>
+        <v>98504</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5258,38 +5240,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580021</v>
+        <v>580049</v>
       </c>
       <c r="R42" t="n">
-        <v>7049755</v>
+        <v>7049765</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5321,7 +5307,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5331,7 +5317,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5358,10 +5344,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123304880</v>
+        <v>123307517</v>
       </c>
       <c r="B43" t="n">
-        <v>98502</v>
+        <v>78788</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5370,47 +5356,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580159</v>
+        <v>580020</v>
       </c>
       <c r="R43" t="n">
-        <v>7049755</v>
+        <v>7049752</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5442,7 +5419,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5452,7 +5429,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5467,22 +5444,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123306199</v>
+        <v>123303786</v>
       </c>
       <c r="B44" t="n">
-        <v>98502</v>
+        <v>57491</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5491,30 +5468,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5523,10 +5501,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580119</v>
+        <v>580193</v>
       </c>
       <c r="R44" t="n">
-        <v>7049689</v>
+        <v>7049674</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5558,7 +5536,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5568,7 +5546,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5595,10 +5578,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123307927</v>
+        <v>123307482</v>
       </c>
       <c r="B45" t="n">
-        <v>79867</v>
+        <v>78788</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5611,21 +5594,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5635,10 +5618,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580078</v>
+        <v>579986</v>
       </c>
       <c r="R45" t="n">
-        <v>7049752</v>
+        <v>7049735</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5670,7 +5653,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5680,7 +5663,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5707,10 +5690,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123307482</v>
+        <v>123308246</v>
       </c>
       <c r="B46" t="n">
-        <v>78786</v>
+        <v>98504</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5719,35 +5702,39 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>579986</v>
+        <v>580053</v>
       </c>
       <c r="R46" t="n">
         <v>7049735</v>
@@ -5782,7 +5769,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5792,7 +5779,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5819,10 +5806,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123306520</v>
+        <v>123306694</v>
       </c>
       <c r="B47" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5854,7 +5841,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5863,10 +5850,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580082</v>
+        <v>580043</v>
       </c>
       <c r="R47" t="n">
-        <v>7049717</v>
+        <v>7049753</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5898,7 +5885,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5908,7 +5895,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5923,22 +5910,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123303674</v>
+        <v>123308517</v>
       </c>
       <c r="B48" t="n">
-        <v>78786</v>
+        <v>90990</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5951,21 +5938,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5975,10 +5962,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580206</v>
+        <v>580100</v>
       </c>
       <c r="R48" t="n">
-        <v>7049658</v>
+        <v>7049758</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6010,7 +5997,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6020,7 +6007,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6047,10 +6034,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123308246</v>
+        <v>123309206</v>
       </c>
       <c r="B49" t="n">
-        <v>98502</v>
+        <v>78788</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6059,42 +6046,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580053</v>
+        <v>580174</v>
       </c>
       <c r="R49" t="n">
-        <v>7049735</v>
+        <v>7049673</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6126,7 +6109,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6136,7 +6119,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6163,10 +6146,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123307517</v>
+        <v>123304879</v>
       </c>
       <c r="B50" t="n">
-        <v>78786</v>
+        <v>98504</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6175,38 +6158,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580020</v>
+        <v>580143</v>
       </c>
       <c r="R50" t="n">
-        <v>7049752</v>
+        <v>7049655</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6238,7 +6225,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6248,7 +6235,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6275,10 +6262,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123309206</v>
+        <v>123304172</v>
       </c>
       <c r="B51" t="n">
-        <v>78786</v>
+        <v>98504</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6287,38 +6274,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580174</v>
+        <v>580186</v>
       </c>
       <c r="R51" t="n">
-        <v>7049673</v>
+        <v>7049672</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6350,7 +6346,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6360,7 +6356,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6375,22 +6371,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123308600</v>
+        <v>123306520</v>
       </c>
       <c r="B52" t="n">
-        <v>79867</v>
+        <v>98504</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6399,38 +6395,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580103</v>
+        <v>580082</v>
       </c>
       <c r="R52" t="n">
-        <v>7049748</v>
+        <v>7049717</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -2050,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123308088</v>
+        <v>123308600</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,39 +2066,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580037</v>
+        <v>580103</v>
       </c>
       <c r="R14" t="n">
-        <v>7049732</v>
+        <v>7049748</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,7 +2125,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2140,12 +2135,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123308600</v>
+        <v>123308088</v>
       </c>
       <c r="B15" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,34 +2178,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580103</v>
+        <v>580037</v>
       </c>
       <c r="R15" t="n">
-        <v>7049748</v>
+        <v>7049732</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2247,7 +2242,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2257,7 +2252,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -4084,10 +4084,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123304722</v>
+        <v>123304811</v>
       </c>
       <c r="B32" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4100,21 +4100,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580163</v>
+        <v>580141</v>
       </c>
       <c r="R32" t="n">
         <v>7049654</v>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4196,10 +4196,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123306094</v>
+        <v>123304722</v>
       </c>
       <c r="B33" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4212,21 +4212,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580111</v>
+        <v>580163</v>
       </c>
       <c r="R33" t="n">
-        <v>7049724</v>
+        <v>7049654</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4296,19 +4296,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123304811</v>
+        <v>123306094</v>
       </c>
       <c r="B34" t="n">
         <v>79869</v>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580141</v>
+        <v>580111</v>
       </c>
       <c r="R34" t="n">
-        <v>7049654</v>
+        <v>7049724</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4408,22 +4408,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123305019</v>
+        <v>123306062</v>
       </c>
       <c r="B35" t="n">
-        <v>57491</v>
+        <v>92271</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4432,43 +4432,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580166</v>
+        <v>580126</v>
       </c>
       <c r="R35" t="n">
-        <v>7049779</v>
+        <v>7049722</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4500,7 +4495,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4510,12 +4505,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4542,7 +4532,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123306062</v>
+        <v>123304706</v>
       </c>
       <c r="B36" t="n">
         <v>92271</v>
@@ -4582,10 +4572,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580126</v>
+        <v>580179</v>
       </c>
       <c r="R36" t="n">
-        <v>7049722</v>
+        <v>7049708</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4617,7 +4607,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4627,7 +4617,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4654,10 +4644,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123304706</v>
+        <v>123306849</v>
       </c>
       <c r="B37" t="n">
-        <v>92271</v>
+        <v>78788</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4666,25 +4656,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4694,10 +4684,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580179</v>
+        <v>580039</v>
       </c>
       <c r="R37" t="n">
-        <v>7049708</v>
+        <v>7049688</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4729,7 +4719,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4739,7 +4729,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4754,22 +4744,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123306849</v>
+        <v>123305019</v>
       </c>
       <c r="B38" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4782,34 +4772,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580039</v>
+        <v>580166</v>
       </c>
       <c r="R38" t="n">
-        <v>7049688</v>
+        <v>7049779</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4841,7 +4836,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4851,7 +4846,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4866,12 +4866,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -6034,10 +6034,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123309206</v>
+        <v>123304879</v>
       </c>
       <c r="B49" t="n">
-        <v>78788</v>
+        <v>98504</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6046,38 +6046,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580174</v>
+        <v>580143</v>
       </c>
       <c r="R49" t="n">
-        <v>7049673</v>
+        <v>7049655</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6109,7 +6113,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6119,7 +6123,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6146,7 +6150,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123304879</v>
+        <v>123304172</v>
       </c>
       <c r="B50" t="n">
         <v>98504</v>
@@ -6181,7 +6185,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6190,10 +6199,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580143</v>
+        <v>580186</v>
       </c>
       <c r="R50" t="n">
-        <v>7049655</v>
+        <v>7049672</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6225,7 +6234,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6235,7 +6244,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6250,19 +6259,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123304172</v>
+        <v>123306520</v>
       </c>
       <c r="B51" t="n">
         <v>98504</v>
@@ -6297,12 +6306,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6311,10 +6315,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580186</v>
+        <v>580082</v>
       </c>
       <c r="R51" t="n">
-        <v>7049672</v>
+        <v>7049717</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6346,7 +6350,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6356,7 +6360,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6371,22 +6375,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123306520</v>
+        <v>123309206</v>
       </c>
       <c r="B52" t="n">
-        <v>98504</v>
+        <v>78788</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6395,42 +6399,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580082</v>
+        <v>580174</v>
       </c>
       <c r="R52" t="n">
-        <v>7049717</v>
+        <v>7049673</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -1826,7 +1826,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123306079</v>
+        <v>123303674</v>
       </c>
       <c r="B12" t="n">
         <v>78788</v>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580118</v>
+        <v>580206</v>
       </c>
       <c r="R12" t="n">
-        <v>7049697</v>
+        <v>7049658</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123307927</v>
+        <v>123306981</v>
       </c>
       <c r="B13" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,21 +1954,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580078</v>
+        <v>580007</v>
       </c>
       <c r="R13" t="n">
-        <v>7049752</v>
+        <v>7049703</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123308600</v>
+        <v>123304879</v>
       </c>
       <c r="B14" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,38 +2062,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580103</v>
+        <v>580143</v>
       </c>
       <c r="R14" t="n">
-        <v>7049748</v>
+        <v>7049655</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2135,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123308088</v>
+        <v>123308600</v>
       </c>
       <c r="B15" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,39 +2182,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580037</v>
+        <v>580103</v>
       </c>
       <c r="R15" t="n">
-        <v>7049732</v>
+        <v>7049748</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2252,12 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2284,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123307914</v>
+        <v>123304706</v>
       </c>
       <c r="B16" t="n">
-        <v>79869</v>
+        <v>92271</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,25 +2290,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2324,10 +2318,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580053</v>
+        <v>580179</v>
       </c>
       <c r="R16" t="n">
-        <v>7049758</v>
+        <v>7049708</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2359,7 +2353,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2363,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,19 +2378,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123309182</v>
+        <v>123304722</v>
       </c>
       <c r="B17" t="n">
         <v>78788</v>
@@ -2436,10 +2430,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580139</v>
+        <v>580163</v>
       </c>
       <c r="R17" t="n">
-        <v>7049712</v>
+        <v>7049654</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,7 +2465,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,7 +2475,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2508,10 +2502,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123304342</v>
+        <v>123307482</v>
       </c>
       <c r="B18" t="n">
-        <v>92271</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2520,25 +2514,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2548,10 +2542,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580158</v>
+        <v>579986</v>
       </c>
       <c r="R18" t="n">
-        <v>7049670</v>
+        <v>7049735</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2583,7 +2577,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2593,7 +2587,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2620,10 +2614,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123303895</v>
+        <v>123307517</v>
       </c>
       <c r="B19" t="n">
-        <v>92271</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2632,25 +2626,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2660,10 +2654,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580189</v>
+        <v>580020</v>
       </c>
       <c r="R19" t="n">
-        <v>7049660</v>
+        <v>7049752</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2695,7 +2689,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2705,7 +2699,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2732,10 +2726,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123307810</v>
+        <v>123304880</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2744,38 +2738,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580037</v>
+        <v>580159</v>
       </c>
       <c r="R20" t="n">
-        <v>7049763</v>
+        <v>7049755</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2807,7 +2810,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2817,7 +2820,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2832,22 +2835,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123307802</v>
+        <v>123306199</v>
       </c>
       <c r="B21" t="n">
-        <v>82575</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2856,38 +2859,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580037</v>
+        <v>580119</v>
       </c>
       <c r="R21" t="n">
-        <v>7049768</v>
+        <v>7049689</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2919,7 +2926,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2929,7 +2936,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2956,10 +2963,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123305283</v>
+        <v>123309206</v>
       </c>
       <c r="B22" t="n">
-        <v>98504</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2968,42 +2975,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580160</v>
+        <v>580174</v>
       </c>
       <c r="R22" t="n">
-        <v>7049663</v>
+        <v>7049673</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3035,7 +3038,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3045,7 +3048,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3072,7 +3075,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123303674</v>
+        <v>123306849</v>
       </c>
       <c r="B23" t="n">
         <v>78788</v>
@@ -3112,10 +3115,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580206</v>
+        <v>580039</v>
       </c>
       <c r="R23" t="n">
-        <v>7049658</v>
+        <v>7049688</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3147,7 +3150,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3157,7 +3160,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3184,10 +3187,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123305088</v>
+        <v>123307841</v>
       </c>
       <c r="B24" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3196,38 +3199,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580164</v>
+        <v>580049</v>
       </c>
       <c r="R24" t="n">
-        <v>7049642</v>
+        <v>7049765</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3259,7 +3266,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3269,7 +3276,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3296,10 +3303,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123306199</v>
+        <v>123306694</v>
       </c>
       <c r="B25" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3331,7 +3338,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3340,10 +3347,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580119</v>
+        <v>580043</v>
       </c>
       <c r="R25" t="n">
-        <v>7049689</v>
+        <v>7049753</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3375,7 +3382,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3385,7 +3392,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3400,22 +3407,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123309023</v>
+        <v>123305283</v>
       </c>
       <c r="B26" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3424,38 +3431,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580106</v>
+        <v>580160</v>
       </c>
       <c r="R26" t="n">
-        <v>7049714</v>
+        <v>7049663</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3487,7 +3498,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3497,7 +3508,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3524,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123307659</v>
+        <v>123306079</v>
       </c>
       <c r="B27" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3540,21 +3551,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3564,10 +3575,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580022</v>
+        <v>580118</v>
       </c>
       <c r="R27" t="n">
-        <v>7049763</v>
+        <v>7049697</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3599,7 +3610,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3609,7 +3620,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3636,10 +3647,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123305011</v>
+        <v>123303786</v>
       </c>
       <c r="B28" t="n">
-        <v>90990</v>
+        <v>57491</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3652,34 +3663,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580151</v>
+        <v>580193</v>
       </c>
       <c r="R28" t="n">
-        <v>7049633</v>
+        <v>7049674</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3711,7 +3727,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3721,7 +3737,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3748,10 +3769,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123306981</v>
+        <v>123307927</v>
       </c>
       <c r="B29" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3764,21 +3785,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3788,10 +3809,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580007</v>
+        <v>580078</v>
       </c>
       <c r="R29" t="n">
-        <v>7049703</v>
+        <v>7049752</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3823,7 +3844,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3833,7 +3854,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3860,10 +3881,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123305387</v>
+        <v>123307802</v>
       </c>
       <c r="B30" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3876,21 +3897,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3900,10 +3921,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580124</v>
+        <v>580037</v>
       </c>
       <c r="R30" t="n">
-        <v>7049764</v>
+        <v>7049768</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3935,7 +3956,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3945,7 +3966,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3960,22 +3981,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123307053</v>
+        <v>123304342</v>
       </c>
       <c r="B31" t="n">
-        <v>78788</v>
+        <v>92271</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3984,25 +4005,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4012,10 +4033,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>579979</v>
+        <v>580158</v>
       </c>
       <c r="R31" t="n">
-        <v>7049720</v>
+        <v>7049670</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4047,7 +4068,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4057,7 +4078,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4084,10 +4105,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123304811</v>
+        <v>123308088</v>
       </c>
       <c r="B32" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4100,34 +4121,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580141</v>
+        <v>580037</v>
       </c>
       <c r="R32" t="n">
-        <v>7049654</v>
+        <v>7049732</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4159,7 +4185,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4169,7 +4195,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4196,10 +4227,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123304722</v>
+        <v>123303895</v>
       </c>
       <c r="B33" t="n">
-        <v>78788</v>
+        <v>92271</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4208,25 +4239,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4236,10 +4267,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580163</v>
+        <v>580189</v>
       </c>
       <c r="R33" t="n">
-        <v>7049654</v>
+        <v>7049660</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4271,7 +4302,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4281,7 +4312,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4308,10 +4339,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123306094</v>
+        <v>123305019</v>
       </c>
       <c r="B34" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4324,34 +4355,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580111</v>
+        <v>580166</v>
       </c>
       <c r="R34" t="n">
-        <v>7049724</v>
+        <v>7049779</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4383,7 +4419,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4393,7 +4429,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4420,10 +4461,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123306062</v>
+        <v>123305011</v>
       </c>
       <c r="B35" t="n">
-        <v>92271</v>
+        <v>90990</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4432,25 +4473,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4460,10 +4501,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580126</v>
+        <v>580151</v>
       </c>
       <c r="R35" t="n">
-        <v>7049722</v>
+        <v>7049633</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4495,7 +4536,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4505,7 +4546,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4520,22 +4561,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123304706</v>
+        <v>123304172</v>
       </c>
       <c r="B36" t="n">
-        <v>92271</v>
+        <v>98079</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4544,38 +4585,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580179</v>
+        <v>580186</v>
       </c>
       <c r="R36" t="n">
-        <v>7049708</v>
+        <v>7049672</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4607,7 +4657,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4617,7 +4667,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4644,10 +4694,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123306849</v>
+        <v>123307914</v>
       </c>
       <c r="B37" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4660,21 +4710,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4684,10 +4734,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580039</v>
+        <v>580053</v>
       </c>
       <c r="R37" t="n">
-        <v>7049688</v>
+        <v>7049758</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4719,7 +4769,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4729,7 +4779,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4756,10 +4806,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123305019</v>
+        <v>123309023</v>
       </c>
       <c r="B38" t="n">
-        <v>57491</v>
+        <v>90990</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4772,39 +4822,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580166</v>
+        <v>580106</v>
       </c>
       <c r="R38" t="n">
-        <v>7049779</v>
+        <v>7049714</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4836,7 +4881,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4846,12 +4891,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4866,22 +4906,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123304880</v>
+        <v>123308517</v>
       </c>
       <c r="B39" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4890,47 +4930,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580159</v>
+        <v>580100</v>
       </c>
       <c r="R39" t="n">
-        <v>7049755</v>
+        <v>7049758</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4962,7 +4993,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4972,7 +5003,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4987,22 +5018,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123307604</v>
+        <v>123307053</v>
       </c>
       <c r="B40" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5015,21 +5046,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5039,10 +5070,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580021</v>
+        <v>579979</v>
       </c>
       <c r="R40" t="n">
-        <v>7049755</v>
+        <v>7049720</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5074,7 +5105,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5084,7 +5115,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5111,10 +5142,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123307035</v>
+        <v>123307659</v>
       </c>
       <c r="B41" t="n">
-        <v>57507</v>
+        <v>79869</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5127,39 +5158,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>579970</v>
+        <v>580022</v>
       </c>
       <c r="R41" t="n">
-        <v>7049717</v>
+        <v>7049763</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5191,7 +5217,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5201,7 +5227,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5228,10 +5254,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123307841</v>
+        <v>123307604</v>
       </c>
       <c r="B42" t="n">
-        <v>98504</v>
+        <v>82575</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5240,42 +5266,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580049</v>
+        <v>580021</v>
       </c>
       <c r="R42" t="n">
-        <v>7049765</v>
+        <v>7049755</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5307,7 +5329,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5317,7 +5339,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5344,10 +5366,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123307517</v>
+        <v>123306094</v>
       </c>
       <c r="B43" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5360,21 +5382,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5384,10 +5406,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580020</v>
+        <v>580111</v>
       </c>
       <c r="R43" t="n">
-        <v>7049752</v>
+        <v>7049724</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5419,7 +5441,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5429,7 +5451,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5444,22 +5466,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123303786</v>
+        <v>123305088</v>
       </c>
       <c r="B44" t="n">
-        <v>57491</v>
+        <v>90990</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5472,39 +5494,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580193</v>
+        <v>580164</v>
       </c>
       <c r="R44" t="n">
-        <v>7049674</v>
+        <v>7049642</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5536,7 +5553,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5546,12 +5563,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5578,10 +5590,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123307482</v>
+        <v>123306520</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5590,38 +5602,42 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>579986</v>
+        <v>580082</v>
       </c>
       <c r="R45" t="n">
-        <v>7049735</v>
+        <v>7049717</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5653,7 +5669,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5663,7 +5679,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5693,7 +5709,7 @@
         <v>123308246</v>
       </c>
       <c r="B46" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5806,10 +5822,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123306694</v>
+        <v>123306062</v>
       </c>
       <c r="B47" t="n">
-        <v>98504</v>
+        <v>92271</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5818,42 +5834,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580043</v>
+        <v>580126</v>
       </c>
       <c r="R47" t="n">
-        <v>7049753</v>
+        <v>7049722</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5885,7 +5897,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5895,7 +5907,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5922,10 +5934,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123308517</v>
+        <v>123307810</v>
       </c>
       <c r="B48" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5938,21 +5950,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5962,10 +5974,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580100</v>
+        <v>580037</v>
       </c>
       <c r="R48" t="n">
-        <v>7049758</v>
+        <v>7049763</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5997,7 +6009,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6007,7 +6019,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6034,10 +6046,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123304879</v>
+        <v>123309182</v>
       </c>
       <c r="B49" t="n">
-        <v>98504</v>
+        <v>78788</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6046,42 +6058,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580143</v>
+        <v>580139</v>
       </c>
       <c r="R49" t="n">
-        <v>7049655</v>
+        <v>7049712</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6113,7 +6121,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6123,7 +6131,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6150,10 +6158,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123304172</v>
+        <v>123305387</v>
       </c>
       <c r="B50" t="n">
-        <v>98504</v>
+        <v>78788</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6162,47 +6170,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580186</v>
+        <v>580124</v>
       </c>
       <c r="R50" t="n">
-        <v>7049672</v>
+        <v>7049764</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6234,7 +6233,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6244,7 +6243,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6271,10 +6270,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123306520</v>
+        <v>123304811</v>
       </c>
       <c r="B51" t="n">
-        <v>98504</v>
+        <v>79869</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6283,42 +6282,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580082</v>
+        <v>580141</v>
       </c>
       <c r="R51" t="n">
-        <v>7049717</v>
+        <v>7049654</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6350,7 +6345,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6360,7 +6355,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6387,10 +6382,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123309206</v>
+        <v>123307035</v>
       </c>
       <c r="B52" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6403,34 +6398,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580174</v>
+        <v>579970</v>
       </c>
       <c r="R52" t="n">
-        <v>7049673</v>
+        <v>7049717</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -2050,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123304879</v>
+        <v>123308600</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,42 +2062,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580143</v>
+        <v>580103</v>
       </c>
       <c r="R14" t="n">
-        <v>7049655</v>
+        <v>7049748</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2125,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2135,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2162,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123308600</v>
+        <v>123304879</v>
       </c>
       <c r="B15" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,38 +2174,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580103</v>
+        <v>580143</v>
       </c>
       <c r="R15" t="n">
-        <v>7049748</v>
+        <v>7049655</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2847,10 +2847,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123306199</v>
+        <v>123309206</v>
       </c>
       <c r="B21" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2859,42 +2859,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580119</v>
+        <v>580174</v>
       </c>
       <c r="R21" t="n">
-        <v>7049689</v>
+        <v>7049673</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2926,7 +2922,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2936,7 +2932,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,10 +2959,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123309206</v>
+        <v>123306199</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2975,38 +2971,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580174</v>
+        <v>580119</v>
       </c>
       <c r="R22" t="n">
-        <v>7049673</v>
+        <v>7049689</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3075,10 +3075,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123306849</v>
+        <v>123307841</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3087,38 +3087,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580039</v>
+        <v>580049</v>
       </c>
       <c r="R23" t="n">
-        <v>7049688</v>
+        <v>7049765</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,7 +3154,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3160,7 +3164,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3187,7 +3191,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123307841</v>
+        <v>123306694</v>
       </c>
       <c r="B24" t="n">
         <v>98079</v>
@@ -3222,7 +3226,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3231,10 +3235,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580049</v>
+        <v>580043</v>
       </c>
       <c r="R24" t="n">
-        <v>7049765</v>
+        <v>7049753</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3266,7 +3270,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3276,7 +3280,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3291,19 +3295,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123306694</v>
+        <v>123305283</v>
       </c>
       <c r="B25" t="n">
         <v>98079</v>
@@ -3338,7 +3342,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3347,10 +3351,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580043</v>
+        <v>580160</v>
       </c>
       <c r="R25" t="n">
-        <v>7049753</v>
+        <v>7049663</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3382,7 +3386,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3392,7 +3396,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3407,22 +3411,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123305283</v>
+        <v>123306849</v>
       </c>
       <c r="B26" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3431,42 +3435,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580160</v>
+        <v>580039</v>
       </c>
       <c r="R26" t="n">
-        <v>7049663</v>
+        <v>7049688</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3993,10 +3993,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123304342</v>
+        <v>123308088</v>
       </c>
       <c r="B31" t="n">
-        <v>92271</v>
+        <v>57491</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4005,38 +4005,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580158</v>
+        <v>580037</v>
       </c>
       <c r="R31" t="n">
-        <v>7049670</v>
+        <v>7049732</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4068,7 +4073,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4078,7 +4083,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4105,10 +4115,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123308088</v>
+        <v>123304342</v>
       </c>
       <c r="B32" t="n">
-        <v>57491</v>
+        <v>92271</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4117,43 +4127,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580037</v>
+        <v>580158</v>
       </c>
       <c r="R32" t="n">
-        <v>7049732</v>
+        <v>7049670</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4185,7 +4190,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4195,12 +4200,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -1826,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123303674</v>
+        <v>123306062</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>92271</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,25 +1838,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580206</v>
+        <v>580126</v>
       </c>
       <c r="R12" t="n">
-        <v>7049658</v>
+        <v>7049722</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,22 +1926,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123306981</v>
+        <v>123307659</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,21 +1954,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580007</v>
+        <v>580022</v>
       </c>
       <c r="R13" t="n">
-        <v>7049703</v>
+        <v>7049763</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123308600</v>
+        <v>123306694</v>
       </c>
       <c r="B14" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,38 +2062,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580103</v>
+        <v>580043</v>
       </c>
       <c r="R14" t="n">
-        <v>7049748</v>
+        <v>7049753</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2135,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,22 +2154,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123304879</v>
+        <v>123305019</v>
       </c>
       <c r="B15" t="n">
-        <v>98079</v>
+        <v>57491</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,30 +2178,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2206,10 +2211,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580143</v>
+        <v>580166</v>
       </c>
       <c r="R15" t="n">
-        <v>7049655</v>
+        <v>7049779</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2246,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2256,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,22 +2276,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123304706</v>
+        <v>123308600</v>
       </c>
       <c r="B16" t="n">
-        <v>92271</v>
+        <v>79869</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,25 +2300,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2318,10 +2328,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580179</v>
+        <v>580103</v>
       </c>
       <c r="R16" t="n">
-        <v>7049708</v>
+        <v>7049748</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2363,7 +2373,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,22 +2388,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123304722</v>
+        <v>123307927</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2406,21 +2416,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2430,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580163</v>
+        <v>580078</v>
       </c>
       <c r="R17" t="n">
-        <v>7049654</v>
+        <v>7049752</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2475,7 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2502,10 +2512,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123307482</v>
+        <v>123308517</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2518,21 +2528,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2542,10 +2552,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579986</v>
+        <v>580100</v>
       </c>
       <c r="R18" t="n">
-        <v>7049735</v>
+        <v>7049758</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2577,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2587,7 +2597,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2614,10 +2624,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123307517</v>
+        <v>123305088</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,21 +2640,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2654,10 +2664,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580020</v>
+        <v>580164</v>
       </c>
       <c r="R19" t="n">
-        <v>7049752</v>
+        <v>7049642</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2689,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2699,7 +2709,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2726,7 +2736,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123304880</v>
+        <v>123307841</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2761,12 +2771,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2775,10 +2780,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580159</v>
+        <v>580049</v>
       </c>
       <c r="R20" t="n">
-        <v>7049755</v>
+        <v>7049765</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2810,7 +2815,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2820,7 +2825,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2835,19 +2840,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123309206</v>
+        <v>123305387</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -2887,10 +2892,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580174</v>
+        <v>580124</v>
       </c>
       <c r="R21" t="n">
-        <v>7049673</v>
+        <v>7049764</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2922,7 +2927,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2932,7 +2937,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2947,22 +2952,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123306199</v>
+        <v>123307053</v>
       </c>
       <c r="B22" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2971,42 +2976,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580119</v>
+        <v>579979</v>
       </c>
       <c r="R22" t="n">
-        <v>7049689</v>
+        <v>7049720</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3038,7 +3039,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3048,7 +3049,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3075,10 +3076,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123307841</v>
+        <v>123309206</v>
       </c>
       <c r="B23" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3087,42 +3088,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580049</v>
+        <v>580174</v>
       </c>
       <c r="R23" t="n">
-        <v>7049765</v>
+        <v>7049673</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3154,7 +3151,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3164,7 +3161,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3191,10 +3188,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123306694</v>
+        <v>123303786</v>
       </c>
       <c r="B24" t="n">
-        <v>98079</v>
+        <v>57491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3203,30 +3200,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3235,10 +3233,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580043</v>
+        <v>580193</v>
       </c>
       <c r="R24" t="n">
-        <v>7049753</v>
+        <v>7049674</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3270,7 +3268,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3280,7 +3278,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3295,22 +3298,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123305283</v>
+        <v>123308088</v>
       </c>
       <c r="B25" t="n">
-        <v>98079</v>
+        <v>57491</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3319,30 +3322,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3351,10 +3355,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580160</v>
+        <v>580037</v>
       </c>
       <c r="R25" t="n">
-        <v>7049663</v>
+        <v>7049732</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3386,7 +3390,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3396,7 +3400,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3423,7 +3432,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123306849</v>
+        <v>123307517</v>
       </c>
       <c r="B26" t="n">
         <v>78788</v>
@@ -3463,10 +3472,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580039</v>
+        <v>580020</v>
       </c>
       <c r="R26" t="n">
-        <v>7049688</v>
+        <v>7049752</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3498,7 +3507,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3508,7 +3517,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3535,7 +3544,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123306079</v>
+        <v>123309182</v>
       </c>
       <c r="B27" t="n">
         <v>78788</v>
@@ -3575,10 +3584,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580118</v>
+        <v>580139</v>
       </c>
       <c r="R27" t="n">
-        <v>7049697</v>
+        <v>7049712</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3610,7 +3619,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3620,7 +3629,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3647,10 +3656,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123303786</v>
+        <v>123304722</v>
       </c>
       <c r="B28" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3663,39 +3672,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580193</v>
+        <v>580163</v>
       </c>
       <c r="R28" t="n">
-        <v>7049674</v>
+        <v>7049654</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3727,7 +3731,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3737,12 +3741,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3769,10 +3768,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123307927</v>
+        <v>123307482</v>
       </c>
       <c r="B29" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3785,21 +3784,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3809,10 +3808,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580078</v>
+        <v>579986</v>
       </c>
       <c r="R29" t="n">
-        <v>7049752</v>
+        <v>7049735</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3844,7 +3843,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3854,7 +3853,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3881,10 +3880,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123307802</v>
+        <v>123306079</v>
       </c>
       <c r="B30" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3897,21 +3896,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3921,10 +3920,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580037</v>
+        <v>580118</v>
       </c>
       <c r="R30" t="n">
-        <v>7049768</v>
+        <v>7049697</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3956,7 +3955,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3966,7 +3965,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3993,10 +3992,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123308088</v>
+        <v>123308246</v>
       </c>
       <c r="B31" t="n">
-        <v>57491</v>
+        <v>98079</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4005,31 +4004,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4038,10 +4036,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580037</v>
+        <v>580053</v>
       </c>
       <c r="R31" t="n">
-        <v>7049732</v>
+        <v>7049735</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4073,7 +4071,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4083,12 +4081,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4115,10 +4108,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123304342</v>
+        <v>123307802</v>
       </c>
       <c r="B32" t="n">
-        <v>92271</v>
+        <v>82575</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4127,25 +4120,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4155,10 +4148,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580158</v>
+        <v>580037</v>
       </c>
       <c r="R32" t="n">
-        <v>7049670</v>
+        <v>7049768</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4190,7 +4183,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4200,7 +4193,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4227,10 +4220,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123303895</v>
+        <v>123307035</v>
       </c>
       <c r="B33" t="n">
-        <v>92271</v>
+        <v>57507</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4239,38 +4232,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580189</v>
+        <v>579970</v>
       </c>
       <c r="R33" t="n">
-        <v>7049660</v>
+        <v>7049717</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4302,7 +4300,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4312,7 +4310,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4339,10 +4337,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123305019</v>
+        <v>123307604</v>
       </c>
       <c r="B34" t="n">
-        <v>57491</v>
+        <v>82575</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4355,39 +4353,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580166</v>
+        <v>580021</v>
       </c>
       <c r="R34" t="n">
-        <v>7049779</v>
+        <v>7049755</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4419,7 +4412,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4429,12 +4422,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4449,22 +4437,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123305011</v>
+        <v>123303674</v>
       </c>
       <c r="B35" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4477,21 +4465,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4501,10 +4489,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580151</v>
+        <v>580206</v>
       </c>
       <c r="R35" t="n">
-        <v>7049633</v>
+        <v>7049658</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4536,7 +4524,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4546,7 +4534,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4573,10 +4561,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123304172</v>
+        <v>123306849</v>
       </c>
       <c r="B36" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4585,47 +4573,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580186</v>
+        <v>580039</v>
       </c>
       <c r="R36" t="n">
-        <v>7049672</v>
+        <v>7049688</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4657,7 +4636,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4667,7 +4646,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4682,22 +4661,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123307914</v>
+        <v>123306199</v>
       </c>
       <c r="B37" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4706,38 +4685,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580053</v>
+        <v>580119</v>
       </c>
       <c r="R37" t="n">
-        <v>7049758</v>
+        <v>7049689</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4769,7 +4752,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4779,7 +4762,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4806,10 +4789,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123309023</v>
+        <v>123306981</v>
       </c>
       <c r="B38" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4822,21 +4805,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4846,10 +4829,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580106</v>
+        <v>580007</v>
       </c>
       <c r="R38" t="n">
-        <v>7049714</v>
+        <v>7049703</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4881,7 +4864,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4891,7 +4874,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4918,10 +4901,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123308517</v>
+        <v>123307914</v>
       </c>
       <c r="B39" t="n">
-        <v>90990</v>
+        <v>79869</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4934,21 +4917,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4958,7 +4941,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580100</v>
+        <v>580053</v>
       </c>
       <c r="R39" t="n">
         <v>7049758</v>
@@ -4993,7 +4976,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5003,7 +4986,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5030,10 +5013,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123307053</v>
+        <v>123303895</v>
       </c>
       <c r="B40" t="n">
-        <v>78788</v>
+        <v>92271</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5042,25 +5025,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5070,10 +5053,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>579979</v>
+        <v>580189</v>
       </c>
       <c r="R40" t="n">
-        <v>7049720</v>
+        <v>7049660</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5105,7 +5088,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5115,7 +5098,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5142,10 +5125,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123307659</v>
+        <v>123304706</v>
       </c>
       <c r="B41" t="n">
-        <v>79869</v>
+        <v>92271</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5154,25 +5137,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5182,10 +5165,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580022</v>
+        <v>580179</v>
       </c>
       <c r="R41" t="n">
-        <v>7049763</v>
+        <v>7049708</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5217,7 +5200,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5227,7 +5210,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5242,22 +5225,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123307604</v>
+        <v>123304879</v>
       </c>
       <c r="B42" t="n">
-        <v>82575</v>
+        <v>98079</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5266,38 +5249,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580021</v>
+        <v>580143</v>
       </c>
       <c r="R42" t="n">
-        <v>7049755</v>
+        <v>7049655</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5329,7 +5316,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5339,7 +5326,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5366,10 +5353,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123306094</v>
+        <v>123304172</v>
       </c>
       <c r="B43" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5378,38 +5365,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580111</v>
+        <v>580186</v>
       </c>
       <c r="R43" t="n">
-        <v>7049724</v>
+        <v>7049672</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5441,7 +5437,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5451,7 +5447,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5478,7 +5474,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123305088</v>
+        <v>123309023</v>
       </c>
       <c r="B44" t="n">
         <v>90990</v>
@@ -5518,10 +5514,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580164</v>
+        <v>580106</v>
       </c>
       <c r="R44" t="n">
-        <v>7049642</v>
+        <v>7049714</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5553,7 +5549,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5563,7 +5559,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5590,10 +5586,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123306520</v>
+        <v>123305011</v>
       </c>
       <c r="B45" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5602,42 +5598,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580082</v>
+        <v>580151</v>
       </c>
       <c r="R45" t="n">
-        <v>7049717</v>
+        <v>7049633</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5669,7 +5661,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5679,7 +5671,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5706,10 +5698,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123308246</v>
+        <v>123304342</v>
       </c>
       <c r="B46" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5718,42 +5710,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580053</v>
+        <v>580158</v>
       </c>
       <c r="R46" t="n">
-        <v>7049735</v>
+        <v>7049670</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5785,7 +5773,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5795,7 +5783,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5822,10 +5810,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123306062</v>
+        <v>123304811</v>
       </c>
       <c r="B47" t="n">
-        <v>92271</v>
+        <v>79869</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5834,25 +5822,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5862,10 +5850,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580126</v>
+        <v>580141</v>
       </c>
       <c r="R47" t="n">
-        <v>7049722</v>
+        <v>7049654</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5897,7 +5885,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5907,7 +5895,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5922,22 +5910,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123307810</v>
+        <v>123304880</v>
       </c>
       <c r="B48" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5946,38 +5934,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580037</v>
+        <v>580159</v>
       </c>
       <c r="R48" t="n">
-        <v>7049763</v>
+        <v>7049755</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6009,7 +6006,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6019,7 +6016,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6034,22 +6031,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123309182</v>
+        <v>123305283</v>
       </c>
       <c r="B49" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6058,38 +6055,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580139</v>
+        <v>580160</v>
       </c>
       <c r="R49" t="n">
-        <v>7049712</v>
+        <v>7049663</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6121,7 +6122,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6131,7 +6132,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6158,10 +6159,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123305387</v>
+        <v>123306520</v>
       </c>
       <c r="B50" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6170,38 +6171,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580124</v>
+        <v>580082</v>
       </c>
       <c r="R50" t="n">
-        <v>7049764</v>
+        <v>7049717</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6233,7 +6238,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6243,7 +6248,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6258,19 +6263,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123304811</v>
+        <v>123306094</v>
       </c>
       <c r="B51" t="n">
         <v>79869</v>
@@ -6310,10 +6315,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580141</v>
+        <v>580111</v>
       </c>
       <c r="R51" t="n">
-        <v>7049654</v>
+        <v>7049724</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6345,7 +6350,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6355,7 +6360,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6370,22 +6375,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123307035</v>
+        <v>123307810</v>
       </c>
       <c r="B52" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6398,39 +6403,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>579970</v>
+        <v>580037</v>
       </c>
       <c r="R52" t="n">
-        <v>7049717</v>
+        <v>7049763</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -1826,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123306062</v>
+        <v>123305088</v>
       </c>
       <c r="B12" t="n">
-        <v>92271</v>
+        <v>90990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,25 +1838,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580126</v>
+        <v>580164</v>
       </c>
       <c r="R12" t="n">
-        <v>7049722</v>
+        <v>7049642</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,19 +1926,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123307659</v>
+        <v>123308600</v>
       </c>
       <c r="B13" t="n">
         <v>79869</v>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580022</v>
+        <v>580103</v>
       </c>
       <c r="R13" t="n">
-        <v>7049763</v>
+        <v>7049748</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,10 +2050,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123306694</v>
+        <v>123309182</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,42 +2062,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580043</v>
+        <v>580139</v>
       </c>
       <c r="R14" t="n">
-        <v>7049753</v>
+        <v>7049712</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2125,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2135,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,22 +2150,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123305019</v>
+        <v>123307517</v>
       </c>
       <c r="B15" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,39 +2178,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580166</v>
+        <v>580020</v>
       </c>
       <c r="R15" t="n">
-        <v>7049779</v>
+        <v>7049752</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,7 +2237,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2256,12 +2247,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2276,22 +2262,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123308600</v>
+        <v>123304706</v>
       </c>
       <c r="B16" t="n">
-        <v>79869</v>
+        <v>92271</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,25 +2286,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580103</v>
+        <v>580179</v>
       </c>
       <c r="R16" t="n">
-        <v>7049748</v>
+        <v>7049708</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2363,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2373,7 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,22 +2374,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123307927</v>
+        <v>123304879</v>
       </c>
       <c r="B17" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,38 +2398,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580078</v>
+        <v>580143</v>
       </c>
       <c r="R17" t="n">
-        <v>7049752</v>
+        <v>7049655</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2465,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2475,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2624,10 +2614,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123305088</v>
+        <v>123304172</v>
       </c>
       <c r="B19" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2636,38 +2626,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580164</v>
+        <v>580186</v>
       </c>
       <c r="R19" t="n">
-        <v>7049642</v>
+        <v>7049672</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,7 +2698,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,7 +2708,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,19 +2723,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123307841</v>
+        <v>123308246</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2771,7 +2770,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2780,10 +2779,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580049</v>
+        <v>580053</v>
       </c>
       <c r="R20" t="n">
-        <v>7049765</v>
+        <v>7049735</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,7 +2814,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2825,7 +2824,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,7 +2851,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123305387</v>
+        <v>123306079</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -2892,10 +2891,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580124</v>
+        <v>580118</v>
       </c>
       <c r="R21" t="n">
-        <v>7049764</v>
+        <v>7049697</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2927,7 +2926,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2937,7 +2936,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2952,22 +2951,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123307053</v>
+        <v>123307927</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2980,21 +2979,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3004,10 +3003,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579979</v>
+        <v>580078</v>
       </c>
       <c r="R22" t="n">
-        <v>7049720</v>
+        <v>7049752</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3039,7 +3038,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3049,7 +3048,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3076,7 +3075,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123309206</v>
+        <v>123307810</v>
       </c>
       <c r="B23" t="n">
         <v>78788</v>
@@ -3116,10 +3115,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580174</v>
+        <v>580037</v>
       </c>
       <c r="R23" t="n">
-        <v>7049673</v>
+        <v>7049763</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3151,7 +3150,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3161,7 +3160,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3188,10 +3187,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123303786</v>
+        <v>123305283</v>
       </c>
       <c r="B24" t="n">
-        <v>57491</v>
+        <v>98079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3200,31 +3199,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3233,10 +3231,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580193</v>
+        <v>580160</v>
       </c>
       <c r="R24" t="n">
-        <v>7049674</v>
+        <v>7049663</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3268,7 +3266,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3278,12 +3276,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3310,10 +3303,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123308088</v>
+        <v>123309023</v>
       </c>
       <c r="B25" t="n">
-        <v>57491</v>
+        <v>90990</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3326,39 +3319,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580037</v>
+        <v>580106</v>
       </c>
       <c r="R25" t="n">
-        <v>7049732</v>
+        <v>7049714</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3390,7 +3378,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3400,12 +3388,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3432,7 +3415,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123307517</v>
+        <v>123306849</v>
       </c>
       <c r="B26" t="n">
         <v>78788</v>
@@ -3472,10 +3455,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580020</v>
+        <v>580039</v>
       </c>
       <c r="R26" t="n">
-        <v>7049752</v>
+        <v>7049688</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3507,7 +3490,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3517,7 +3500,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3544,7 +3527,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123309182</v>
+        <v>123309206</v>
       </c>
       <c r="B27" t="n">
         <v>78788</v>
@@ -3584,10 +3567,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580139</v>
+        <v>580174</v>
       </c>
       <c r="R27" t="n">
-        <v>7049712</v>
+        <v>7049673</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3619,7 +3602,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3629,7 +3612,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3656,10 +3639,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123304722</v>
+        <v>123306520</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3668,38 +3651,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580163</v>
+        <v>580082</v>
       </c>
       <c r="R28" t="n">
-        <v>7049654</v>
+        <v>7049717</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3731,7 +3718,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3741,7 +3728,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3768,7 +3755,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123307482</v>
+        <v>123305387</v>
       </c>
       <c r="B29" t="n">
         <v>78788</v>
@@ -3808,10 +3795,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579986</v>
+        <v>580124</v>
       </c>
       <c r="R29" t="n">
-        <v>7049735</v>
+        <v>7049764</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3843,7 +3830,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3853,7 +3840,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3868,22 +3855,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123306079</v>
+        <v>123307914</v>
       </c>
       <c r="B30" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3896,21 +3883,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3920,10 +3907,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580118</v>
+        <v>580053</v>
       </c>
       <c r="R30" t="n">
-        <v>7049697</v>
+        <v>7049758</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3955,7 +3942,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3965,7 +3952,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3992,7 +3979,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123308246</v>
+        <v>123304880</v>
       </c>
       <c r="B31" t="n">
         <v>98079</v>
@@ -4027,7 +4014,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4036,10 +4028,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580053</v>
+        <v>580159</v>
       </c>
       <c r="R31" t="n">
-        <v>7049735</v>
+        <v>7049755</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4071,7 +4063,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4081,7 +4073,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4096,22 +4088,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123307802</v>
+        <v>123303674</v>
       </c>
       <c r="B32" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4124,21 +4116,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4148,10 +4140,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580037</v>
+        <v>580206</v>
       </c>
       <c r="R32" t="n">
-        <v>7049768</v>
+        <v>7049658</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4183,7 +4175,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4193,7 +4185,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4220,10 +4212,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123307035</v>
+        <v>123305019</v>
       </c>
       <c r="B33" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4236,16 +4228,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4256,7 +4248,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4265,10 +4257,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>579970</v>
+        <v>580166</v>
       </c>
       <c r="R33" t="n">
-        <v>7049717</v>
+        <v>7049779</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4300,7 +4292,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4310,7 +4302,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4325,22 +4322,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123307604</v>
+        <v>123304342</v>
       </c>
       <c r="B34" t="n">
-        <v>82575</v>
+        <v>92271</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4349,25 +4346,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4377,10 +4374,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580021</v>
+        <v>580158</v>
       </c>
       <c r="R34" t="n">
-        <v>7049755</v>
+        <v>7049670</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4412,7 +4409,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4422,7 +4419,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4449,7 +4446,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123303674</v>
+        <v>123307053</v>
       </c>
       <c r="B35" t="n">
         <v>78788</v>
@@ -4489,10 +4486,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580206</v>
+        <v>579979</v>
       </c>
       <c r="R35" t="n">
-        <v>7049658</v>
+        <v>7049720</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4524,7 +4521,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4534,7 +4531,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4561,10 +4558,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123306849</v>
+        <v>123304811</v>
       </c>
       <c r="B36" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4577,21 +4574,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4601,10 +4598,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580039</v>
+        <v>580141</v>
       </c>
       <c r="R36" t="n">
-        <v>7049688</v>
+        <v>7049654</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4636,7 +4633,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4646,7 +4643,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4673,10 +4670,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123306199</v>
+        <v>123306062</v>
       </c>
       <c r="B37" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4685,42 +4682,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580119</v>
+        <v>580126</v>
       </c>
       <c r="R37" t="n">
-        <v>7049689</v>
+        <v>7049722</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4752,7 +4745,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4762,7 +4755,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4777,22 +4770,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123306981</v>
+        <v>123303895</v>
       </c>
       <c r="B38" t="n">
-        <v>78788</v>
+        <v>92271</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4801,25 +4794,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4829,10 +4822,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580007</v>
+        <v>580189</v>
       </c>
       <c r="R38" t="n">
-        <v>7049703</v>
+        <v>7049660</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4864,7 +4857,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4874,7 +4867,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4901,7 +4894,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123307914</v>
+        <v>123306094</v>
       </c>
       <c r="B39" t="n">
         <v>79869</v>
@@ -4941,10 +4934,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580053</v>
+        <v>580111</v>
       </c>
       <c r="R39" t="n">
-        <v>7049758</v>
+        <v>7049724</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4976,7 +4969,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4986,7 +4979,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5001,22 +4994,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123303895</v>
+        <v>123307035</v>
       </c>
       <c r="B40" t="n">
-        <v>92271</v>
+        <v>57507</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5025,38 +5018,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580189</v>
+        <v>579970</v>
       </c>
       <c r="R40" t="n">
-        <v>7049660</v>
+        <v>7049717</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5088,7 +5086,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5098,7 +5096,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5125,10 +5123,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123304706</v>
+        <v>123307802</v>
       </c>
       <c r="B41" t="n">
-        <v>92271</v>
+        <v>82575</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5137,25 +5135,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5165,10 +5163,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580179</v>
+        <v>580037</v>
       </c>
       <c r="R41" t="n">
-        <v>7049708</v>
+        <v>7049768</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5200,7 +5198,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5210,7 +5208,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5225,22 +5223,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123304879</v>
+        <v>123307659</v>
       </c>
       <c r="B42" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5249,42 +5247,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580143</v>
+        <v>580022</v>
       </c>
       <c r="R42" t="n">
-        <v>7049655</v>
+        <v>7049763</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5316,7 +5310,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5326,7 +5320,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5353,10 +5347,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123304172</v>
+        <v>123307482</v>
       </c>
       <c r="B43" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5365,47 +5359,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580186</v>
+        <v>579986</v>
       </c>
       <c r="R43" t="n">
-        <v>7049672</v>
+        <v>7049735</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5437,7 +5422,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5447,7 +5432,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5462,19 +5447,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123309023</v>
+        <v>123305011</v>
       </c>
       <c r="B44" t="n">
         <v>90990</v>
@@ -5514,10 +5499,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580106</v>
+        <v>580151</v>
       </c>
       <c r="R44" t="n">
-        <v>7049714</v>
+        <v>7049633</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5549,7 +5534,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5559,7 +5544,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5586,10 +5571,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123305011</v>
+        <v>123303786</v>
       </c>
       <c r="B45" t="n">
-        <v>90990</v>
+        <v>57491</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5602,34 +5587,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580151</v>
+        <v>580193</v>
       </c>
       <c r="R45" t="n">
-        <v>7049633</v>
+        <v>7049674</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5661,7 +5651,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5671,7 +5661,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5698,10 +5693,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123304342</v>
+        <v>123308088</v>
       </c>
       <c r="B46" t="n">
-        <v>92271</v>
+        <v>57491</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5710,38 +5705,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580158</v>
+        <v>580037</v>
       </c>
       <c r="R46" t="n">
-        <v>7049670</v>
+        <v>7049732</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5783,7 +5783,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5810,10 +5815,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123304811</v>
+        <v>123306981</v>
       </c>
       <c r="B47" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5826,21 +5831,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5850,10 +5855,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580141</v>
+        <v>580007</v>
       </c>
       <c r="R47" t="n">
-        <v>7049654</v>
+        <v>7049703</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5885,7 +5890,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5895,7 +5900,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5922,10 +5927,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123304880</v>
+        <v>123304722</v>
       </c>
       <c r="B48" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5934,47 +5939,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580159</v>
+        <v>580163</v>
       </c>
       <c r="R48" t="n">
-        <v>7049755</v>
+        <v>7049654</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6006,7 +6002,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6016,7 +6012,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6031,19 +6027,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123305283</v>
+        <v>123307841</v>
       </c>
       <c r="B49" t="n">
         <v>98079</v>
@@ -6078,7 +6074,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6087,10 +6083,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580160</v>
+        <v>580049</v>
       </c>
       <c r="R49" t="n">
-        <v>7049663</v>
+        <v>7049765</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6122,7 +6118,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6132,7 +6128,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6159,7 +6155,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123306520</v>
+        <v>123306199</v>
       </c>
       <c r="B50" t="n">
         <v>98079</v>
@@ -6194,7 +6190,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6203,10 +6199,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580082</v>
+        <v>580119</v>
       </c>
       <c r="R50" t="n">
-        <v>7049717</v>
+        <v>7049689</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6238,7 +6234,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6248,7 +6244,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6275,10 +6271,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123306094</v>
+        <v>123307604</v>
       </c>
       <c r="B51" t="n">
-        <v>79869</v>
+        <v>82575</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6291,21 +6287,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6315,10 +6311,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580111</v>
+        <v>580021</v>
       </c>
       <c r="R51" t="n">
-        <v>7049724</v>
+        <v>7049755</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6350,7 +6346,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6360,7 +6356,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6375,22 +6371,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123307810</v>
+        <v>123306694</v>
       </c>
       <c r="B52" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6399,38 +6395,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580037</v>
+        <v>580043</v>
       </c>
       <c r="R52" t="n">
-        <v>7049763</v>
+        <v>7049753</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6487,12 +6487,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -1826,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123305088</v>
+        <v>123308246</v>
       </c>
       <c r="B12" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,38 +1838,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580164</v>
+        <v>580053</v>
       </c>
       <c r="R12" t="n">
-        <v>7049642</v>
+        <v>7049735</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123308600</v>
+        <v>123307053</v>
       </c>
       <c r="B13" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,21 +1958,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1978,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580103</v>
+        <v>579979</v>
       </c>
       <c r="R13" t="n">
-        <v>7049748</v>
+        <v>7049720</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2027,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,10 +2054,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123309182</v>
+        <v>123308517</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,21 +2070,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2090,10 +2094,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580139</v>
+        <v>580100</v>
       </c>
       <c r="R14" t="n">
-        <v>7049712</v>
+        <v>7049758</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,7 +2129,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2135,7 +2139,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123307517</v>
+        <v>123307914</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,21 +2182,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2202,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580020</v>
+        <v>580053</v>
       </c>
       <c r="R15" t="n">
-        <v>7049752</v>
+        <v>7049758</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,7 +2241,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2247,7 +2251,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,10 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123304706</v>
+        <v>123306094</v>
       </c>
       <c r="B16" t="n">
-        <v>92271</v>
+        <v>79869</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2286,25 +2290,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2314,10 +2318,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580179</v>
+        <v>580111</v>
       </c>
       <c r="R16" t="n">
-        <v>7049708</v>
+        <v>7049724</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2349,7 +2353,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2363,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,7 +2390,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123304879</v>
+        <v>123306694</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2421,7 +2425,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2430,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580143</v>
+        <v>580043</v>
       </c>
       <c r="R17" t="n">
-        <v>7049655</v>
+        <v>7049753</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2475,7 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,19 +2494,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123308517</v>
+        <v>123309023</v>
       </c>
       <c r="B18" t="n">
         <v>90990</v>
@@ -2542,10 +2546,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580100</v>
+        <v>580106</v>
       </c>
       <c r="R18" t="n">
-        <v>7049758</v>
+        <v>7049714</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2577,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2587,7 +2591,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2614,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123304172</v>
+        <v>123304706</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2626,47 +2630,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580186</v>
+        <v>580179</v>
       </c>
       <c r="R19" t="n">
-        <v>7049672</v>
+        <v>7049708</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2698,7 +2693,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2708,7 +2703,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,10 +2730,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123308246</v>
+        <v>123305088</v>
       </c>
       <c r="B20" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2747,42 +2742,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580053</v>
+        <v>580164</v>
       </c>
       <c r="R20" t="n">
-        <v>7049735</v>
+        <v>7049642</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2814,7 +2805,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2824,7 +2815,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2963,10 +2954,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123307927</v>
+        <v>123305283</v>
       </c>
       <c r="B22" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2975,38 +2966,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580078</v>
+        <v>580160</v>
       </c>
       <c r="R22" t="n">
-        <v>7049752</v>
+        <v>7049663</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3038,7 +3033,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3048,7 +3043,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3075,7 +3070,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123307810</v>
+        <v>123307517</v>
       </c>
       <c r="B23" t="n">
         <v>78788</v>
@@ -3115,10 +3110,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580037</v>
+        <v>580020</v>
       </c>
       <c r="R23" t="n">
-        <v>7049763</v>
+        <v>7049752</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3150,7 +3145,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3160,7 +3155,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3187,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123305283</v>
+        <v>123304811</v>
       </c>
       <c r="B24" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3199,42 +3194,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580160</v>
+        <v>580141</v>
       </c>
       <c r="R24" t="n">
-        <v>7049663</v>
+        <v>7049654</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3266,7 +3257,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3276,7 +3267,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3303,10 +3294,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123309023</v>
+        <v>123304172</v>
       </c>
       <c r="B25" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3315,38 +3306,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580106</v>
+        <v>580186</v>
       </c>
       <c r="R25" t="n">
-        <v>7049714</v>
+        <v>7049672</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3403,22 +3403,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123306849</v>
+        <v>123306062</v>
       </c>
       <c r="B26" t="n">
-        <v>78788</v>
+        <v>92271</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3427,25 +3427,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580039</v>
+        <v>580126</v>
       </c>
       <c r="R26" t="n">
-        <v>7049688</v>
+        <v>7049722</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3515,22 +3515,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123309206</v>
+        <v>123308088</v>
       </c>
       <c r="B27" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3543,34 +3543,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580174</v>
+        <v>580037</v>
       </c>
       <c r="R27" t="n">
-        <v>7049673</v>
+        <v>7049732</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3602,7 +3607,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3612,7 +3617,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3639,7 +3649,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123306520</v>
+        <v>123304880</v>
       </c>
       <c r="B28" t="n">
         <v>98079</v>
@@ -3674,7 +3684,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3683,10 +3698,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580082</v>
+        <v>580159</v>
       </c>
       <c r="R28" t="n">
-        <v>7049717</v>
+        <v>7049755</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3718,7 +3733,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3728,7 +3743,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3743,19 +3758,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123305387</v>
+        <v>123306981</v>
       </c>
       <c r="B29" t="n">
         <v>78788</v>
@@ -3795,10 +3810,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580124</v>
+        <v>580007</v>
       </c>
       <c r="R29" t="n">
-        <v>7049764</v>
+        <v>7049703</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3830,7 +3845,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3840,7 +3855,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3855,22 +3870,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123307914</v>
+        <v>123309206</v>
       </c>
       <c r="B30" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3883,21 +3898,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3907,10 +3922,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580053</v>
+        <v>580174</v>
       </c>
       <c r="R30" t="n">
-        <v>7049758</v>
+        <v>7049673</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3942,7 +3957,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3952,7 +3967,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3979,10 +3994,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123304880</v>
+        <v>123306849</v>
       </c>
       <c r="B31" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3991,47 +4006,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580159</v>
+        <v>580039</v>
       </c>
       <c r="R31" t="n">
-        <v>7049755</v>
+        <v>7049688</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4063,7 +4069,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4073,7 +4079,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4088,22 +4094,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123303674</v>
+        <v>123308600</v>
       </c>
       <c r="B32" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4116,21 +4122,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4140,10 +4146,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580206</v>
+        <v>580103</v>
       </c>
       <c r="R32" t="n">
-        <v>7049658</v>
+        <v>7049748</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4175,7 +4181,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4185,7 +4191,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4212,10 +4218,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123305019</v>
+        <v>123305011</v>
       </c>
       <c r="B33" t="n">
-        <v>57491</v>
+        <v>90990</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4228,39 +4234,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580166</v>
+        <v>580151</v>
       </c>
       <c r="R33" t="n">
-        <v>7049779</v>
+        <v>7049633</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4292,7 +4293,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4302,12 +4303,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4322,22 +4318,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123304342</v>
+        <v>123307810</v>
       </c>
       <c r="B34" t="n">
-        <v>92271</v>
+        <v>78788</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4346,25 +4342,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4374,10 +4370,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580158</v>
+        <v>580037</v>
       </c>
       <c r="R34" t="n">
-        <v>7049670</v>
+        <v>7049763</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4409,7 +4405,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4419,7 +4415,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4446,10 +4442,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123307053</v>
+        <v>123307802</v>
       </c>
       <c r="B35" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4462,21 +4458,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4486,10 +4482,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>579979</v>
+        <v>580037</v>
       </c>
       <c r="R35" t="n">
-        <v>7049720</v>
+        <v>7049768</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4521,7 +4517,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4531,7 +4527,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4558,10 +4554,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123304811</v>
+        <v>123306199</v>
       </c>
       <c r="B36" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4570,38 +4566,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580141</v>
+        <v>580119</v>
       </c>
       <c r="R36" t="n">
-        <v>7049654</v>
+        <v>7049689</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4670,7 +4670,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123306062</v>
+        <v>123304342</v>
       </c>
       <c r="B37" t="n">
         <v>92271</v>
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580126</v>
+        <v>580158</v>
       </c>
       <c r="R37" t="n">
-        <v>7049722</v>
+        <v>7049670</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4770,12 +4770,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4894,10 +4894,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123306094</v>
+        <v>123303786</v>
       </c>
       <c r="B39" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4910,34 +4910,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580111</v>
+        <v>580193</v>
       </c>
       <c r="R39" t="n">
-        <v>7049724</v>
+        <v>7049674</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4969,7 +4974,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4979,7 +4984,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4994,22 +5004,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123307035</v>
+        <v>123303674</v>
       </c>
       <c r="B40" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5022,39 +5032,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>579970</v>
+        <v>580206</v>
       </c>
       <c r="R40" t="n">
-        <v>7049717</v>
+        <v>7049658</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5086,7 +5091,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5096,7 +5101,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5123,10 +5128,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123307802</v>
+        <v>123306520</v>
       </c>
       <c r="B41" t="n">
-        <v>82575</v>
+        <v>98079</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5135,38 +5140,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580037</v>
+        <v>580082</v>
       </c>
       <c r="R41" t="n">
-        <v>7049768</v>
+        <v>7049717</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5198,7 +5207,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5208,7 +5217,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5235,7 +5244,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123307659</v>
+        <v>123307927</v>
       </c>
       <c r="B42" t="n">
         <v>79869</v>
@@ -5275,10 +5284,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580022</v>
+        <v>580078</v>
       </c>
       <c r="R42" t="n">
-        <v>7049763</v>
+        <v>7049752</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5310,7 +5319,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5320,7 +5329,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5347,7 +5356,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123307482</v>
+        <v>123305387</v>
       </c>
       <c r="B43" t="n">
         <v>78788</v>
@@ -5387,10 +5396,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>579986</v>
+        <v>580124</v>
       </c>
       <c r="R43" t="n">
-        <v>7049735</v>
+        <v>7049764</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5422,7 +5431,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5432,7 +5441,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5447,22 +5456,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123305011</v>
+        <v>123307604</v>
       </c>
       <c r="B44" t="n">
-        <v>90990</v>
+        <v>82575</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5475,21 +5484,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5499,10 +5508,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580151</v>
+        <v>580021</v>
       </c>
       <c r="R44" t="n">
-        <v>7049633</v>
+        <v>7049755</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5534,7 +5543,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5544,7 +5553,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5571,10 +5580,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123303786</v>
+        <v>123304722</v>
       </c>
       <c r="B45" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5587,39 +5596,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580193</v>
+        <v>580163</v>
       </c>
       <c r="R45" t="n">
-        <v>7049674</v>
+        <v>7049654</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5651,7 +5655,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5661,12 +5665,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5693,7 +5692,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123308088</v>
+        <v>123305019</v>
       </c>
       <c r="B46" t="n">
         <v>57491</v>
@@ -5729,7 +5728,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5738,10 +5737,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580037</v>
+        <v>580166</v>
       </c>
       <c r="R46" t="n">
-        <v>7049732</v>
+        <v>7049779</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5773,7 +5772,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5783,7 +5782,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5803,22 +5802,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123306981</v>
+        <v>123304879</v>
       </c>
       <c r="B47" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5827,38 +5826,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580007</v>
+        <v>580143</v>
       </c>
       <c r="R47" t="n">
-        <v>7049703</v>
+        <v>7049655</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5890,7 +5893,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5900,7 +5903,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5927,7 +5930,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123304722</v>
+        <v>123309182</v>
       </c>
       <c r="B48" t="n">
         <v>78788</v>
@@ -5967,10 +5970,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580163</v>
+        <v>580139</v>
       </c>
       <c r="R48" t="n">
-        <v>7049654</v>
+        <v>7049712</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6002,7 +6005,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6012,7 +6015,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6155,10 +6158,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123306199</v>
+        <v>123307659</v>
       </c>
       <c r="B50" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6167,42 +6170,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580119</v>
+        <v>580022</v>
       </c>
       <c r="R50" t="n">
-        <v>7049689</v>
+        <v>7049763</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6234,7 +6233,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6244,7 +6243,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6271,10 +6270,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123307604</v>
+        <v>123307482</v>
       </c>
       <c r="B51" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6287,21 +6286,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6311,10 +6310,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>580021</v>
+        <v>579986</v>
       </c>
       <c r="R51" t="n">
-        <v>7049755</v>
+        <v>7049735</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6346,7 +6345,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6356,7 +6355,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6383,10 +6382,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123306694</v>
+        <v>123307035</v>
       </c>
       <c r="B52" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6395,30 +6394,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6427,10 +6427,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>580043</v>
+        <v>579970</v>
       </c>
       <c r="R52" t="n">
-        <v>7049753</v>
+        <v>7049717</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6487,12 +6487,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -3070,10 +3070,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123307517</v>
+        <v>123304172</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3082,38 +3082,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580020</v>
+        <v>580186</v>
       </c>
       <c r="R23" t="n">
-        <v>7049752</v>
+        <v>7049672</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3145,7 +3154,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3155,7 +3164,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3170,22 +3179,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123304811</v>
+        <v>123308088</v>
       </c>
       <c r="B24" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3198,34 +3207,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580141</v>
+        <v>580037</v>
       </c>
       <c r="R24" t="n">
-        <v>7049654</v>
+        <v>7049732</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3257,7 +3271,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3267,7 +3281,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3294,10 +3313,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123304172</v>
+        <v>123306062</v>
       </c>
       <c r="B25" t="n">
-        <v>98079</v>
+        <v>92271</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3306,47 +3325,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580186</v>
+        <v>580126</v>
       </c>
       <c r="R25" t="n">
-        <v>7049672</v>
+        <v>7049722</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3378,7 +3388,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3388,7 +3398,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3415,10 +3425,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123306062</v>
+        <v>123307517</v>
       </c>
       <c r="B26" t="n">
-        <v>92271</v>
+        <v>78788</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3427,25 +3437,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3455,10 +3465,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580126</v>
+        <v>580020</v>
       </c>
       <c r="R26" t="n">
-        <v>7049722</v>
+        <v>7049752</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3490,7 +3500,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3500,7 +3510,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3515,22 +3525,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123308088</v>
+        <v>123304811</v>
       </c>
       <c r="B27" t="n">
-        <v>57491</v>
+        <v>79869</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3543,39 +3553,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580037</v>
+        <v>580141</v>
       </c>
       <c r="R27" t="n">
-        <v>7049732</v>
+        <v>7049654</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3607,7 +3612,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3617,12 +3622,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4782,10 +4782,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123303895</v>
+        <v>123303786</v>
       </c>
       <c r="B38" t="n">
-        <v>92271</v>
+        <v>57491</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4794,38 +4794,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580189</v>
+        <v>580193</v>
       </c>
       <c r="R38" t="n">
-        <v>7049660</v>
+        <v>7049674</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4857,7 +4862,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4867,7 +4872,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4894,10 +4904,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123303786</v>
+        <v>123303895</v>
       </c>
       <c r="B39" t="n">
-        <v>57491</v>
+        <v>92271</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4906,43 +4916,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580193</v>
+        <v>580189</v>
       </c>
       <c r="R39" t="n">
-        <v>7049674</v>
+        <v>7049660</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4974,7 +4979,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4984,12 +4989,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6497,6 +6497,725 @@
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>127645449</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79018</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>580068</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7049781</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>127645196</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>580141</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7049779</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>127645486</v>
+      </c>
+      <c r="B55" t="n">
+        <v>80150</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>580063</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7049769</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>127644712</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91491</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>580205</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7049660</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>127645717</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78685</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>353</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>579964</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7049697</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>127644969</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>580158</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7049727</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>127645627</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>579980</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7049714</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -6502,7 +6502,7 @@
         <v>127645449</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>127645196</v>
       </c>
       <c r="B54" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>127645486</v>
       </c>
       <c r="B55" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>127644712</v>
       </c>
       <c r="B56" t="n">
-        <v>91491</v>
+        <v>91493</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>127645717</v>
       </c>
       <c r="B57" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>127644969</v>
       </c>
       <c r="B58" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>127645627</v>
       </c>
       <c r="B59" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -6823,7 +6823,7 @@
         <v>127644712</v>
       </c>
       <c r="B56" t="n">
-        <v>91493</v>
+        <v>91499</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>127645627</v>
       </c>
       <c r="B59" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -6502,7 +6502,7 @@
         <v>127645449</v>
       </c>
       <c r="B53" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>127645196</v>
       </c>
       <c r="B54" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>127645486</v>
       </c>
       <c r="B55" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>127644712</v>
       </c>
       <c r="B56" t="n">
-        <v>91499</v>
+        <v>91502</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>127645717</v>
       </c>
       <c r="B57" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>127644969</v>
       </c>
       <c r="B58" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>127645627</v>
       </c>
       <c r="B59" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -6502,7 +6502,7 @@
         <v>127645449</v>
       </c>
       <c r="B53" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>127645196</v>
       </c>
       <c r="B54" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>127645486</v>
       </c>
       <c r="B55" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>127644712</v>
       </c>
       <c r="B56" t="n">
-        <v>91502</v>
+        <v>91510</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>127645717</v>
       </c>
       <c r="B57" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>127644969</v>
       </c>
       <c r="B58" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>127645627</v>
       </c>
       <c r="B59" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -6823,7 +6823,7 @@
         <v>127644712</v>
       </c>
       <c r="B56" t="n">
-        <v>91510</v>
+        <v>91511</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>127645627</v>
       </c>
       <c r="B59" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -6823,7 +6823,7 @@
         <v>127644712</v>
       </c>
       <c r="B56" t="n">
-        <v>91511</v>
+        <v>91512</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>127645627</v>
       </c>
       <c r="B59" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -6823,7 +6823,7 @@
         <v>127644712</v>
       </c>
       <c r="B56" t="n">
-        <v>91512</v>
+        <v>91513</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>127645627</v>
       </c>
       <c r="B59" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118644684</v>
+        <v>127645717</v>
       </c>
       <c r="B2" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nipan (Nipan), Ång</t>
+          <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580133</v>
+        <v>579964</v>
       </c>
       <c r="R2" t="n">
-        <v>7049804</v>
+        <v>7049697</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>23:19</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>23:19</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,66 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118643973</v>
+        <v>123305011</v>
       </c>
       <c r="B3" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nipan (Nipan), Ång</t>
+          <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580064</v>
+        <v>580151</v>
       </c>
       <c r="R3" t="n">
-        <v>7049713</v>
+        <v>7049633</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,22 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118643561</v>
+        <v>123305088</v>
       </c>
       <c r="B4" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,39 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nipan (Nipan), Ång</t>
+          <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580118</v>
+        <v>580164</v>
       </c>
       <c r="R4" t="n">
-        <v>7049814</v>
+        <v>7049642</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,22 +944,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22:09</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>22:09</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,15 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118644513</v>
+        <v>123308517</v>
       </c>
       <c r="B5" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,39 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nipan (Nipan), Ång</t>
+          <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580057</v>
+        <v>580100</v>
       </c>
       <c r="R5" t="n">
-        <v>7049777</v>
+        <v>7049758</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,22 +1051,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,54 +1093,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118644504</v>
+        <v>123309023</v>
       </c>
       <c r="B6" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nipan (Nipan), Ång</t>
+          <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580053</v>
+        <v>580106</v>
       </c>
       <c r="R6" t="n">
-        <v>7049779</v>
+        <v>7049714</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,22 +1158,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,15 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118644154</v>
+        <v>127645627</v>
       </c>
       <c r="B7" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,34 +1211,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nipan (Nipan), Ång</t>
+          <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579992</v>
+        <v>579980</v>
       </c>
       <c r="R7" t="n">
-        <v>7049709</v>
+        <v>7049714</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,22 +1265,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,15 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118643173</v>
+        <v>123307604</v>
       </c>
       <c r="B8" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,34 +1318,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nipan (Nipan), Ång</t>
+          <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580202</v>
+        <v>580021</v>
       </c>
       <c r="R8" t="n">
-        <v>7049653</v>
+        <v>7049755</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,22 +1372,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,15 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118644547</v>
+        <v>123307802</v>
       </c>
       <c r="B9" t="n">
-        <v>78229</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,34 +1425,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nipan (Nipan), Ång</t>
+          <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580056</v>
+        <v>580037</v>
       </c>
       <c r="R9" t="n">
-        <v>7049785</v>
+        <v>7049768</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,22 +1479,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>23:08</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>23:08</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,15 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118644274</v>
+        <v>127644712</v>
       </c>
       <c r="B10" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,41 +1532,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nipan (Nipan), Ång</t>
+          <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579969</v>
+        <v>580205</v>
       </c>
       <c r="R10" t="n">
-        <v>7049721</v>
+        <v>7049660</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1667,22 +1586,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>22:47</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>22:47</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,27 +1606,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118643749</v>
+        <v>123303895</v>
       </c>
       <c r="B11" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1725,39 +1629,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nipan (Nipan), Ång</t>
+          <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580116</v>
+        <v>580189</v>
       </c>
       <c r="R11" t="n">
-        <v>7049726</v>
+        <v>7049660</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,22 +1683,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1826,54 +1725,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123308246</v>
+        <v>123304342</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580053</v>
+        <v>580158</v>
       </c>
       <c r="R12" t="n">
-        <v>7049735</v>
+        <v>7049670</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1795,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1805,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,15 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123307053</v>
+        <v>123304706</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1958,21 +1843,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1982,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579979</v>
+        <v>580179</v>
       </c>
       <c r="R13" t="n">
-        <v>7049720</v>
+        <v>7049708</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +1902,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +1912,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,27 +1927,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123308517</v>
+        <v>123306062</v>
       </c>
       <c r="B14" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2094,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580100</v>
+        <v>580126</v>
       </c>
       <c r="R14" t="n">
-        <v>7049758</v>
+        <v>7049722</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2009,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2019,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,27 +2034,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123307914</v>
+        <v>123307433</v>
       </c>
       <c r="B15" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2206,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580053</v>
+        <v>579944</v>
       </c>
       <c r="R15" t="n">
-        <v>7049758</v>
+        <v>7049716</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2116,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,7 +2126,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,37 +2153,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123306094</v>
+        <v>118643173</v>
       </c>
       <c r="B16" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2318,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580111</v>
+        <v>580202</v>
       </c>
       <c r="R16" t="n">
-        <v>7049724</v>
+        <v>7049653</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2348,22 +2218,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,27 +2248,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123306694</v>
+        <v>118644154</v>
       </c>
       <c r="B17" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,38 +2271,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580043</v>
+        <v>579992</v>
       </c>
       <c r="R17" t="n">
-        <v>7049753</v>
+        <v>7049709</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2464,22 +2325,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,49 +2355,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123309023</v>
+        <v>123303674</v>
       </c>
       <c r="B18" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2546,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580106</v>
+        <v>580206</v>
       </c>
       <c r="R18" t="n">
-        <v>7049714</v>
+        <v>7049658</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,7 +2437,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2447,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,37 +2474,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123304706</v>
+        <v>123304722</v>
       </c>
       <c r="B19" t="n">
-        <v>92271</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2658,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580179</v>
+        <v>580163</v>
       </c>
       <c r="R19" t="n">
-        <v>7049708</v>
+        <v>7049654</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2693,7 +2544,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2703,7 +2554,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2718,49 +2569,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123305088</v>
+        <v>123305387</v>
       </c>
       <c r="B20" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2770,10 +2616,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580164</v>
+        <v>580124</v>
       </c>
       <c r="R20" t="n">
-        <v>7049642</v>
+        <v>7049764</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2830,12 +2676,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2845,16 +2691,11 @@
         <v>123306079</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2954,15 +2795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123305283</v>
+        <v>123306849</v>
       </c>
       <c r="B22" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2970,38 +2806,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580160</v>
+        <v>580039</v>
       </c>
       <c r="R22" t="n">
-        <v>7049663</v>
+        <v>7049688</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3033,7 +2865,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3043,7 +2875,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3070,15 +2902,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123304172</v>
+        <v>123306981</v>
       </c>
       <c r="B23" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,43 +2913,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580186</v>
+        <v>580007</v>
       </c>
       <c r="R23" t="n">
-        <v>7049672</v>
+        <v>7049703</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3154,7 +2972,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3164,7 +2982,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3179,67 +2997,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123308088</v>
+        <v>123307053</v>
       </c>
       <c r="B24" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>580037</v>
+        <v>579979</v>
       </c>
       <c r="R24" t="n">
-        <v>7049732</v>
+        <v>7049720</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3271,7 +3079,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3281,12 +3089,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3313,37 +3116,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123306062</v>
+        <v>123307482</v>
       </c>
       <c r="B25" t="n">
-        <v>92271</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3353,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580126</v>
+        <v>579986</v>
       </c>
       <c r="R25" t="n">
-        <v>7049722</v>
+        <v>7049735</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3388,7 +3186,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3398,7 +3196,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3413,12 +3211,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3428,16 +3226,11 @@
         <v>123307517</v>
       </c>
       <c r="B26" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3537,37 +3330,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123304811</v>
+        <v>123307810</v>
       </c>
       <c r="B27" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3577,10 +3365,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580141</v>
+        <v>580037</v>
       </c>
       <c r="R27" t="n">
-        <v>7049654</v>
+        <v>7049763</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3612,7 +3400,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3622,7 +3410,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3649,15 +3437,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123304880</v>
+        <v>123309182</v>
       </c>
       <c r="B28" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3665,43 +3448,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580159</v>
+        <v>580139</v>
       </c>
       <c r="R28" t="n">
-        <v>7049755</v>
+        <v>7049712</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3733,7 +3507,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3743,7 +3517,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3758,31 +3532,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123306981</v>
+        <v>123309206</v>
       </c>
       <c r="B29" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3810,10 +3579,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580007</v>
+        <v>580174</v>
       </c>
       <c r="R29" t="n">
-        <v>7049703</v>
+        <v>7049673</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3845,7 +3614,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3855,7 +3624,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3882,19 +3651,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123309206</v>
+        <v>127645449</v>
       </c>
       <c r="B30" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3922,10 +3686,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580174</v>
+        <v>580068</v>
       </c>
       <c r="R30" t="n">
-        <v>7049673</v>
+        <v>7049781</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3952,22 +3716,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3994,15 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123306849</v>
+        <v>118644547</v>
       </c>
       <c r="B31" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4010,21 +3769,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4034,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580039</v>
+        <v>580056</v>
       </c>
       <c r="R31" t="n">
-        <v>7049688</v>
+        <v>7049785</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4064,22 +3823,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>23:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>23:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4106,15 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123308600</v>
+        <v>127644969</v>
       </c>
       <c r="B32" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4122,21 +3876,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4146,13 +3900,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>580103</v>
+        <v>580158</v>
       </c>
       <c r="R32" t="n">
-        <v>7049748</v>
+        <v>7049727</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4176,22 +3930,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:29</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:29</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4206,27 +3950,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123305011</v>
+        <v>123304811</v>
       </c>
       <c r="B33" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4234,21 +3973,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4258,10 +3997,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>580151</v>
+        <v>580141</v>
       </c>
       <c r="R33" t="n">
-        <v>7049633</v>
+        <v>7049654</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4293,7 +4032,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4303,7 +4042,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4330,15 +4069,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123307810</v>
+        <v>123306094</v>
       </c>
       <c r="B34" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4346,21 +4080,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4370,10 +4104,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>580037</v>
+        <v>580111</v>
       </c>
       <c r="R34" t="n">
-        <v>7049763</v>
+        <v>7049724</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4405,7 +4139,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4415,7 +4149,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4430,27 +4164,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123307802</v>
+        <v>123307659</v>
       </c>
       <c r="B35" t="n">
-        <v>82575</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4458,21 +4187,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4482,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>580037</v>
+        <v>580022</v>
       </c>
       <c r="R35" t="n">
-        <v>7049768</v>
+        <v>7049763</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4517,7 +4246,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4527,7 +4256,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4554,54 +4283,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123306199</v>
+        <v>123307914</v>
       </c>
       <c r="B36" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>580119</v>
+        <v>580053</v>
       </c>
       <c r="R36" t="n">
-        <v>7049689</v>
+        <v>7049758</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4633,7 +4353,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4643,7 +4363,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4670,37 +4390,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123304342</v>
+        <v>123307927</v>
       </c>
       <c r="B37" t="n">
-        <v>92271</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4710,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>580158</v>
+        <v>580078</v>
       </c>
       <c r="R37" t="n">
-        <v>7049670</v>
+        <v>7049752</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4745,7 +4460,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4755,7 +4470,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4782,15 +4497,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123303786</v>
+        <v>123308600</v>
       </c>
       <c r="B38" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4798,39 +4508,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>580193</v>
+        <v>580103</v>
       </c>
       <c r="R38" t="n">
-        <v>7049674</v>
+        <v>7049748</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4862,7 +4567,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4872,12 +4577,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4904,15 +4604,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123303895</v>
+        <v>127645486</v>
       </c>
       <c r="B39" t="n">
-        <v>92271</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4920,21 +4615,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4944,13 +4639,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>580189</v>
+        <v>580063</v>
       </c>
       <c r="R39" t="n">
-        <v>7049660</v>
+        <v>7049769</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4974,22 +4669,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>12:57</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>12:57</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5004,62 +4689,62 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123303674</v>
+        <v>118644513</v>
       </c>
       <c r="B40" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>580206</v>
+        <v>580057</v>
       </c>
       <c r="R40" t="n">
-        <v>7049658</v>
+        <v>7049777</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5086,22 +4771,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5128,42 +4813,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123306520</v>
+        <v>123307035</v>
       </c>
       <c r="B41" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5172,7 +4853,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>580082</v>
+        <v>579970</v>
       </c>
       <c r="R41" t="n">
         <v>7049717</v>
@@ -5207,7 +4888,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5217,7 +4898,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5244,15 +4925,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123307927</v>
+        <v>118643561</v>
       </c>
       <c r="B42" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5260,34 +4936,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>580078</v>
+        <v>580118</v>
       </c>
       <c r="R42" t="n">
-        <v>7049752</v>
+        <v>7049814</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5314,22 +4995,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5356,15 +5037,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123305387</v>
+        <v>118643749</v>
       </c>
       <c r="B43" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5372,34 +5048,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>580124</v>
+        <v>580116</v>
       </c>
       <c r="R43" t="n">
-        <v>7049764</v>
+        <v>7049726</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5426,22 +5107,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5456,27 +5137,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123307604</v>
+        <v>118644129</v>
       </c>
       <c r="B44" t="n">
-        <v>82575</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5484,34 +5160,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>580021</v>
+        <v>580020</v>
       </c>
       <c r="R44" t="n">
-        <v>7049755</v>
+        <v>7049677</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5538,22 +5219,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5580,15 +5261,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123304722</v>
+        <v>118644592</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5596,34 +5272,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>580163</v>
+        <v>580054</v>
       </c>
       <c r="R45" t="n">
-        <v>7049654</v>
+        <v>7049792</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5650,22 +5331,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>23:09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>23:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5692,15 +5373,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123305019</v>
+        <v>118644929</v>
       </c>
       <c r="B46" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5737,10 +5413,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>580166</v>
+        <v>580191</v>
       </c>
       <c r="R46" t="n">
-        <v>7049779</v>
+        <v>7049762</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5767,27 +5443,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5802,54 +5473,50 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123304879</v>
+        <v>123303786</v>
       </c>
       <c r="B47" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5858,10 +5525,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>580143</v>
+        <v>580193</v>
       </c>
       <c r="R47" t="n">
-        <v>7049655</v>
+        <v>7049674</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5893,7 +5560,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5903,7 +5570,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5930,15 +5602,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123309182</v>
+        <v>123305019</v>
       </c>
       <c r="B48" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5946,34 +5613,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>580139</v>
+        <v>580166</v>
       </c>
       <c r="R48" t="n">
-        <v>7049712</v>
+        <v>7049779</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6005,7 +5677,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6015,7 +5687,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6030,54 +5707,50 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123307841</v>
+        <v>123308088</v>
       </c>
       <c r="B49" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6086,10 +5759,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>580049</v>
+        <v>580037</v>
       </c>
       <c r="R49" t="n">
-        <v>7049765</v>
+        <v>7049732</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6121,7 +5794,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6131,7 +5804,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6158,15 +5836,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123307659</v>
+        <v>127645196</v>
       </c>
       <c r="B50" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6174,34 +5847,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>580022</v>
+        <v>580141</v>
       </c>
       <c r="R50" t="n">
-        <v>7049763</v>
+        <v>7049779</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6228,22 +5906,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6270,50 +5953,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123307482</v>
+        <v>118643973</v>
       </c>
       <c r="B51" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>579986</v>
+        <v>580064</v>
       </c>
       <c r="R51" t="n">
-        <v>7049735</v>
+        <v>7049713</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6340,22 +6022,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6382,43 +6064,37 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123307035</v>
+        <v>118644274</v>
       </c>
       <c r="B52" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6427,10 +6103,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>579970</v>
+        <v>579969</v>
       </c>
       <c r="R52" t="n">
-        <v>7049717</v>
+        <v>7049721</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6457,22 +6133,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6499,45 +6175,49 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127645449</v>
+        <v>118644504</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>580068</v>
+        <v>580053</v>
       </c>
       <c r="R53" t="n">
-        <v>7049781</v>
+        <v>7049779</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6564,22 +6244,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>23:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6606,38 +6286,37 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127645196</v>
+        <v>118644684</v>
       </c>
       <c r="B54" t="n">
-        <v>57672</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6646,10 +6325,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>580141</v>
+        <v>580133</v>
       </c>
       <c r="R54" t="n">
-        <v>7049779</v>
+        <v>7049804</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6676,27 +6355,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:59</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>23:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6723,48 +6397,57 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127645486</v>
+        <v>123304172</v>
       </c>
       <c r="B55" t="n">
-        <v>80161</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>580063</v>
+        <v>580186</v>
       </c>
       <c r="R55" t="n">
-        <v>7049769</v>
+        <v>7049672</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6788,12 +6471,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6808,22 +6501,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127644712</v>
+        <v>123304879</v>
       </c>
       <c r="B56" t="n">
-        <v>91513</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6831,37 +6524,41 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>580205</v>
+        <v>580143</v>
       </c>
       <c r="R56" t="n">
-        <v>7049660</v>
+        <v>7049655</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6885,12 +6582,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6905,60 +6612,69 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127645717</v>
+        <v>123304880</v>
       </c>
       <c r="B57" t="n">
-        <v>78696</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>579964</v>
+        <v>580159</v>
       </c>
       <c r="R57" t="n">
-        <v>7049697</v>
+        <v>7049755</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6982,12 +6698,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7002,60 +6728,64 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127644969</v>
+        <v>123305283</v>
       </c>
       <c r="B58" t="n">
-        <v>78787</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>580158</v>
+        <v>580160</v>
       </c>
       <c r="R58" t="n">
-        <v>7049727</v>
+        <v>7049663</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7079,12 +6809,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7099,57 +6839,61 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127645627</v>
+        <v>123306199</v>
       </c>
       <c r="B59" t="n">
-        <v>91352</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Nipan, Nipan, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>579980</v>
+        <v>580119</v>
       </c>
       <c r="R59" t="n">
-        <v>7049714</v>
+        <v>7049689</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7176,22 +6920,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7215,6 +6959,450 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>123306520</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>580082</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7049717</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>123306694</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>580043</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7049753</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>123307841</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>580049</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7049765</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>123308246</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Nipan, Nipan, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>580053</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7049735</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30571-2024 artfynd.xlsx
+++ b/artfynd/A 30571-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127645717</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123305011</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123305088</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123308517</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123309023</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127645627</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123307604</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123307802</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127644712</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123303895</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123304342</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1936,6 +1996,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123304706</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2043,6 +2108,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123306062</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2150,6 +2220,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123307433</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2257,6 +2332,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118643173</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2364,6 +2444,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644154</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2471,6 +2556,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123303674</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2578,6 +2668,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123304722</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2685,6 +2780,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123305387</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2792,6 +2892,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123306079</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2899,6 +3004,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123306849</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3006,6 +3116,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123306981</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3113,6 +3228,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123307053</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3220,6 +3340,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123307482</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3327,6 +3452,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123307517</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3434,6 +3564,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123307810</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3541,6 +3676,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123309182</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3648,6 +3788,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123309206</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3755,6 +3900,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127645449</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3862,6 +4012,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644547</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3959,6 +4114,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127644969</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4066,6 +4226,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123304811</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4173,6 +4338,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123306094</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4280,6 +4450,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123307659</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4387,6 +4562,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123307914</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4494,6 +4674,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123307927</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4601,6 +4786,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123308600</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4698,6 +4888,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127645486</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4810,6 +5005,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644513</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4922,6 +5122,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123307035</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5034,6 +5239,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118643561</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5146,6 +5356,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118643749</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5258,6 +5473,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644129</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5370,6 +5590,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644592</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5482,6 +5707,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644929</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5599,6 +5829,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123303786</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5716,6 +5951,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123305019</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5833,6 +6073,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123308088</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5950,6 +6195,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127645196</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6061,6 +6311,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118643973</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6172,6 +6427,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644274</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6283,6 +6543,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644504</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6394,6 +6659,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118644684</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6510,6 +6780,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123304172</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6621,6 +6896,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123304879</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6737,6 +7017,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123304880</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6848,6 +7133,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123305283</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6959,6 +7249,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123306199</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7070,6 +7365,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123306520</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7181,6 +7481,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123306694</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7292,6 +7597,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123307841</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7403,8 +7713,77 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123308246</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>